--- a/output/源清单.xlsx
+++ b/output/源清单.xlsx
@@ -4641,17 +4641,17 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>分类实测</t>
+          <t>域名/标记</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>存活</t>
+          <t>失活</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>18禁/动漫</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -4660,13 +4660,9 @@
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>国产情色 | 日本无码 | AV明星 | 中文字幕 | 网红主播 | 成人动漫 | 欧美情色 | 国模私拍 | 长腿丝袜 | 邻家人妻 | 韩国伦理 | 香港伦理 | 精品推荐 | 原纱央莉 | 柚木TINA | 大桥未久 | AV明星1 | 仁科百华 | 天海翼 | 小川阿佐美</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
@@ -6629,17 +6625,17 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>域名/标记</t>
+          <t>上游标记</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>存活/非标准</t>
+          <t>存活</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>动漫/影视/短剧</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
@@ -6648,9 +6644,13 @@
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K107" s="2" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>国产区 | AV区 | 欧美区 | 动漫区 | 网红主播 | 国产传媒 | 探花系列 | 人妻熟女 | 日本无码 | 美乳巨乳 | 强制侵犯 | 制服诱惑 | 绝色佳人 | 风俗泡泡浴 | 家庭乱伦 | AV解说 | 三级电影 | 少女萝莉 | SM调教 | 绝顶潮吹</t>
+        </is>
+      </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
           <t>sp696</t>
@@ -8637,17 +8637,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>分类实测</t>
+          <t>域名/标记</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>存活</t>
+          <t>失活</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>18禁/动漫</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -8656,13 +8656,9 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>7</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>国产情色 | 日本无码 | AV明星 | 中文字幕 | 网红主播 | 成人动漫 | 欧美情色 | 国模私拍 | 长腿丝袜 | 邻家人妻 | 韩国伦理 | 香港伦理 | 精品推荐 | 原纱央莉 | 柚木TINA | 大桥未久 | AV明星1 | 仁科百华 | 天海翼 | 小川阿佐美</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
@@ -9085,17 +9081,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>域名/标记</t>
+          <t>上游标记</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>存活/非标准</t>
+          <t>存活</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>动漫/影视/短剧</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -9104,9 +9100,13 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>国产区 | AV区 | 欧美区 | 动漫区 | 网红主播 | 国产传媒 | 探花系列 | 人妻熟女 | 日本无码 | 美乳巨乳 | 强制侵犯 | 制服诱惑 | 绝色佳人 | 风俗泡泡浴 | 家庭乱伦 | AV解说 | 三级电影 | 少女萝莉 | SM调教 | 绝顶潮吹</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>sp696</t>

--- a/output/源清单.xlsx
+++ b/output/源清单.xlsx
@@ -4641,17 +4641,17 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>域名/标记</t>
+          <t>分类实测</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>失活</t>
+          <t>存活</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>18禁/动漫</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -4660,9 +4660,13 @@
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" s="2" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>国产情色 | 日本无码 | AV明星 | 中文字幕 | 网红主播 | 成人动漫 | 欧美情色 | 国模私拍 | 长腿丝袜 | 邻家人妻 | 韩国伦理 | 香港伦理 | 精品推荐 | 原纱央莉 | 柚木TINA | 大桥未久 | AV明星1 | 仁科百华 | 天海翼 | 小川阿佐美</t>
+        </is>
+      </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
@@ -8637,17 +8641,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>域名/标记</t>
+          <t>分类实测</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>失活</t>
+          <t>存活</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>18禁/动漫</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -8656,9 +8660,13 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>国产情色 | 日本无码 | AV明星 | 中文字幕 | 网红主播 | 成人动漫 | 欧美情色 | 国模私拍 | 长腿丝袜 | 邻家人妻 | 韩国伦理 | 香港伦理 | 精品推荐 | 原纱央莉 | 柚木TINA | 大桥未久 | AV明星1 | 仁科百华 | 天海翼 | 小川阿佐美</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>

--- a/output/源清单.xlsx
+++ b/output/源清单.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="源清单" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18禁源" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="播放测速" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L118"/>
+  <dimension ref="A1:M118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.6" customWidth="1" min="1" max="1"/>
@@ -440,11 +441,12 @@
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="9.600000000000001" customWidth="1" min="7" max="7"/>
-    <col width="12.8" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="12.8" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="60" customWidth="1" min="11" max="11"/>
-    <col width="52.8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
+    <col width="52.8" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -485,25 +487,30 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>响应ms</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>内容标签</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>含成人栏目</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>成人栏目数</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>分类名</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
@@ -545,25 +552,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" t="n">
+        <v>1361</v>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>1</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 台湾剧 | 韩国剧 | 欧美剧 | 香港剧 | 泰国剧 | 日本剧 | 福利 | 记录片</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置</t>
         </is>
@@ -605,25 +615,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="n">
+        <v>265</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>18禁/动漫</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="n">
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>无码专区 | 麻豆传媒 | 制服诱惑 | 三级伦理 | AI换脸 | 中文字幕 | 卡通动漫 | 欧美系列 | 美女主播 | 国产自拍 | 熟女人妻 | 萝莉少女 | 女同性爱 | 多人群交 | 美乳巨乳 | 强奸乱伦 | 生活都市 | 不偷恋情 | 学生校园 | 人妻熟女</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -665,25 +678,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" t="n">
+        <v>2277</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 伦理片 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 韩国剧 | 欧美剧 | 体育 | NBA | 惊悚片 | 家庭篇</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,cmliu配置</t>
         </is>
@@ -725,25 +741,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" t="n">
+        <v>492</v>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>伦理片 | 教程</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -785,25 +804,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" t="n">
+        <v>7679</v>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 港澳剧 | 日剧 | 欧美剧 | 动漫电影 | 台湾剧 | 韩剧 | 泰剧 | 记录片</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库3,cmliu配置</t>
         </is>
@@ -845,25 +867,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" t="n">
+        <v>5053</v>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 港澳剧 | 日剧 | 欧美剧 | 动漫电影 | 台湾剧 | 韩剧 | 泰剧 | 记录片</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置,sp696</t>
         </is>
@@ -905,25 +930,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" t="n">
+        <v>507</v>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 伦理片 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 惊悚片 | 家庭片 | 古装片 | 历史片 | 悬疑片 | 犯罪片 | 灾难片 | 记录片</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -945,7 +973,6 @@
           <t>https://api.wujinapi.cc/api.php/provide/vod</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>否</t>
@@ -961,25 +988,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" t="n">
+        <v>87</v>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>6</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 资讯 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 台湾剧 | 美国剧 | 公告 | 头条 | 伦理片 | 纪录片</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置</t>
         </is>
@@ -1021,25 +1051,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" t="n">
+        <v>677</v>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>6</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 欧美剧 | 韩剧 | 日剧 | 港剧 | 台剧 | 泰剧 | 纪录片 | 海外剧</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置,sp696</t>
         </is>
@@ -1081,25 +1114,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" t="n">
+        <v>497</v>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 剧情片 | 恐怖片 | 战争片 | 大陆剧 | 欧美剧 | 港澳剧 | 韩剧 | 动漫电影 | 日剧 | 台湾剧 | 泰剧 | 记录片</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置,sp696</t>
         </is>
@@ -1141,21 +1177,23 @@
           <t>存活/非标准</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H12" t="n">
+        <v>104</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -1177,7 +1215,6 @@
           <t>https://collect.wolongzy.cc/api.php/provide/vod</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>否</t>
@@ -1203,11 +1240,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -1249,21 +1290,23 @@
           <t>存活/非标准</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H14" t="n">
+        <v>100</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,sp696</t>
         </is>
@@ -1305,25 +1348,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" t="n">
+        <v>504</v>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 欧美剧 | 韩国剧 | 日本剧 | 港台剧 | 台湾剧 | 泰国剧 | 纪录片 | 海外剧</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,cmliu配置</t>
         </is>
@@ -1365,25 +1411,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" t="n">
+        <v>4002</v>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>电影片 | 连续剧 | 综艺片 | 动漫片 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 韩国剧 | 欧美剧 | 记录片 | 台湾剧 | 日本剧 | 海外剧 | 泰国剧</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,sp696</t>
         </is>
@@ -1435,11 +1484,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J17" t="n">
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版</t>
         </is>
@@ -1481,25 +1534,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" t="n">
+        <v>476</v>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>电影 | 电视剧 | 动漫 | 综艺 | 纪录片 | 动作片 | 爱情片 | 科幻片 | 战争片 | 剧情片 | 恐怖片 | 喜剧片 | 大陆剧 | 港澳剧 | 台湾剧 | 欧美剧 | 动画片 | 韩剧 | 日剧 | 泰剧</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -1541,25 +1597,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" t="n">
+        <v>270</v>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>6</v>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 资讯 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 台湾剧 | 美国剧 | 公告 | 头条 | 伦理片 | 纪录片</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置,sp696</t>
         </is>
@@ -1601,25 +1660,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" t="n">
+        <v>281</v>
+      </c>
+      <c r="I20" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>6</v>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 资讯 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 台湾剧 | 美国剧 | 公告 | 头条 | 伦理片 | 纪录片</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -1641,7 +1703,6 @@
           <t>https://api.wujinapi.net/api.php/provide/vod</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>否</t>
@@ -1657,25 +1718,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" t="n">
+        <v>646</v>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>6</v>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 资讯 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 台湾剧 | 美国剧 | 公告 | 头条 | 伦理片 | 纪录片</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置</t>
         </is>
@@ -1717,21 +1781,23 @@
           <t>存活/非标准</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H22" t="n">
+        <v>860</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J22" t="n">
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
         <v>0</v>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,sp696</t>
         </is>
@@ -1773,21 +1839,23 @@
           <t>存活/非标准</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H23" t="n">
+        <v>830</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J23" t="n">
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
         <v>0</v>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -1829,25 +1897,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H24" t="n">
+        <v>821</v>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>电影片 | 动作片 | 喜剧片 | 恐怖片 | 科幻片 | 爱情片 | 剧情片 | 战争片 | 纪录片 | 理论片 | 连续剧 | 国产剧 | 欧美剧 | 香港剧 | 韩国剧 | 台湾剧 | 日本剧 | 海外剧 | 泰国剧 | 动漫片</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -1889,25 +1960,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H25" t="n">
+        <v>395</v>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>6</v>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 欧美剧 | 韩剧 | 日剧 | 港剧 | 台剧 | 泰剧 | 纪录片 | 海外剧</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置,sp696</t>
         </is>
@@ -1949,25 +2023,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26" t="n">
+        <v>233</v>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>6</v>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 欧美剧 | 韩剧 | 日剧 | 港剧 | 台剧 | 泰剧 | 纪录片 | 海外剧</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -2009,25 +2086,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H27" t="n">
+        <v>364</v>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>动漫/影视</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 资讯 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 台湾剧 | 韩国剧 | 公告 | 头条 | 犯罪片 | 纪录片</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -2049,7 +2129,6 @@
           <t>https://api.yparse.com/api/json</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>否</t>
@@ -2065,25 +2144,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H28" t="n">
+        <v>1567</v>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>2</v>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>动漫 | 综艺 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 战争片 | 国产剧 | 香港剧 | 欧美剧 | 日本剧 | 海外剧 | 台湾剧 | 韩国剧 | 泰国剧 | 剧情片 | 纪录片 | 动画片 | 微电影</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -2125,25 +2207,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H29" t="n">
+        <v>436</v>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>6</v>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 欧美剧 | 韩剧 | 日剧 | 港剧 | 台剧 | 泰剧 | 纪录片 | 海外剧</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置</t>
         </is>
@@ -2185,25 +2270,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30" t="n">
+        <v>1074</v>
+      </c>
+      <c r="I30" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>1</v>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>电影片 | 连续剧 | 综艺片 | 动漫片 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 韩国剧 | 欧美剧 | 记录片 | 台湾剧 | 日本剧 | 海外剧 | 泰国剧</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -2255,11 +2343,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J31" s="2" t="n">
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -2301,25 +2394,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H32" t="n">
+        <v>604</v>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J32" t="n">
+      <c r="K32" t="n">
         <v>6</v>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 大陆剧 | 欧美剧 | 韩剧 | 日剧 | 港澳剧 | 台湾剧 | 泰剧 | 纪录片 | 其他剧</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库3,cmliu配置</t>
         </is>
@@ -2361,25 +2457,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H33" t="n">
+        <v>857</v>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
         <v>1</v>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 台湾剧 | 韩国剧 | 欧美剧 | 香港剧 | 泰国剧 | 日本剧 | 福利 | 记录片</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库3,cmliu配置</t>
         </is>
@@ -2421,25 +2520,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H34" t="n">
+        <v>302</v>
+      </c>
+      <c r="I34" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J34" t="n">
+      <c r="K34" t="n">
         <v>6</v>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 欧美剧 | 韩剧 | 日剧 | 港剧 | 台剧 | 泰剧 | 纪录片 | 海外剧</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置,sp696</t>
         </is>
@@ -2481,25 +2583,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H35" t="n">
+        <v>367</v>
+      </c>
+      <c r="I35" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J35" t="n">
+      <c r="K35" t="n">
         <v>1</v>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 港澳剧 | 日剧 | 欧美剧 | 台湾剧 | 泰剧 | 韩剧 | 纪录片 | 动漫电影</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -2541,25 +2646,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H36" t="n">
+        <v>6352</v>
+      </c>
+      <c r="I36" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J36" t="n">
+      <c r="K36" t="n">
         <v>1</v>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>电影 | 连续剧 | 综艺片 | 动漫 | 纪录片 | 动作片 | 爱情片 | 喜剧片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 欧美剧 | 韩剧 | 动漫电影 | 泰国剧 | 日本剧 | 台湾剧</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,sp696</t>
         </is>
@@ -2601,25 +2709,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H37" t="n">
+        <v>894</v>
+      </c>
+      <c r="I37" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J37" t="n">
+      <c r="K37" t="n">
         <v>1</v>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>电视剧 | 电影 | 欧美剧 | 香港剧 | 韩剧 | 日剧 | 马泰剧 | 伦理片 | 动作片 | 爱情片 | 喜剧片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 记录片 | 动漫 | 内地剧 | 动画片 | 中国动漫</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置,sp696</t>
         </is>
@@ -2671,11 +2782,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J38" t="n">
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
         <v>0</v>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -2717,25 +2832,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H39" t="n">
+        <v>658</v>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J39" t="n">
+      <c r="K39" t="n">
         <v>1</v>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>电影 | 连续剧 | 综艺片 | 动漫 | 纪录片 | 动作片 | 爱情片 | 喜剧片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 欧美剧 | 韩剧 | 动漫电影 | 泰国剧 | 日本剧 | 台湾剧</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,cmliu配置</t>
         </is>
@@ -2777,25 +2895,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H40" t="n">
+        <v>452</v>
+      </c>
+      <c r="I40" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J40" t="n">
+      <c r="K40" t="n">
         <v>1</v>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>电视剧 | 电影 | 欧美剧 | 香港剧 | 韩剧 | 日剧 | 马泰剧 | 伦理片 | 动作片 | 爱情片 | 喜剧片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 记录片 | 动漫 | 内地剧 | 动画片 | 中国动漫</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -2837,25 +2958,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H41" t="n">
+        <v>708</v>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J41" t="n">
+      <c r="K41" t="n">
         <v>1</v>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>电影 | 电视剧 | 动漫 | 综艺 | 纪录片 | 动作片 | 爱情片 | 科幻片 | 战争片 | 剧情片 | 恐怖片 | 喜剧片 | 动漫电影 | 大陆剧 | 台湾剧 | 韩剧 | 美剧 | 港澳剧 | 日剧 | 泰剧</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -2897,25 +3021,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H42" t="n">
+        <v>525</v>
+      </c>
+      <c r="I42" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J42" t="n">
+      <c r="K42" t="n">
         <v>1</v>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>电影片 | 连续剧 | 综艺片 | 动漫片 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 韩国剧 | 欧美剧 | 记录片 | 台湾剧 | 日本剧 | 海外剧 | 泰国剧</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -2957,25 +3084,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H43" t="n">
+        <v>713</v>
+      </c>
+      <c r="I43" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J43" t="n">
+      <c r="K43" t="n">
         <v>1</v>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>电视剧 | 电影 | 欧美剧 | 香港剧 | 韩剧 | 日剧 | 马泰剧 | 伦理片 | 动作片 | 爱情片 | 喜剧片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 记录片 | 动漫 | 内地剧 | 动画片 | 中国动漫</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -3017,25 +3147,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H44" t="n">
+        <v>439</v>
+      </c>
+      <c r="I44" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J44" t="n">
+      <c r="K44" t="n">
         <v>1</v>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>电视剧 | 电影 | 欧美剧 | 香港剧 | 韩剧 | 日剧 | 马泰剧 | 伦理片 | 动作片 | 爱情片 | 喜剧片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 记录片 | 动漫 | 内地剧 | 动画片 | 中国动漫</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置</t>
         </is>
@@ -3077,25 +3210,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H45" t="n">
+        <v>435</v>
+      </c>
+      <c r="I45" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J45" t="n">
+      <c r="K45" t="n">
         <v>6</v>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 欧美剧 | 韩剧 | 日剧 | 港剧 | 台剧 | 泰剧 | 纪录片 | 海外剧</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置</t>
         </is>
@@ -3137,25 +3273,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H46" t="n">
+        <v>3344</v>
+      </c>
+      <c r="I46" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J46" t="n">
+      <c r="K46" t="n">
         <v>1</v>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>电影片 | 连续剧 | 综艺片 | 动漫片 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 韩国剧 | 欧美剧 | 记录片 | 台湾剧 | 日本剧 | 海外剧 | 泰国剧</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -3207,11 +3346,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J47" t="n">
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
         <v>0</v>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -3263,11 +3406,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J48" t="n">
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
         <v>0</v>
       </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3</t>
         </is>
@@ -3309,25 +3456,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H49" t="n">
+        <v>748</v>
+      </c>
+      <c r="I49" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J49" t="n">
+      <c r="K49" t="n">
         <v>1</v>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>国产动漫 | 日韩动漫 | 欧美动漫 | 港台动漫 | 动漫电影 | 里番动漫 | 电影 | 连续剧 | 综艺 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 惊悚片 | 家庭片 | 古装片 | 历史片</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置,sp696</t>
         </is>
@@ -3369,25 +3519,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H50" t="n">
+        <v>816</v>
+      </c>
+      <c r="I50" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J50" t="n">
+      <c r="K50" t="n">
         <v>1</v>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>国产动漫 | 日韩动漫 | 欧美动漫 | 港台动漫 | 动漫电影 | 里番动漫 | 电影 | 连续剧 | 综艺 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 惊悚片 | 家庭片 | 古装片 | 历史片</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -3429,21 +3582,23 @@
           <t>存活/非标准</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H51" t="n">
+        <v>169</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J51" t="n">
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
         <v>0</v>
       </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版</t>
         </is>
@@ -3485,21 +3640,23 @@
           <t>存活/非标准</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H52" t="n">
+        <v>179</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J52" t="n">
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
         <v>0</v>
       </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -3541,25 +3698,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H53" s="2" t="n">
+        <v>643</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
         <is>
           <t>18禁</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="n">
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="K53" s="2" t="inlineStr">
+      <c r="L53" s="2" t="inlineStr">
         <is>
           <t>麻豆视频 | 91制片厂 | 天美传媒 | 蜜桃传媒 | 皇家华人 | 星空传媒 | 精东影业 | 海角社区 | 成人头条 | 乌鸦传媒 | 兔子先生 | 杏吧原创 | 玩偶姐姐 | mini传媒 | 大象传媒 | 91视频 | PsychoPorn | 糖心Vlog | 萝莉社 | 性视界</t>
         </is>
       </c>
-      <c r="L53" s="2" t="inlineStr">
+      <c r="M53" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -3607,11 +3767,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J54" s="2" t="n">
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K54" s="2" t="inlineStr"/>
-      <c r="L54" s="2" t="inlineStr">
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -3653,25 +3818,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H55" s="2" t="n">
+        <v>379</v>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
         <is>
           <t>18禁/动漫</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="n">
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="K55" s="2" t="inlineStr">
+      <c r="L55" s="2" t="inlineStr">
         <is>
           <t>中文字幕 | 日本有码 | 日本无码 | AV解说 | cosplay | 都市激情 | 校园情事 | 人妻纵情 | 风俗伦理 | 另类小说 | 武侠古典 | 长篇连载 | 黑丝诱惑 | SWAG | 自拍偷拍 | 激情动漫 | 网红主播 | 探花系列 | 三级伦理 | VR视角</t>
         </is>
       </c>
-      <c r="L55" s="2" t="inlineStr">
+      <c r="M55" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -3713,25 +3881,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H56" s="2" t="n">
+        <v>780</v>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
         <is>
           <t>18禁/动漫</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="n">
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="K56" s="2" t="inlineStr">
+      <c r="L56" s="2" t="inlineStr">
         <is>
           <t>中文传媒 | 国产 | 欧美AV | 日本AV | 传媒-麻豆传媒 | 传媒-精东影业 | 传媒-蜜桃传媒 | 传媒-果冻传媒 | 传媒-星空无限传媒 | 传媒-SA国际传媒 | 传媒-性视界传媒 | 国产-自拍 | 国产-偷拍 | 国产-探花 | 国产-主播 | 传媒-天美传媒 | 欧美-高清无码 | 欧美-高清有码 | 日本-中文字幕 | 日本-无码流出</t>
         </is>
       </c>
-      <c r="L56" s="2" t="inlineStr">
+      <c r="M56" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -3773,25 +3944,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H57" s="2" t="n">
+        <v>842</v>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
         <is>
           <t>18禁/动漫</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="n">
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="K57" s="2" t="inlineStr">
+      <c r="L57" s="2" t="inlineStr">
         <is>
           <t>亚洲情色 | 国产主播 | 国产自拍 | 无码专区 | 欧美性爱 | 熟女人妻 | 强奸乱伦 | 巨乳美乳 | 中文字幕 | 制服诱惑 | 女同性恋 | 卡通动画 | 视频伦理 | 少女萝莉 | 重口色情 | 人兽性交 | 福利姬</t>
         </is>
       </c>
-      <c r="L57" s="2" t="inlineStr">
+      <c r="M57" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -3833,25 +4007,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H58" s="2" t="n">
+        <v>803</v>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
         <is>
           <t>18禁/动漫</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="n">
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="K58" s="2" t="inlineStr">
+      <c r="L58" s="2" t="inlineStr">
         <is>
           <t>国产视频 | 中文字幕 | 国产传媒 | 日本有码 | 日本无码 | 欧美无码 | 强奸乱伦 | 制服诱惑 | 国产主播 | 激情动漫 | 明星换脸 | 抖阴视频 | 女优明星 | 视频一区 | 视频二区 | 网曝黑料 | 视频三区 | 伦理三级 | AV解说 | SM调教</t>
         </is>
       </c>
-      <c r="L58" s="2" t="inlineStr">
+      <c r="M58" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -3893,25 +4070,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H59" s="2" t="n">
+        <v>1602</v>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
         <is>
           <t>18禁/动漫</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="n">
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="K59" s="2" t="inlineStr">
+      <c r="L59" s="2" t="inlineStr">
         <is>
           <t>精品国产 | 精品日韩 | 精品综合 | 精品小说 | 精品美图 | 国产自拍 | 主播诱惑 | 探花约炮 | 偷拍偷窥 | 网曝吃瓜 | 抖阴短片 | 传媒剧情 | 日韩主播 | 日韩无码 | 中文字幕 | AV解说 | 换脸明星 | 强奸乱伦 | 女优明星 | 欧美激情</t>
         </is>
       </c>
-      <c r="L59" s="2" t="inlineStr">
+      <c r="M59" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -3953,25 +4133,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H60" s="2" t="n">
+        <v>699</v>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
         <is>
           <t>18禁/动漫</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="n">
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="K60" s="2" t="inlineStr">
+      <c r="L60" s="2" t="inlineStr">
         <is>
           <t>精品推荐 | 国产色情 | 主播直播 | 亚洲无码 | 亚洲有码 | 中文字幕 | 巨乳美乳 | 人妻熟女 | 强奸乱伦 | 欧美精品 | 萝莉少女 | 伦理三级 | 成人动漫 | 自拍偷拍 | 制服丝袜 | 口交颜射 | 日本精品 | Cosplay | 素人自拍 | 台湾辣妹</t>
         </is>
       </c>
-      <c r="L60" s="2" t="inlineStr">
+      <c r="M60" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置</t>
         </is>
@@ -4013,21 +4196,24 @@
           <t>存活/非标准</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H61" s="2" t="n">
+        <v>948</v>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="n">
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K61" s="2" t="inlineStr"/>
-      <c r="L61" s="2" t="inlineStr">
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -4069,25 +4255,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H62" s="2" t="n">
+        <v>486</v>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
         <is>
           <t>18禁/动漫</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="n">
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="K62" s="2" t="inlineStr">
+      <c r="L62" s="2" t="inlineStr">
         <is>
           <t>精品推荐 | 国产精品 | 主播秀色 | 日本有码 | 日本无码 | 中文字幕 | 童颜巨乳 | 性感人妻 | 强奸乱伦 | 欧美情色 | 三级伦理 | 卡通动漫 | 丝袜OL | 自拍偷拍 | 日本片商 | 剧情介绍 | 网曝系列 | 麻豆传媒 | 明星换脸 | 国产乱伦</t>
         </is>
       </c>
-      <c r="L62" s="2" t="inlineStr">
+      <c r="M62" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -4129,25 +4318,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H63" s="2" t="n">
+        <v>758</v>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
         <is>
           <t>18禁/动漫</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="n">
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="K63" s="2" t="inlineStr">
+      <c r="L63" s="2" t="inlineStr">
         <is>
           <t>制服丝袜 | 群交淫乱 | 无码专区 | 偷拍自拍 | 卡通动漫 | 中文字幕 | 欧美性爱 | 巨乳美乳 | 国产裸聊 | 国产自拍 | 国产盗摄 | 伦理三级 | 女同性恋 | 少女萝莉 | 人妖系列 | 虚拟VR | 亚州图片 | 欧美图片 | 美腿丝袜 | 网友自拍</t>
         </is>
       </c>
-      <c r="L63" s="2" t="inlineStr">
+      <c r="M63" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -4189,21 +4381,24 @@
           <t>存活/非标准</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H64" s="2" t="n">
+        <v>854</v>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="n">
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K64" s="2" t="inlineStr"/>
-      <c r="L64" s="2" t="inlineStr">
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -4245,25 +4440,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H65" s="2" t="n">
+        <v>581</v>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="n">
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K65" s="2" t="inlineStr">
+      <c r="L65" s="2" t="inlineStr">
         <is>
           <t>国产 | 日本 | 欧美 | 动漫 | 偷拍自拍 | 国产大制作 | 乱伦毁三观 | 嫖妓全过程 | 淫乱学生妹 | 黑料不打烊 | 监控摄像头 | 主播网红 | 高清无码 | 中文字幕 | 成人综艺 | 媚黑母狗 | 为国争光 | 少女破处 | 人兽典藏 | 中文剧情</t>
         </is>
       </c>
-      <c r="L65" s="2" t="inlineStr">
+      <c r="M65" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -4305,21 +4503,24 @@
           <t>存活/非标准</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H66" s="2" t="n">
+        <v>4097</v>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="n">
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K66" s="2" t="inlineStr"/>
-      <c r="L66" s="2" t="inlineStr">
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -4361,25 +4562,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H67" s="2" t="n">
+        <v>626</v>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
         <is>
           <t>18禁/动漫</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J67" s="2" t="n">
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="K67" s="2" t="inlineStr">
+      <c r="L67" s="2" t="inlineStr">
         <is>
           <t>精品推荐 | 国产精品 | 主播秀色 | 日本有码 | 日本无码 | 中文字幕 | 童颜巨乳 | 性感人妻 | 强奸乱伦 | 欧美情色 | 三级伦理 | 卡通动漫 | 丝袜OL | 自拍偷拍 | 日本片商 | 剧情介绍 | 网曝系列 | 麻豆传媒 | 明星换脸 | 国产乱伦</t>
         </is>
       </c>
-      <c r="L67" s="2" t="inlineStr">
+      <c r="M67" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -4431,11 +4635,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J68" s="2" t="n">
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K68" s="2" t="inlineStr"/>
-      <c r="L68" s="2" t="inlineStr">
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -4487,11 +4696,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J69" s="2" t="n">
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K69" s="2" t="inlineStr"/>
-      <c r="L69" s="2" t="inlineStr">
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -4533,25 +4747,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H70" s="2" t="n">
+        <v>753</v>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
         <is>
           <t>动漫</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J70" s="2" t="n">
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="K70" s="2" t="inlineStr">
+      <c r="L70" s="2" t="inlineStr">
         <is>
           <t>国产自拍 | 欧美极品 | 日韩无码 | AV明星 | 公告 | 头条 | 中文字幕 | 动漫精品 | 极骚萝莉 | 人妖视频 | 重咸口味 | 三级自慰 | 强奸乱伦 | 独家擂台格斗 | 辣椒GIGA | HEYZO | 独家DMM | HEY诱惑 | 童颜巨乳 | 高潮喷吹</t>
         </is>
       </c>
-      <c r="L70" s="2" t="inlineStr">
+      <c r="M70" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -4593,21 +4810,24 @@
           <t>存活/非标准</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H71" s="2" t="n">
+        <v>773</v>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J71" s="2" t="n">
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K71" s="2" t="inlineStr"/>
-      <c r="L71" s="2" t="inlineStr">
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -4649,25 +4869,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H72" s="2" t="n">
+        <v>3585</v>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
         <is>
           <t>18禁/动漫</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J72" s="2" t="n">
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="K72" s="2" t="inlineStr">
+      <c r="L72" s="2" t="inlineStr">
         <is>
           <t>国产情色 | 日本无码 | AV明星 | 中文字幕 | 网红主播 | 成人动漫 | 欧美情色 | 国模私拍 | 长腿丝袜 | 邻家人妻 | 韩国伦理 | 香港伦理 | 精品推荐 | 原纱央莉 | 柚木TINA | 大桥未久 | AV明星1 | 仁科百华 | 天海翼 | 小川阿佐美</t>
         </is>
       </c>
-      <c r="L72" s="2" t="inlineStr">
+      <c r="M72" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -4709,21 +4932,24 @@
           <t>存活/非标准</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H73" s="2" t="n">
+        <v>1774</v>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J73" s="2" t="n">
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K73" s="2" t="inlineStr"/>
-      <c r="L73" s="2" t="inlineStr">
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -4765,25 +4991,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H74" t="n">
+        <v>3547</v>
+      </c>
+      <c r="I74" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J74" t="n">
+      <c r="K74" t="n">
         <v>1</v>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t>电影片 | 连续剧 | 综艺片 | 动漫片 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 韩国剧 | 欧美剧 | 记录片 | 台湾剧 | 日本剧 | 海外剧 | 泰国剧</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -4825,25 +5054,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="H75" t="n">
+        <v>416</v>
+      </c>
+      <c r="I75" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J75" t="n">
+      <c r="K75" t="n">
         <v>1</v>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>电视剧 | 电影 | 欧美剧 | 香港剧 | 韩剧 | 日剧 | 马泰剧 | 伦理片 | 动作片 | 爱情片 | 喜剧片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 记录片 | 动漫 | 内地剧 | 动画片 | 中国动漫</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -4891,11 +5123,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J76" s="2" t="n">
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K76" s="2" t="inlineStr"/>
-      <c r="L76" s="2" t="inlineStr">
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -4933,25 +5170,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H77" s="2" t="n">
+        <v>712</v>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
         <is>
           <t>18禁/动漫</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="n">
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="K77" s="2" t="inlineStr">
+      <c r="L77" s="2" t="inlineStr">
         <is>
           <t>视频一区 | 日韩无码 | 国产主播 | 视频三区 | 日韩精品 | 欧美劲爆 | 成人动漫 | 自拍偷拍 | 伦理影片 | 中文字幕 | 人妻系列 | 制服诱惑 | 强奸乱伦 | AV明星 | SM重味 | 视频二区 | 巨乳尤物 | 颜射系列 | 口交视频 | 自慰系列</t>
         </is>
       </c>
-      <c r="L77" s="2" t="inlineStr">
+      <c r="M77" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置</t>
         </is>
@@ -4973,7 +5213,6 @@
           <t>https://www.aiduanju.cc/</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>否</t>
@@ -4999,11 +5238,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J78" t="n">
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
         <v>0</v>
       </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -5025,7 +5268,6 @@
           <t>https://huawei8.live/api.php/provide/vod</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>否</t>
@@ -5051,11 +5293,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J79" t="n">
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
         <v>0</v>
       </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -5077,7 +5323,6 @@
           <t>https://taopianapi.com/cjapi/sda/vod</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>否</t>
@@ -5103,11 +5348,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J80" t="n">
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
         <v>0</v>
       </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -5129,7 +5378,6 @@
           <t>https://www.hongniuzy3.com/api.php/provide/vod</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>否</t>
@@ -5145,25 +5393,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="H81" t="n">
+        <v>575</v>
+      </c>
+      <c r="I81" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J81" t="n">
+      <c r="K81" t="n">
         <v>1</v>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 港澳剧 | 日剧 | 欧美剧 | 台湾剧 | 泰剧 | 韩剧 | 纪录片 | 动漫电影</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置</t>
         </is>
@@ -5205,25 +5456,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="H82" t="n">
+        <v>415</v>
+      </c>
+      <c r="I82" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J82" t="n">
+      <c r="K82" t="n">
         <v>6</v>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 欧美剧 | 韩剧 | 日剧 | 港剧 | 台剧 | 泰剧 | 纪录片 | 海外剧</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置,sp696</t>
         </is>
@@ -5245,7 +5499,6 @@
           <t>https://jyzyapi.com/provide/vod</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>否</t>
@@ -5261,25 +5514,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="H83" t="n">
+        <v>369</v>
+      </c>
+      <c r="I83" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J83" t="n">
+      <c r="K83" t="n">
         <v>1</v>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t>电视剧 | 电影 | 欧美剧 | 香港剧 | 韩剧 | 日剧 | 马泰剧 | 伦理片 | 动作片 | 爱情片 | 喜剧片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 记录片 | 动漫 | 内地剧 | 动画片 | 中国动漫</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -5301,7 +5557,6 @@
           <t>https://api.fczy888.me/api.php/provide/vod</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>否</t>
@@ -5327,11 +5582,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J84" t="n">
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
         <v>0</v>
       </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -5353,7 +5612,6 @@
           <t>https://api.jmzy.com/api.php/provide/vod</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>否</t>
@@ -5379,11 +5637,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J85" t="n">
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
         <v>0</v>
       </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -5405,7 +5667,6 @@
           <t>https://dadiapi.com/api.php/provide/vod</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>否</t>
@@ -5421,21 +5682,23 @@
           <t>存活/非标准</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H86" t="n">
+        <v>510</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J86" t="n">
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
         <v>0</v>
       </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -5473,25 +5736,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="H87" s="2" t="n">
+        <v>459</v>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J87" s="2" t="n">
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="K87" s="2" t="inlineStr">
+      <c r="L87" s="2" t="inlineStr">
         <is>
           <t>国产区 | AV区 | 欧美区 | 动漫区 | 网红主播 | 国产传媒 | 探花系列 | 人妻熟女 | 日本无码 | 美乳巨乳 | 强制侵犯 | 制服诱惑 | 绝色佳人 | 风俗泡泡浴 | 家庭乱伦 | AV解说 | 三级电影 | 少女萝莉 | SM调教 | 绝顶潮吹</t>
         </is>
       </c>
-      <c r="L87" s="2" t="inlineStr">
+      <c r="M87" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -5533,25 +5799,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="H88" s="2" t="n">
+        <v>290</v>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
         <is>
           <t>动漫</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J88" s="2" t="n">
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="K88" s="2" t="inlineStr">
+      <c r="L88" s="2" t="inlineStr">
         <is>
           <t>国产自拍 | 日韩AV | 欧美精品 | 异族风情 | 动漫专栏 | 强奸迷奸 | 丝袜制服 | 国产厂牌 | SM调教 | 乱伦 | 网曝黑料 | 主播网红 | 自拍偷拍 | 口交自慰 | 群交多P | AI换脸 | 素人特摄 | 无码高清 | 经典有码 | 中文字幕</t>
         </is>
       </c>
-      <c r="L88" s="2" t="inlineStr">
+      <c r="M88" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -5573,7 +5842,6 @@
           <t>https://caiji.kuaichezy.org/api.php/provide</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
           <t>否</t>
@@ -5589,21 +5857,23 @@
           <t>存活/非标准</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H89" t="n">
+        <v>178</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J89" t="n">
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
         <v>0</v>
       </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -5641,21 +5911,24 @@
           <t>存活/非标准</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H90" s="2" t="n">
+        <v>756</v>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J90" s="2" t="n">
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K90" s="2" t="inlineStr"/>
-      <c r="L90" s="2" t="inlineStr">
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -5677,7 +5950,6 @@
           <t>https://api.yzzy-api.com/inc/ldg_api_all.php/provide/vod</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>否</t>
@@ -5693,21 +5965,23 @@
           <t>存活/非标准</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H91" t="n">
+        <v>383</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J91" t="n">
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
         <v>0</v>
       </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -5749,25 +6023,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="H92" t="n">
+        <v>1811</v>
+      </c>
+      <c r="I92" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J92" t="n">
+      <c r="K92" t="n">
         <v>1</v>
       </c>
-      <c r="K92" t="inlineStr">
+      <c r="L92" t="inlineStr">
         <is>
           <t>国产动漫 | 日韩动漫 | 欧美动漫 | 港台动漫 | 动漫电影 | 里番动漫 | 电影 | 连续剧 | 综艺 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 惊悚片 | 家庭片 | 古装片 | 历史片</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置,sp696</t>
         </is>
@@ -5809,21 +6086,24 @@
           <t>存活/非标准</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H93" s="2" t="n">
+        <v>519</v>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J93" s="2" t="n">
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K93" s="2" t="inlineStr"/>
-      <c r="L93" s="2" t="inlineStr">
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -5845,7 +6125,6 @@
           <t>https://www.qiqidys.com/api.php/provide/vod/</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
           <t>否</t>
@@ -5871,11 +6150,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J94" t="n">
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
         <v>0</v>
       </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr">
+      <c r="M94" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -5917,25 +6200,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="H95" t="n">
+        <v>1303</v>
+      </c>
+      <c r="I95" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J95" t="n">
+      <c r="K95" t="n">
         <v>1</v>
       </c>
-      <c r="K95" t="inlineStr">
+      <c r="L95" t="inlineStr">
         <is>
           <t>电影片 | 连续剧 | 综艺片 | 动漫片 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 韩国剧 | 欧美剧 | 记录片 | 台湾剧 | 日本剧 | 海外剧 | 泰国剧</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
+      <c r="M95" t="inlineStr">
         <is>
           <t>仓库2-基础版</t>
         </is>
@@ -5977,25 +6263,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="H96" t="n">
+        <v>379</v>
+      </c>
+      <c r="I96" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J96" t="n">
+      <c r="K96" t="n">
         <v>6</v>
       </c>
-      <c r="K96" t="inlineStr">
+      <c r="L96" t="inlineStr">
         <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 欧美剧 | 韩剧 | 日剧 | 港剧 | 台剧 | 泰剧 | 纪录片 | 海外剧</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr">
+      <c r="M96" t="inlineStr">
         <is>
           <t>cmliu配置,sp696</t>
         </is>
@@ -6037,25 +6326,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="H97" t="n">
+        <v>583</v>
+      </c>
+      <c r="I97" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
+      <c r="J97" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J97" t="n">
+      <c r="K97" t="n">
         <v>1</v>
       </c>
-      <c r="K97" t="inlineStr">
+      <c r="L97" t="inlineStr">
         <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 伦理片 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 韩国剧 | 欧美剧 | 体育 | NBA | 惊悚片 | 家庭篇</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr">
+      <c r="M97" t="inlineStr">
         <is>
           <t>cmliu配置,sp696</t>
         </is>
@@ -6097,25 +6389,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="H98" t="n">
+        <v>589</v>
+      </c>
+      <c r="I98" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
+      <c r="J98" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J98" t="n">
+      <c r="K98" t="n">
         <v>1</v>
       </c>
-      <c r="K98" t="inlineStr">
+      <c r="L98" t="inlineStr">
         <is>
           <t>电影片 | 连续剧 | 综艺片 | 动漫片 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 韩国剧 | 欧美剧 | 记录片 | 台湾剧 | 日本剧 | 海外剧 | 泰国剧</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
+      <c r="M98" t="inlineStr">
         <is>
           <t>cmliu配置,sp696</t>
         </is>
@@ -6157,25 +6452,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="H99" t="n">
+        <v>756</v>
+      </c>
+      <c r="I99" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
+      <c r="J99" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J99" t="n">
+      <c r="K99" t="n">
         <v>1</v>
       </c>
-      <c r="K99" t="inlineStr">
+      <c r="L99" t="inlineStr">
         <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 伦理片 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 韩国剧 | 欧美剧 | 体育 | NBA | 惊悚片 | 家庭篇</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
+      <c r="M99" t="inlineStr">
         <is>
           <t>cmliu配置,sp696</t>
         </is>
@@ -6217,25 +6515,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="H100" t="n">
+        <v>617</v>
+      </c>
+      <c r="I100" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J100" t="n">
+      <c r="K100" t="n">
         <v>1</v>
       </c>
-      <c r="K100" t="inlineStr">
+      <c r="L100" t="inlineStr">
         <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 台湾剧 | 韩国剧 | 欧美剧 | 香港剧 | 泰国剧 | 日本剧 | 福利 | 记录片</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
+      <c r="M100" t="inlineStr">
         <is>
           <t>cmliu配置,sp696</t>
         </is>
@@ -6277,25 +6578,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="H101" t="n">
+        <v>1068</v>
+      </c>
+      <c r="I101" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
+      <c r="J101" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J101" t="n">
+      <c r="K101" t="n">
         <v>1</v>
       </c>
-      <c r="K101" t="inlineStr">
+      <c r="L101" t="inlineStr">
         <is>
           <t>电影 | 连续剧 | 综艺片 | 动漫 | 纪录片 | 动作片 | 爱情片 | 喜剧片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 欧美剧 | 韩剧 | 动漫电影 | 泰国剧 | 日本剧 | 台湾剧</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr">
+      <c r="M101" t="inlineStr">
         <is>
           <t>cmliu配置,sp696</t>
         </is>
@@ -6337,25 +6641,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="H102" t="n">
+        <v>254</v>
+      </c>
+      <c r="I102" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
+      <c r="J102" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J102" t="n">
+      <c r="K102" t="n">
         <v>1</v>
       </c>
-      <c r="K102" t="inlineStr">
+      <c r="L102" t="inlineStr">
         <is>
           <t>电视剧 | 电影 | 欧美剧 | 香港剧 | 韩剧 | 日剧 | 马泰剧 | 伦理片 | 动作片 | 爱情片 | 喜剧片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 记录片 | 动漫 | 内地剧 | 动画片 | 中国动漫</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr">
+      <c r="M102" t="inlineStr">
         <is>
           <t>cmliu配置</t>
         </is>
@@ -6397,25 +6704,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="H103" t="n">
+        <v>2810</v>
+      </c>
+      <c r="I103" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
+      <c r="J103" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J103" t="n">
+      <c r="K103" t="n">
         <v>8</v>
       </c>
-      <c r="K103" t="inlineStr">
+      <c r="L103" t="inlineStr">
         <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 福利视频 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 犯罪片 | 战争片 | 国产剧 | 港台剧 | 日韩剧 | 欧美剧 | 三级伦理 | 网红主播 | 动画电影 | 剧情片</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr">
+      <c r="M103" t="inlineStr">
         <is>
           <t>cmliu配置,sp696</t>
         </is>
@@ -6457,25 +6767,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
+      <c r="H104" t="n">
+        <v>2299</v>
+      </c>
+      <c r="I104" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
+      <c r="J104" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J104" t="n">
+      <c r="K104" t="n">
         <v>1</v>
       </c>
-      <c r="K104" t="inlineStr">
+      <c r="L104" t="inlineStr">
         <is>
           <t>电影片 | 连续剧 | 综艺片 | 动漫片 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 韩国剧 | 欧美剧 | 记录片 | 台湾剧 | 日本剧 | 海外剧 | 泰国剧</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr">
+      <c r="M104" t="inlineStr">
         <is>
           <t>cmliu配置</t>
         </is>
@@ -6517,25 +6830,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="H105" t="n">
+        <v>505</v>
+      </c>
+      <c r="I105" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
+      <c r="J105" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J105" t="n">
+      <c r="K105" t="n">
         <v>6</v>
       </c>
-      <c r="K105" t="inlineStr">
+      <c r="L105" t="inlineStr">
         <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 大陆剧 | 欧美剧 | 韩剧 | 日剧 | 港澳剧 | 台湾剧 | 泰剧 | 纪录片 | 其他剧</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr">
+      <c r="M105" t="inlineStr">
         <is>
           <t>cmliu配置,sp696</t>
         </is>
@@ -6577,25 +6893,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
+      <c r="H106" t="n">
+        <v>547</v>
+      </c>
+      <c r="I106" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
+      <c r="J106" t="inlineStr">
         <is>
           <t>是(少量)</t>
         </is>
       </c>
-      <c r="J106" t="n">
+      <c r="K106" t="n">
         <v>1</v>
       </c>
-      <c r="K106" t="inlineStr">
+      <c r="L106" t="inlineStr">
         <is>
           <t>电视剧 | 电影 | 欧美剧 | 香港剧 | 韩剧 | 日剧 | 马泰剧 | 伦理片 | 动作片 | 爱情片 | 喜剧片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 记录片 | 动漫 | 内地剧 | 动画片 | 中国动漫</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr">
+      <c r="M106" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -6637,25 +6956,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="H107" s="2" t="n">
+        <v>407</v>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I107" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J107" s="2" t="n">
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="K107" s="2" t="inlineStr">
+      <c r="L107" s="2" t="inlineStr">
         <is>
           <t>国产区 | AV区 | 欧美区 | 动漫区 | 网红主播 | 国产传媒 | 探花系列 | 人妻熟女 | 日本无码 | 美乳巨乳 | 强制侵犯 | 制服诱惑 | 绝色佳人 | 风俗泡泡浴 | 家庭乱伦 | AV解说 | 三级电影 | 少女萝莉 | SM调教 | 绝顶潮吹</t>
         </is>
       </c>
-      <c r="L107" s="2" t="inlineStr">
+      <c r="M107" s="2" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -6697,25 +7019,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="H108" s="2" t="n">
+        <v>707</v>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
         <is>
           <t>动漫</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J108" s="2" t="n">
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="K108" s="2" t="inlineStr">
+      <c r="L108" s="2" t="inlineStr">
         <is>
           <t>视频一区 | 视频二区 | 视频三区 | 视频四区 | 精品推荐 | 国产主播 | 国产乱伦 | 自拍偷拍 | 制服丝袜 | 网曝事件 | 传媒探花 | 清纯学生 | A V 解说 | 淫妻作乐 | 港台辣妹 | 足浴撩妹 | 反差母狗 | A I 换脸 | V R 视角 | 重口性癖</t>
         </is>
       </c>
-      <c r="L108" s="2" t="inlineStr">
+      <c r="M108" s="2" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -6757,25 +7082,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="H109" s="2" t="n">
+        <v>805</v>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
         <is>
           <t>18禁/动漫</t>
         </is>
       </c>
-      <c r="I109" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J109" s="2" t="n">
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="K109" s="2" t="inlineStr">
+      <c r="L109" s="2" t="inlineStr">
         <is>
           <t>精品推荐 | 国产色情 | 主播直播 | 亚洲无码 | 亚洲有码 | 中文字幕 | 巨乳美乳 | 人妻熟女 | 强奸乱伦 | 欧美精品 | 萝莉少女 | 伦理三级 | 成人动漫 | 自拍偷拍 | 制服丝袜 | 口交颜射 | 日本精品 | Cosplay | 素人自拍 | 台湾辣妹</t>
         </is>
       </c>
-      <c r="L109" s="2" t="inlineStr">
+      <c r="M109" s="2" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -6817,25 +7145,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="H110" s="2" t="n">
+        <v>364</v>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
         <is>
           <t>18禁/动漫</t>
         </is>
       </c>
-      <c r="I110" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J110" s="2" t="n">
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="K110" s="2" t="inlineStr">
+      <c r="L110" s="2" t="inlineStr">
         <is>
           <t>采集教程 | 国产视频 | 国产传媒 | 国产探花 | 极品学生 | 野战户外 | 网曝黑料 | 日本有码 | 主播大秀 | 校园春色 | SM虐待 | 巨乳系列 | 偷拍自拍 | 强奸乱伦 | 制服诱惑 | 欧美精品 | 三级伦理 | AV解说 | 成人动漫 | 日本无码</t>
         </is>
       </c>
-      <c r="L110" s="2" t="inlineStr">
+      <c r="M110" s="2" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -6877,25 +7208,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="H111" s="2" t="n">
+        <v>542</v>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
         <is>
           <t>18禁/动漫</t>
         </is>
       </c>
-      <c r="I111" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J111" s="2" t="n">
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="K111" s="2" t="inlineStr">
+      <c r="L111" s="2" t="inlineStr">
         <is>
           <t>国产专区 | 国产厂商 | 主播视讯 | 日本无码 | 日本有码 | 中文字幕 | 中字无码 | 中字有码 | 水果派解说 | 麻豆传媒 | 91制片厂 | 蜜桃影像传媒 | 天美传媒 | 精东影业 | 星空无限传媒 | 台湾swag | 其他传媒 | 三级伦理 | 美女写真 | 卡通动漫</t>
         </is>
       </c>
-      <c r="L111" s="2" t="inlineStr">
+      <c r="M111" s="2" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -6937,25 +7271,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="H112" s="2" t="n">
+        <v>808</v>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
         <is>
           <t>18禁/动漫</t>
         </is>
       </c>
-      <c r="I112" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J112" s="2" t="n">
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="K112" s="2" t="inlineStr">
+      <c r="L112" s="2" t="inlineStr">
         <is>
           <t>中文字幕 | 日本有码 | 日本无码 | AV解说 | cosplay | 都市激情 | 校园情事 | 人妻纵情 | 风俗伦理 | 另类小说 | 武侠古典 | 长篇连载 | 黑丝诱惑 | SWAG | 自拍偷拍 | 激情动漫 | 网红主播 | 探花系列 | 三级伦理 | VR视角</t>
         </is>
       </c>
-      <c r="L112" s="2" t="inlineStr">
+      <c r="M112" s="2" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -6997,25 +7334,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="H113" s="2" t="n">
+        <v>496</v>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
         <is>
           <t>短剧</t>
         </is>
       </c>
-      <c r="I113" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J113" s="2" t="n">
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K113" s="2" t="inlineStr">
+      <c r="L113" s="2" t="inlineStr">
         <is>
           <t>视频1区 | 国产精品 | 华语AV | 黑料吃瓜 | 欧美 | 禁漫 | 视频2区 | 学生 | 乱伦 | 探花 | 日本无码 | 日本有码 | 主播网红 | 日本素人 | AI短剧</t>
         </is>
       </c>
-      <c r="L113" s="2" t="inlineStr">
+      <c r="M113" s="2" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -7057,25 +7397,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="H114" s="2" t="n">
+        <v>605</v>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
         <is>
           <t>18禁/动漫</t>
         </is>
       </c>
-      <c r="I114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J114" s="2" t="n">
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="K114" s="2" t="inlineStr">
+      <c r="L114" s="2" t="inlineStr">
         <is>
           <t>中文传媒 | 国产 | 欧美AV | 日本AV | 传媒-麻豆传媒 | 传媒-精东影业 | 传媒-蜜桃传媒 | 传媒-果冻传媒 | 传媒-星空无限传媒 | 传媒-SA国际传媒 | 传媒-性视界传媒 | 国产-自拍 | 国产-偷拍 | 国产-探花 | 国产-主播 | 传媒-天美传媒 | 欧美-高清无码 | 欧美-高清有码 | 日本-中文字幕 | 日本-无码流出</t>
         </is>
       </c>
-      <c r="L114" s="2" t="inlineStr">
+      <c r="M114" s="2" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -7127,11 +7470,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J115" s="2" t="n">
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K115" s="2" t="inlineStr"/>
-      <c r="L115" s="2" t="inlineStr">
+      <c r="L115" s="2" t="inlineStr"/>
+      <c r="M115" s="2" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -7173,25 +7521,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="H116" s="2" t="n">
+        <v>593</v>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
         <is>
           <t>18禁/动漫</t>
         </is>
       </c>
-      <c r="I116" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J116" s="2" t="n">
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="K116" s="2" t="inlineStr">
+      <c r="L116" s="2" t="inlineStr">
         <is>
           <t>视频一区 | 日韩无码 | 国产主播 | 视频三区 | 日韩精品 | 欧美劲爆 | 成人动漫 | 自拍偷拍 | 伦理影片 | 中文字幕 | 人妻系列 | 制服诱惑 | 强奸乱伦 | AV明星 | SM重味 | 视频二区 | 巨乳尤物 | 颜射系列 | 口交视频 | 自慰系列</t>
         </is>
       </c>
-      <c r="L116" s="2" t="inlineStr">
+      <c r="M116" s="2" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -7233,21 +7584,24 @@
           <t>存活/非标准</t>
         </is>
       </c>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="H117" s="2" t="n">
+        <v>652</v>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="I117" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J117" s="2" t="n">
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K117" s="2" t="inlineStr"/>
-      <c r="L117" s="2" t="inlineStr">
+      <c r="L117" s="2" t="inlineStr"/>
+      <c r="M117" s="2" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -7289,25 +7643,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="H118" s="2" t="n">
+        <v>758</v>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
         <is>
           <t>18禁/动漫</t>
         </is>
       </c>
-      <c r="I118" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J118" s="2" t="n">
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="K118" s="2" t="inlineStr">
+      <c r="L118" s="2" t="inlineStr">
         <is>
           <t>国产自拍 | 日本无码 | 日本有码 | 中文字幕 | 欧美精品 | 成人动漫 | 日本素人 | 高清名优 | 三级伦理 | 网红主播 | 映画传媒 | 人妻熟女 | 口爆颜射 | 萝莉少女 | SM调教 | 美乳巨乳 | 短视频 | 制服诱惑 | 女同性爱 | AI换脸</t>
         </is>
       </c>
-      <c r="L118" s="2" t="inlineStr">
+      <c r="M118" s="2" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -7324,7 +7681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7365,25 +7722,30 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>响应ms</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>内容标签</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>含成人栏目</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>成人栏目数</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>分类名</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
@@ -7425,25 +7787,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" t="n">
+        <v>265</v>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>18禁/动漫</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
         <v>17</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>无码专区 | 麻豆传媒 | 制服诱惑 | 三级伦理 | AI换脸 | 中文字幕 | 卡通动漫 | 欧美系列 | 美女主播 | 国产自拍 | 熟女人妻 | 萝莉少女 | 女同性爱 | 多人群交 | 美乳巨乳 | 强奸乱伦 | 生活都市 | 不偷恋情 | 学生校园 | 人妻熟女</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -7495,11 +7860,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -7541,25 +7910,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" t="n">
+        <v>643</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>18禁</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
         <v>8</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>麻豆视频 | 91制片厂 | 天美传媒 | 蜜桃传媒 | 皇家华人 | 星空传媒 | 精东影业 | 海角社区 | 成人头条 | 乌鸦传媒 | 兔子先生 | 杏吧原创 | 玩偶姐姐 | mini传媒 | 大象传媒 | 91视频 | PsychoPorn | 糖心Vlog | 萝莉社 | 性视界</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -7581,7 +7953,6 @@
           <t>http://lbapiby.com/api.php/provide/vod</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>是</t>
@@ -7607,11 +7978,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -7653,25 +8028,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" t="n">
+        <v>379</v>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>18禁/动漫</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
         <v>12</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>中文字幕 | 日本有码 | 日本无码 | AV解说 | cosplay | 都市激情 | 校园情事 | 人妻纵情 | 风俗伦理 | 另类小说 | 武侠古典 | 长篇连载 | 黑丝诱惑 | SWAG | 自拍偷拍 | 激情动漫 | 网红主播 | 探花系列 | 三级伦理 | VR视角</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -7713,25 +8091,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" t="n">
+        <v>780</v>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>18禁/动漫</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
         <v>37</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>中文传媒 | 国产 | 欧美AV | 日本AV | 传媒-麻豆传媒 | 传媒-精东影业 | 传媒-蜜桃传媒 | 传媒-果冻传媒 | 传媒-星空无限传媒 | 传媒-SA国际传媒 | 传媒-性视界传媒 | 国产-自拍 | 国产-偷拍 | 国产-探花 | 国产-主播 | 传媒-天美传媒 | 欧美-高清无码 | 欧美-高清有码 | 日本-中文字幕 | 日本-无码流出</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -7773,25 +8154,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" t="n">
+        <v>842</v>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>18禁/动漫</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
         <v>11</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>亚洲情色 | 国产主播 | 国产自拍 | 无码专区 | 欧美性爱 | 熟女人妻 | 强奸乱伦 | 巨乳美乳 | 中文字幕 | 制服诱惑 | 女同性恋 | 卡通动画 | 视频伦理 | 少女萝莉 | 重口色情 | 人兽性交 | 福利姬</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -7833,25 +8217,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" t="n">
+        <v>803</v>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>18禁/动漫</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
         <v>11</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>国产视频 | 中文字幕 | 国产传媒 | 日本有码 | 日本无码 | 欧美无码 | 强奸乱伦 | 制服诱惑 | 国产主播 | 激情动漫 | 明星换脸 | 抖阴视频 | 女优明星 | 视频一区 | 视频二区 | 网曝黑料 | 视频三区 | 伦理三级 | AV解说 | SM调教</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -7893,25 +8280,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" t="n">
+        <v>1602</v>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>18禁/动漫</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
         <v>12</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>精品国产 | 精品日韩 | 精品综合 | 精品小说 | 精品美图 | 国产自拍 | 主播诱惑 | 探花约炮 | 偷拍偷窥 | 网曝吃瓜 | 抖阴短片 | 传媒剧情 | 日韩主播 | 日韩无码 | 中文字幕 | AV解说 | 换脸明星 | 强奸乱伦 | 女优明星 | 欧美激情</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -7953,25 +8343,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" t="n">
+        <v>699</v>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>18禁/动漫</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
         <v>22</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>精品推荐 | 国产色情 | 主播直播 | 亚洲无码 | 亚洲有码 | 中文字幕 | 巨乳美乳 | 人妻熟女 | 强奸乱伦 | 欧美精品 | 萝莉少女 | 伦理三级 | 成人动漫 | 自拍偷拍 | 制服丝袜 | 口交颜射 | 日本精品 | Cosplay | 素人自拍 | 台湾辣妹</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置</t>
         </is>
@@ -8013,21 +8406,23 @@
           <t>存活/非标准</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" t="n">
+        <v>948</v>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -8069,25 +8464,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" t="n">
+        <v>486</v>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>18禁/动漫</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
         <v>11</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>精品推荐 | 国产精品 | 主播秀色 | 日本有码 | 日本无码 | 中文字幕 | 童颜巨乳 | 性感人妻 | 强奸乱伦 | 欧美情色 | 三级伦理 | 卡通动漫 | 丝袜OL | 自拍偷拍 | 日本片商 | 剧情介绍 | 网曝系列 | 麻豆传媒 | 明星换脸 | 国产乱伦</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -8129,25 +8527,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" t="n">
+        <v>758</v>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>18禁/动漫</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
         <v>12</v>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>制服丝袜 | 群交淫乱 | 无码专区 | 偷拍自拍 | 卡通动漫 | 中文字幕 | 欧美性爱 | 巨乳美乳 | 国产裸聊 | 国产自拍 | 国产盗摄 | 伦理三级 | 女同性恋 | 少女萝莉 | 人妖系列 | 虚拟VR | 亚州图片 | 欧美图片 | 美腿丝袜 | 网友自拍</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -8189,21 +8590,23 @@
           <t>存活/非标准</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" t="n">
+        <v>854</v>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -8245,25 +8648,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" t="n">
+        <v>581</v>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
         <v>4</v>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>国产 | 日本 | 欧美 | 动漫 | 偷拍自拍 | 国产大制作 | 乱伦毁三观 | 嫖妓全过程 | 淫乱学生妹 | 黑料不打烊 | 监控摄像头 | 主播网红 | 高清无码 | 中文字幕 | 成人综艺 | 媚黑母狗 | 为国争光 | 少女破处 | 人兽典藏 | 中文剧情</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -8305,21 +8711,23 @@
           <t>存活/非标准</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" t="n">
+        <v>4097</v>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -8361,25 +8769,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" t="n">
+        <v>626</v>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>18禁/动漫</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
         <v>11</v>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>精品推荐 | 国产精品 | 主播秀色 | 日本有码 | 日本无码 | 中文字幕 | 童颜巨乳 | 性感人妻 | 强奸乱伦 | 欧美情色 | 三级伦理 | 卡通动漫 | 丝袜OL | 自拍偷拍 | 日本片商 | 剧情介绍 | 网曝系列 | 麻豆传媒 | 明星换脸 | 国产乱伦</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -8431,11 +8842,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
         <v>0</v>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -8487,11 +8902,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J20" t="n">
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
         <v>0</v>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -8533,25 +8952,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" t="n">
+        <v>753</v>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>动漫</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
         <v>8</v>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>国产自拍 | 欧美极品 | 日韩无码 | AV明星 | 公告 | 头条 | 中文字幕 | 动漫精品 | 极骚萝莉 | 人妖视频 | 重咸口味 | 三级自慰 | 强奸乱伦 | 独家擂台格斗 | 辣椒GIGA | HEYZO | 独家DMM | HEY诱惑 | 童颜巨乳 | 高潮喷吹</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -8593,21 +9015,23 @@
           <t>存活/非标准</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" t="n">
+        <v>773</v>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J22" t="n">
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
         <v>0</v>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -8649,25 +9073,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H23" t="n">
+        <v>3585</v>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>18禁/动漫</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J23" t="n">
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
         <v>7</v>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>国产情色 | 日本无码 | AV明星 | 中文字幕 | 网红主播 | 成人动漫 | 欧美情色 | 国模私拍 | 长腿丝袜 | 邻家人妻 | 韩国伦理 | 香港伦理 | 精品推荐 | 原纱央莉 | 柚木TINA | 大桥未久 | AV明星1 | 仁科百华 | 天海翼 | 小川阿佐美</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -8709,21 +9136,23 @@
           <t>存活/非标准</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H24" t="n">
+        <v>1774</v>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
         <v>0</v>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -8745,7 +9174,6 @@
           <t>https://gayapi.com/api.php/provide/vod</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>是</t>
@@ -8771,11 +9199,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J25" t="n">
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
         <v>0</v>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -8797,7 +9229,6 @@
           <t>https://xingba111.com/api.php/provide/vod</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>是</t>
@@ -8813,25 +9244,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26" t="n">
+        <v>712</v>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>18禁/动漫</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J26" t="n">
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
         <v>18</v>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>视频一区 | 日韩无码 | 国产主播 | 视频三区 | 日韩精品 | 欧美劲爆 | 成人动漫 | 自拍偷拍 | 伦理影片 | 中文字幕 | 人妻系列 | 制服诱惑 | 强奸乱伦 | AV明星 | SM重味 | 视频二区 | 巨乳尤物 | 颜射系列 | 口交视频 | 自慰系列</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置</t>
         </is>
@@ -8853,7 +9287,6 @@
           <t>https://hsckzy888.com/api.php/provide/vod</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>是</t>
@@ -8869,25 +9302,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H27" t="n">
+        <v>459</v>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
         <v>9</v>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>国产区 | AV区 | 欧美区 | 动漫区 | 网红主播 | 国产传媒 | 探花系列 | 人妻熟女 | 日本无码 | 美乳巨乳 | 强制侵犯 | 制服诱惑 | 绝色佳人 | 风俗泡泡浴 | 家庭乱伦 | AV解说 | 三级电影 | 少女萝莉 | SM调教 | 绝顶潮吹</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -8929,25 +9365,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H28" t="n">
+        <v>290</v>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>动漫</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
         <v>9</v>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>国产自拍 | 日韩AV | 欧美精品 | 异族风情 | 动漫专栏 | 强奸迷奸 | 丝袜制服 | 国产厂牌 | SM调教 | 乱伦 | 网曝黑料 | 主播网红 | 自拍偷拍 | 口交自慰 | 群交多P | AI换脸 | 素人特摄 | 无码高清 | 经典有码 | 中文字幕</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -8969,7 +9408,6 @@
           <t>https://apilj.com/api.php/provide</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>是</t>
@@ -8985,21 +9423,23 @@
           <t>存活/非标准</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H29" t="n">
+        <v>756</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J29" t="n">
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
         <v>0</v>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -9041,21 +9481,23 @@
           <t>存活/非标准</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H30" t="n">
+        <v>519</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J30" t="n">
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
         <v>0</v>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -9097,25 +9539,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H31" t="n">
+        <v>407</v>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>动漫/影视/短剧</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J31" t="n">
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
         <v>9</v>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>国产区 | AV区 | 欧美区 | 动漫区 | 网红主播 | 国产传媒 | 探花系列 | 人妻熟女 | 日本无码 | 美乳巨乳 | 强制侵犯 | 制服诱惑 | 绝色佳人 | 风俗泡泡浴 | 家庭乱伦 | AV解说 | 三级电影 | 少女萝莉 | SM调教 | 绝顶潮吹</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -9157,25 +9602,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H32" t="n">
+        <v>707</v>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>动漫</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J32" t="n">
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
         <v>7</v>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>视频一区 | 视频二区 | 视频三区 | 视频四区 | 精品推荐 | 国产主播 | 国产乱伦 | 自拍偷拍 | 制服丝袜 | 网曝事件 | 传媒探花 | 清纯学生 | A V 解说 | 淫妻作乐 | 港台辣妹 | 足浴撩妹 | 反差母狗 | A I 换脸 | V R 视角 | 重口性癖</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -9217,25 +9665,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H33" t="n">
+        <v>805</v>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t>18禁/动漫</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J33" t="n">
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
         <v>22</v>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>精品推荐 | 国产色情 | 主播直播 | 亚洲无码 | 亚洲有码 | 中文字幕 | 巨乳美乳 | 人妻熟女 | 强奸乱伦 | 欧美精品 | 萝莉少女 | 伦理三级 | 成人动漫 | 自拍偷拍 | 制服丝袜 | 口交颜射 | 日本精品 | Cosplay | 素人自拍 | 台湾辣妹</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -9277,25 +9728,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H34" t="n">
+        <v>364</v>
+      </c>
+      <c r="I34" t="inlineStr">
         <is>
           <t>18禁/动漫</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J34" t="n">
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
         <v>10</v>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>采集教程 | 国产视频 | 国产传媒 | 国产探花 | 极品学生 | 野战户外 | 网曝黑料 | 日本有码 | 主播大秀 | 校园春色 | SM虐待 | 巨乳系列 | 偷拍自拍 | 强奸乱伦 | 制服诱惑 | 欧美精品 | 三级伦理 | AV解说 | 成人动漫 | 日本无码</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -9337,25 +9791,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H35" t="n">
+        <v>542</v>
+      </c>
+      <c r="I35" t="inlineStr">
         <is>
           <t>18禁/动漫</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J35" t="n">
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
         <v>13</v>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>国产专区 | 国产厂商 | 主播视讯 | 日本无码 | 日本有码 | 中文字幕 | 中字无码 | 中字有码 | 水果派解说 | 麻豆传媒 | 91制片厂 | 蜜桃影像传媒 | 天美传媒 | 精东影业 | 星空无限传媒 | 台湾swag | 其他传媒 | 三级伦理 | 美女写真 | 卡通动漫</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -9397,25 +9854,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H36" t="n">
+        <v>808</v>
+      </c>
+      <c r="I36" t="inlineStr">
         <is>
           <t>18禁/动漫</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J36" t="n">
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
         <v>12</v>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>中文字幕 | 日本有码 | 日本无码 | AV解说 | cosplay | 都市激情 | 校园情事 | 人妻纵情 | 风俗伦理 | 另类小说 | 武侠古典 | 长篇连载 | 黑丝诱惑 | SWAG | 自拍偷拍 | 激情动漫 | 网红主播 | 探花系列 | 三级伦理 | VR视角</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -9457,25 +9917,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H37" t="n">
+        <v>496</v>
+      </c>
+      <c r="I37" t="inlineStr">
         <is>
           <t>短剧</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J37" t="n">
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
         <v>3</v>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>视频1区 | 国产精品 | 华语AV | 黑料吃瓜 | 欧美 | 禁漫 | 视频2区 | 学生 | 乱伦 | 探花 | 日本无码 | 日本有码 | 主播网红 | 日本素人 | AI短剧</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -9517,25 +9980,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H38" t="n">
+        <v>605</v>
+      </c>
+      <c r="I38" t="inlineStr">
         <is>
           <t>18禁/动漫</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J38" t="n">
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
         <v>37</v>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>中文传媒 | 国产 | 欧美AV | 日本AV | 传媒-麻豆传媒 | 传媒-精东影业 | 传媒-蜜桃传媒 | 传媒-果冻传媒 | 传媒-星空无限传媒 | 传媒-SA国际传媒 | 传媒-性视界传媒 | 国产-自拍 | 国产-偷拍 | 国产-探花 | 国产-主播 | 传媒-天美传媒 | 欧美-高清无码 | 欧美-高清有码 | 日本-中文字幕 | 日本-无码流出</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -9587,11 +10053,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J39" t="n">
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
         <v>0</v>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -9633,25 +10103,28 @@
           <t>存活</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H40" t="n">
+        <v>593</v>
+      </c>
+      <c r="I40" t="inlineStr">
         <is>
           <t>18禁/动漫</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J40" t="n">
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
         <v>18</v>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>视频一区 | 日韩无码 | 国产主播 | 视频三区 | 日韩精品 | 欧美劲爆 | 成人动漫 | 自拍偷拍 | 伦理影片 | 中文字幕 | 人妻系列 | 制服诱惑 | 强奸乱伦 | AV明星 | SM重味 | 视频二区 | 巨乳尤物 | 颜射系列 | 口交视频 | 自慰系列</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -9693,21 +10166,23 @@
           <t>存活/非标准</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H41" t="n">
+        <v>652</v>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J41" t="n">
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
         <v>0</v>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -9749,27 +10224,3560 @@
           <t>存活</t>
         </is>
       </c>
+      <c r="H42" t="n">
+        <v>758</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>18禁/动漫</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>12</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>国产自拍 | 日本无码 | 日本有码 | 中文字幕 | 欧美精品 | 成人动漫 | 日本素人 | 高清名优 | 三级伦理 | 网红主播 | 映画传媒 | 人妻熟女 | 口爆颜射 | 萝莉少女 | SM调教 | 美乳巨乳 | 短视频 | 制服诱惑 | 女同性爱 | AI换脸</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>sp696</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H84"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>接口</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>是否成人</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>样例片名</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>m3u8延迟ms</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>TS速度KB/s</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>评级</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Cloudflare CDN</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TV-天涯资源</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>https://tyyszy.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>改造旧冷库后我住成了大别墅</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TV-光速资源</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://api.guangsuapi.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>方舟一号第三季</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TV-无尽资源</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://api.wujinapi.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>穿越时空甩掉你</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TV-wujinapi无尽</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://api.wujinapi.cc/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>穿越时空甩掉你</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TV-CK资源</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://ckzy.me/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>如果感激的话就回报到下半身吧</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TV-丫丫点播</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>https://cj.yayazy.net/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>可以爱你吗</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TV-ikun资源</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>https://ikunzyapi.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>某暗部的少女共栖</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TV-无尽资源</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://api.wujinapi.me/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>穿越时空甩掉你</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TV-樱花资源</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://m3u8.apiyhzy.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>裴太太柔弱人设又翻车了</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TV-新浪点播</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://api.xinlangapi.com/xinlangapi.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>方舟一号第三季</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TV-1080资源</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://api.1080zyku.com/inc/api_mac10.php</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>冰雪狙击</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TV-最大点播</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>http://zuidazy.me/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>可以爱你吗</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TV-U酷资源88</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://api.ukuapi88.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>谋杀奇闻 第一季</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TV-百度云资源</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>https://api.apibdzy.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>玄苍路之初入宗门</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TV-索尼资源</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>https://suoniapi.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>改造旧冷库后我住成了大别墅</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TV-红牛资源</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>https://www.hongniuzy2.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>药屋少女的呢喃第三季</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TV-最大资源</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>https://api.zuidapi.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>可以爱你吗</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TV-牛牛点播</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>https://api.niuniuzy.me/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>可以爱你吗</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TV-暴风资源</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>https://bfzyapi.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>乌鸦俱乐部</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TV-虎牙资源</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>https://www.huyaapi.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>南瓜头怪2</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TV-电影天堂资源</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>http://caiji.dyttzyapi.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>霹雳英雄战纪之塗附世界</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TV-豪华资源</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>https://hhzyapi.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>方舟一号第三季</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TV-速博资源</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>https://subocaiji.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>方舟一号第三季</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TV-神马云</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>https://api.1080zyku.com/inc/apijson.php</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>梦想改造家第13季</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TV-金鹰资源</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>https://jyzyapi.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>方舟一号第三季</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TV-金鹰点播</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>https://jinyingzy.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>方舟一号第三季</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TV-步步高资源</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>https://api.yparse.com/api/json</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Word is Bond</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TV-豆瓣资源</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>https://dbzy.tv/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>骑士情缘</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TV-量子资源</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>https://cj.lziapi.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>霹雳英雄战纪之塗附世界</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TV-闪电资源</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>https://sdzyapi.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>可以爱你吗</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TV-U酷资源</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>https://api.ukuapi.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>谋杀奇闻 第一季</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>TV-魔都资源</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>https://www.mdzyapi.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>某暗部的少女共栖</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>TV-魔都动漫</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>https://caiji.moduapi.cc/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>某暗部的少女共栖</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>TV-茅台资源</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>https://caiji.maotaizy.cc/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>梦想改造家 第13季</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>TV-无尽资源</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>https://api.wujinapi.net/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>穿越时空甩掉你</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>TV-360资源</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>https://360zy.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>某暗部的少女共栖</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>🎬极速资源</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>https://jszyapi.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>方舟一号第三季</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>金鹰资源采集网</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>https://jyzyapi.com/provide/vod</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>方舟一号第三季</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>索尼-闪电资源</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>https://xsd.sdzyapi.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>可以爱你吗</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>红牛资源3</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>https://www.hongniuzy3.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>药屋少女的呢喃第三季</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>豪华资源(代理)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>https://pz.v88.qzz.io/?url=https://hhzyapi.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>方舟一号第三季</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>18禁/动漫</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J42" t="n">
-        <v>12</v>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>国产自拍 | 日本无码 | 日本有码 | 中文字幕 | 欧美精品 | 成人动漫 | 日本素人 | 高清名优 | 三级伦理 | 网红主播 | 映画传媒 | 人妻熟女 | 口爆颜射 | 萝莉少女 | SM调教 | 美乳巨乳 | 短视频 | 制服诱惑 | 女同性爱 | AI换脸</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>sp696</t>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>非凡影视</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>http://ffzy5.tv/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>我家的弟弟们真是让您费心了</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>🎬快车资源</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>https://caiji.kuaichezy.org/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>可以爱你吗</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>🎬360 资源</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>https://360zyzz.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Doctor X：白色黑手党时代</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>🎬量子资源</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>https://cj.lzcaiji.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>霹雳英雄战纪之塗附世界</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>百度云zy(代理)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>https://pz.v88.qzz.io/?url=https://api.apibdzy.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>玄苍路之初入宗门</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>🎬豆瓣资源</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>https://caiji.dbzy5.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>骑士情缘</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>🎬优质资源</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>https://api.yzzy-api.com/inc/apijson.php</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>梦想改造家第13季</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>🎬金鹰点播</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>https://jyzyapi.com/provide/vod/from/jinyingyun/at/json</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>方舟一号第三季</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>非凡影视new</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>https://api.ffzyapi.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>我家的弟弟们真是让您费心了</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>TV-如意资源</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>https://cj.rycjapi.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>霹雳英雄战纪之塗附世界</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>iqiyi资源</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>https://www.iqiyizyapi.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>万物生灵第七季</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>TV-非凡资源</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>https://cj.ffzyapi.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>我家的弟弟们真是让您费心了</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>如意资源(代理)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>https://pz.v88.qzz.io/?url=https://cj.rycjapi.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>霹雳英雄战纪之塗附世界</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>艾旦影视(代理)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>https://pz.v88.qzz.io/?url=https://lovedan.net/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>伟大的长征</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>🎬猫眼资源</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>https://api.maoyanapi.top/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>失败:ReadTimeout</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>🔞小鸡资源</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>https://api.xiaojizy.live/provide/vod</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>李素英合3</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>463</v>
+      </c>
+      <c r="F58" t="n">
+        <v>174</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>慢</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>AV-JKUN资源</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>https://jkunzyapi.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>pacopacomama-072023_880-</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>AV-玉兔资源</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>https://apiyutu.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>家庭旅馆偷拍性饥渴嫂子偷情小叔子裤子都没脱就主动</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>AV-奥斯卡资源</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>https://aosikazy.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>真实与后妈乱伦9个月</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>AV-91麻豆</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>https://91md.me/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>被老师欺负的黑丝女高-桥本香菜</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>AV-森林资源</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>https://slapibf.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>FTHTD-144FALENO学校训练营公共浴池</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>AV-souav资源</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>https://api.souavzy.vip/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>白嫩美女月月无套内射初体验</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>AV-精品资源</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>https://www.jingpinx.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>純潔的輪舞曲_2</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>AV-乐播资源</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>https://lbapi9.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>[无码] 苗条人妻床上骚劲爆棚，风骚妩媚狂求内射</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>AV-番号资源</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>http://fhapi9.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>[SSNI-666] 极品人妻被睡服，巨乳爆操内</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>AV-奶香香</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>https://Naixxzy.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>[换脸]孙彩瑛 热热的骚逼..</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>AV-老色逼资源</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>https://apilsbzy1.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>家庭旅馆偷拍性饥渴嫂子偷情小叔子裤子都没脱就主动</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>性吧资源</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>https://xingba111.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DASS-303 被派遣按摩師 按摩到敏感部位 </t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>黄色资源啊啊</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>https://hsckzy888.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>公共厕所肉便器 我二话 高岭千佳</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>AV-155资源</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>https://155api.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>内裤走光后宫学园只有我一MOODYZ大崎広浩治沙</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>AV-辣椒资源</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>https://apilj.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>泌尿科的美人女医8人プラネットプラス伊织凉子,管</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>🔞黄色仓库</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>https://hsckzy.xyz/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>公共厕所肉便器 我二话 高岭千佳</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>🔞滴滴资源</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>https://api.ddapi.cc/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>双飞学生妹【蔡萝莉】SM捆绑~白丝足交~强制高潮</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>🔞森林资源</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>https://beiyong.slapibf.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>FTHTD-144FALENO学校训练营公共浴池</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>🔞豆豆资源</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>https://api.douapi.cc/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>美腿玉足控韩国水娃【Hella_cute】顶级吊</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>🔞-大奶子-</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>https://apidanaizi.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>【最新自录-清纯甜美二次元美少女】白裙情趣装罕见</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>🔞色猫资源</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>https://caiji.semaozy.net/inc/apijson_vod.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>🔞桃花资源</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>https://thzy1.me/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>[HornyVerse]_Jane_Doe_Fu</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>🔞杏吧资源</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>https://xingba222.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DASS-303 被派遣按摩師 按摩到敏感部位 </t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>🔞souavZY</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>https://api.souavzyw.net/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>与儿子所在托儿所的巨乳人妻老师缠绵做爱～老师太过</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>🔞黑料资源</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>https://www.heiliaozyapi.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>绿播福利姬女神下海硬控你十分钟一看就高端货超美脸</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>AV-鲨鱼资源</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>https://shayuapi.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>[瘦猴勾搭] 良家人妻被撩到腿软，眼睛妹妹骚穴求</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>否</t>
         </is>
       </c>
     </row>

--- a/output/源清单.xlsx
+++ b/output/源清单.xlsx
@@ -10310,12 +10310,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TV-天涯资源</t>
+          <t>TV-如意资源</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://tyyszy.com/api.php/provide/vod</t>
+          <t>https://cj.rycjapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -10325,39 +10325,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>改造旧冷库后我住成了大别墅</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>霹雳英雄战纪之塗附世界</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>6564</v>
+      </c>
+      <c r="F2" t="n">
+        <v>377</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>中</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TV-光速资源</t>
+          <t>如意资源(代理)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://api.guangsuapi.com/api.php/provide/vod</t>
+          <t>https://pz.v88.qzz.io/?url=https://cj.rycjapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -10367,22 +10363,18 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>方舟一号第三季</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>霹雳英雄战纪之塗附世界</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>3648</v>
+      </c>
+      <c r="F3" t="n">
+        <v>341</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>中</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -10394,12 +10386,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TV-无尽资源</t>
+          <t>TV-360资源</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://api.wujinapi.com/api.php/provide/vod</t>
+          <t>https://360zy.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -10409,39 +10401,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>穿越时空甩掉你</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>某暗部的少女共栖</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1288</v>
+      </c>
+      <c r="F4" t="n">
+        <v>277</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>中</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TV-wujinapi无尽</t>
+          <t>百度云zy(代理)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://api.wujinapi.cc/api.php/provide/vod</t>
+          <t>https://pz.v88.qzz.io/?url=https://api.apibdzy.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -10451,22 +10439,18 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>穿越时空甩掉你</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>玄苍路之初入宗门</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>505</v>
+      </c>
+      <c r="F5" t="n">
+        <v>248</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>慢</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -10496,19 +10480,15 @@
           <t>如果感激的话就回报到下半身吧</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E6" t="n">
+        <v>511</v>
+      </c>
+      <c r="F6" t="n">
+        <v>240</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>慢</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -10520,12 +10500,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TV-丫丫点播</t>
+          <t>TV-ikun资源</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://cj.yayazy.net/api.php/provide/vod</t>
+          <t>https://ikunzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -10535,22 +10515,18 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>可以爱你吗</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>某暗部的少女共栖</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>541</v>
+      </c>
+      <c r="F7" t="n">
+        <v>186</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>慢</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -10562,12 +10538,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TV-ikun资源</t>
+          <t>iqiyi资源</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://ikunzyapi.com/api.php/provide/vod</t>
+          <t>https://www.iqiyizyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -10577,39 +10553,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>某暗部的少女共栖</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>万物生灵第七季</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2845</v>
+      </c>
+      <c r="F8" t="n">
+        <v>178</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>慢</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TV-无尽资源</t>
+          <t>TV-百度云资源</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://api.wujinapi.me/api.php/provide/vod</t>
+          <t>https://api.apibdzy.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -10619,22 +10591,18 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>穿越时空甩掉你</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>玄苍路之初入宗门</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>416</v>
+      </c>
+      <c r="F9" t="n">
+        <v>167</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>慢</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -10646,12 +10614,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TV-樱花资源</t>
+          <t>TV-茅台资源</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://m3u8.apiyhzy.com/api.php/provide/vod</t>
+          <t>https://caiji.maotaizy.cc/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -10661,39 +10629,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>裴太太柔弱人设又翻车了</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>梦想改造家 第13季</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1641</v>
+      </c>
+      <c r="F10" t="n">
+        <v>118</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>慢</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TV-新浪点播</t>
+          <t>TV-樱花资源</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://api.xinlangapi.com/xinlangapi.php/provide/vod</t>
+          <t>https://m3u8.apiyhzy.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -10703,22 +10667,18 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>方舟一号第三季</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>裴太太柔弱人设又翻车了</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>133</v>
+      </c>
+      <c r="F11" t="n">
+        <v>105</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>慢</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -10730,12 +10690,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TV-1080资源</t>
+          <t>TV-魔都动漫</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://api.1080zyku.com/inc/api_mac10.php</t>
+          <t>https://caiji.moduapi.cc/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -10745,39 +10705,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>冰雪狙击</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>某暗部的少女共栖</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1235</v>
+      </c>
+      <c r="F12" t="n">
+        <v>66</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>慢</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TV-最大点播</t>
+          <t>TV-魔都资源</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>http://zuidazy.me/api.php/provide/vod</t>
+          <t>https://www.mdzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -10787,22 +10743,18 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>可以爱你吗</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>某暗部的少女共栖</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1207</v>
+      </c>
+      <c r="F13" t="n">
+        <v>62</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>慢</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -10814,12 +10766,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TV-U酷资源88</t>
+          <t>TV-光速资源</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://api.ukuapi88.com/api.php/provide/vod</t>
+          <t>https://api.guangsuapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -10829,7 +10781,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>谋杀奇闻 第一季</t>
+          <t>方舟一号第三季</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -10856,12 +10808,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TV-百度云资源</t>
+          <t>TV-新浪点播</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://api.apibdzy.com/api.php/provide/vod</t>
+          <t>https://api.xinlangapi.com/xinlangapi.php/provide/vod</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -10871,7 +10823,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>玄苍路之初入宗门</t>
+          <t>方舟一号第三季</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -10898,12 +10850,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TV-索尼资源</t>
+          <t>TV-U酷资源</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://suoniapi.com/api.php/provide/vod</t>
+          <t>https://api.ukuapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -10913,7 +10865,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>改造旧冷库后我住成了大别墅</t>
+          <t>谋杀奇闻 第一季</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -10940,12 +10892,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TV-红牛资源</t>
+          <t>TV-U酷资源88</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://www.hongniuzy2.com/api.php/provide/vod</t>
+          <t>https://api.ukuapi88.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -10955,7 +10907,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>药屋少女的呢喃第三季</t>
+          <t>谋杀奇闻 第一季</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -10982,12 +10934,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TV-最大资源</t>
+          <t>TV-步步高资源</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://api.zuidapi.com/api.php/provide/vod</t>
+          <t>https://api.yparse.com/api/json</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -10997,7 +10949,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>可以爱你吗</t>
+          <t>Word is Bond</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -11024,12 +10976,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TV-牛牛点播</t>
+          <t>TV-无尽资源</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://api.niuniuzy.me/api.php/provide/vod</t>
+          <t>https://api.wujinapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -11039,13 +10991,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>可以爱你吗</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>穿越时空甩掉你</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>457</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -11054,7 +11004,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -11066,12 +11016,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TV-暴风资源</t>
+          <t>TV-最大资源</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://bfzyapi.com/api.php/provide/vod</t>
+          <t>https://api.zuidapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -11081,13 +11031,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>乌鸦俱乐部</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>可以爱你吗</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>74</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -11096,7 +11044,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -11108,12 +11056,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TV-虎牙资源</t>
+          <t>TV-无尽资源</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://www.huyaapi.com/api.php/provide/vod</t>
+          <t>https://api.wujinapi.me/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -11123,13 +11071,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>南瓜头怪2</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>穿越时空甩掉你</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>60</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -11138,7 +11084,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -11150,12 +11096,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TV-电影天堂资源</t>
+          <t>TV-wujinapi无尽</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>http://caiji.dyttzyapi.com/api.php/provide/vod</t>
+          <t>https://api.wujinapi.cc/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -11165,13 +11111,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>霹雳英雄战纪之塗附世界</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>穿越时空甩掉你</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -11180,24 +11124,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TV-豪华资源</t>
+          <t>TV-最大点播</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://hhzyapi.com/api.php/provide/vod</t>
+          <t>http://zuidazy.me/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -11207,13 +11151,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>方舟一号第三季</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>可以爱你吗</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>677</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -11222,7 +11164,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -11234,12 +11176,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TV-速博资源</t>
+          <t>TV-电影天堂资源</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://subocaiji.com/api.php/provide/vod</t>
+          <t>http://caiji.dyttzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -11249,7 +11191,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>方舟一号第三季</t>
+          <t>霹雳英雄战纪之塗附世界</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11269,19 +11211,19 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TV-神马云</t>
+          <t>TV-红牛资源</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://api.1080zyku.com/inc/apijson.php</t>
+          <t>https://www.hongniuzy2.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -11291,7 +11233,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>梦想改造家第13季</t>
+          <t>药屋少女的呢喃第三季</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -11311,19 +11253,19 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TV-金鹰资源</t>
+          <t>TV-虎牙资源</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://jyzyapi.com/api.php/provide/vod</t>
+          <t>https://www.huyaapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -11333,7 +11275,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>方舟一号第三季</t>
+          <t>南瓜头怪2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -11360,12 +11302,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TV-金鹰点播</t>
+          <t>TV-无尽资源</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://jinyingzy.com/api.php/provide/vod</t>
+          <t>https://api.wujinapi.net/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -11375,13 +11317,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>方舟一号第三季</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>穿越时空甩掉你</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -11390,7 +11330,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -11402,12 +11342,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TV-步步高资源</t>
+          <t>TV-丫丫点播</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://api.yparse.com/api/json</t>
+          <t>https://cj.yayazy.net/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -11417,13 +11357,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Word is Bond</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>可以爱你吗</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>766</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -11432,7 +11370,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -11444,12 +11382,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TV-豆瓣资源</t>
+          <t>TV-豪华资源</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://dbzy.tv/api.php/provide/vod</t>
+          <t>https://hhzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -11459,7 +11397,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>骑士情缘</t>
+          <t>方舟一号第三季</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -11479,19 +11417,19 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TV-量子资源</t>
+          <t>TV-速博资源</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://cj.lziapi.com/api.php/provide/vod</t>
+          <t>https://subocaiji.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -11501,7 +11439,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>霹雳英雄战纪之塗附世界</t>
+          <t>方舟一号第三季</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -11528,12 +11466,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TV-闪电资源</t>
+          <t>TV-金鹰资源</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://sdzyapi.com/api.php/provide/vod</t>
+          <t>https://jyzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -11543,7 +11481,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>可以爱你吗</t>
+          <t>方舟一号第三季</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -11570,12 +11508,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TV-U酷资源</t>
+          <t>TV-量子资源</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://api.ukuapi.com/api.php/provide/vod</t>
+          <t>https://cj.lziapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -11585,7 +11523,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>谋杀奇闻 第一季</t>
+          <t>霹雳英雄战纪之塗附世界</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -11612,12 +11550,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TV-魔都资源</t>
+          <t>TV-豆瓣资源</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://www.mdzyapi.com/api.php/provide/vod</t>
+          <t>https://dbzy.tv/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -11627,7 +11565,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>某暗部的少女共栖</t>
+          <t>骑士情缘</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -11647,19 +11585,19 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TV-魔都动漫</t>
+          <t>TV-金鹰点播</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://caiji.moduapi.cc/api.php/provide/vod</t>
+          <t>https://jinyingzy.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -11669,7 +11607,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>某暗部的少女共栖</t>
+          <t>方舟一号第三季</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -11696,12 +11634,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TV-茅台资源</t>
+          <t>TV-索尼资源</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://caiji.maotaizy.cc/api.php/provide/vod</t>
+          <t>https://suoniapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -11711,13 +11649,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>梦想改造家 第13季</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>改造旧冷库后我住成了大别墅</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>52</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -11726,24 +11662,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TV-无尽资源</t>
+          <t>TV-闪电资源</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://api.wujinapi.net/api.php/provide/vod</t>
+          <t>https://sdzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -11753,13 +11689,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>穿越时空甩掉你</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>可以爱你吗</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>728</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -11768,7 +11702,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -11780,12 +11714,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TV-360资源</t>
+          <t>TV-牛牛点播</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://360zy.com/api.php/provide/vod</t>
+          <t>https://api.niuniuzy.me/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -11795,13 +11729,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>某暗部的少女共栖</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>可以爱你吗</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>731</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -11810,24 +11742,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>🎬极速资源</t>
+          <t>TV-非凡资源</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://jszyapi.com/api.php/provide/vod</t>
+          <t>https://cj.ffzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -11837,7 +11769,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>方舟一号第三季</t>
+          <t>我家的弟弟们真是让您费心了</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -11857,19 +11789,19 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>金鹰资源采集网</t>
+          <t>TV-暴风资源</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://jyzyapi.com/provide/vod</t>
+          <t>https://bfzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -11879,13 +11811,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>方舟一号第三季</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>乌鸦俱乐部</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>716</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -11894,7 +11824,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -11906,12 +11836,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>索尼-闪电资源</t>
+          <t>TV-1080资源</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://xsd.sdzyapi.com/api.php/provide/vod</t>
+          <t>https://api.1080zyku.com/inc/api_mac10.php</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -11921,13 +11851,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>可以爱你吗</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>冰雪狙击</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>730</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -11936,24 +11864,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>红牛资源3</t>
+          <t>TV-天涯资源</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://www.hongniuzy3.com/api.php/provide/vod</t>
+          <t>https://tyyszy.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -11963,13 +11891,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>药屋少女的呢喃第三季</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>改造旧冷库后我住成了大别墅</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>264</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -11978,24 +11904,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>失败:ReadTimeout</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>豪华资源(代理)</t>
+          <t>🎬极速资源</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://pz.v88.qzz.io/?url=https://hhzyapi.com/api.php/provide/vod</t>
+          <t>https://jszyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -12032,12 +11958,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>非凡影视</t>
+          <t>金鹰资源采集网</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>http://ffzy5.tv/api.php/provide/vod</t>
+          <t>https://jyzyapi.com/provide/vod</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -12047,7 +11973,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>我家的弟弟们真是让您费心了</t>
+          <t>方舟一号第三季</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -12067,19 +11993,19 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>🎬快车资源</t>
+          <t>红牛资源3</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://caiji.kuaichezy.org/api.php/provide/vod</t>
+          <t>https://www.hongniuzy3.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -12089,7 +12015,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>可以爱你吗</t>
+          <t>药屋少女的呢喃第三季</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -12109,19 +12035,19 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>🎬360 资源</t>
+          <t>非凡影视new</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://360zyzz.com/api.php/provide/vod</t>
+          <t>https://api.ffzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -12131,7 +12057,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Doctor X：白色黑手党时代</t>
+          <t>我家的弟弟们真是让您费心了</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -12158,12 +12084,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>🎬量子资源</t>
+          <t>非凡影视</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://cj.lzcaiji.com/api.php/provide/vod</t>
+          <t>http://ffzy5.tv/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -12173,7 +12099,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>霹雳英雄战纪之塗附世界</t>
+          <t>我家的弟弟们真是让您费心了</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -12193,19 +12119,19 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>百度云zy(代理)</t>
+          <t>豪华资源(代理)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://pz.v88.qzz.io/?url=https://api.apibdzy.com/api.php/provide/vod</t>
+          <t>https://pz.v88.qzz.io/?url=https://hhzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -12215,7 +12141,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>玄苍路之初入宗门</t>
+          <t>方舟一号第三季</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -12242,12 +12168,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>🎬豆瓣资源</t>
+          <t>🎬量子资源</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://caiji.dbzy5.com/api.php/provide/vod</t>
+          <t>https://cj.lzcaiji.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -12257,7 +12183,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>骑士情缘</t>
+          <t>霹雳英雄战纪之塗附世界</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -12277,19 +12203,19 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>🎬优质资源</t>
+          <t>索尼-闪电资源</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://api.yzzy-api.com/inc/apijson.php</t>
+          <t>https://xsd.sdzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -12299,13 +12225,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>梦想改造家第13季</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>可以爱你吗</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>702</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -12314,12 +12238,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -12368,12 +12292,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>非凡影视new</t>
+          <t>🎬豆瓣资源</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://api.ffzyapi.com/api.php/provide/vod</t>
+          <t>https://caiji.dbzy5.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -12383,7 +12307,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>我家的弟弟们真是让您费心了</t>
+          <t>骑士情缘</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -12410,12 +12334,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>TV-如意资源</t>
+          <t>TV-神马云</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://cj.rycjapi.com/api.php/provide/vod</t>
+          <t>https://api.1080zyku.com/inc/apijson.php</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -12425,13 +12349,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>霹雳英雄战纪之塗附世界</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>绿头苍蝇</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>661</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -12440,7 +12362,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -12452,12 +12374,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>iqiyi资源</t>
+          <t>🎬360 资源</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://www.iqiyizyapi.com/api.php/provide/vod</t>
+          <t>https://360zyzz.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -12467,13 +12389,11 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>万物生灵第七季</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Doctor X：白色黑手党时代</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>621</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -12482,7 +12402,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -12494,12 +12414,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TV-非凡资源</t>
+          <t>🎬快车资源</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://cj.ffzyapi.com/api.php/provide/vod</t>
+          <t>https://caiji.kuaichezy.org/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -12509,13 +12429,11 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>我家的弟弟们真是让您费心了</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>可以爱你吗</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>733</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -12524,24 +12442,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>如意资源(代理)</t>
+          <t>艾旦影视(代理)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://pz.v88.qzz.io/?url=https://cj.rycjapi.com/api.php/provide/vod</t>
+          <t>https://pz.v88.qzz.io/?url=https://lovedan.net/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -12551,13 +12469,11 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>霹雳英雄战纪之塗附世界</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>伟大的长征</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>3497</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -12566,7 +12482,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -12578,12 +12494,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>艾旦影视(代理)</t>
+          <t>🎬优质资源</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://pz.v88.qzz.io/?url=https://lovedan.net/api.php/provide/vod</t>
+          <t>https://api.yzzy-api.com/inc/apijson.php</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -12593,13 +12509,11 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>伟大的长征</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>绿头苍蝇</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>867</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -12608,12 +12522,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -12658,12 +12572,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>🔞小鸡资源</t>
+          <t>AV-森林资源</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://api.xiaojizy.live/provide/vod</t>
+          <t>https://slapibf.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -12673,35 +12587,35 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>李素英合3</t>
+          <t>FTHTD-144FALENO学校训练营公共浴池</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>463</v>
+        <v>492</v>
       </c>
       <c r="F58" t="n">
-        <v>174</v>
+        <v>11175</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>慢</t>
+          <t>快</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AV-JKUN资源</t>
+          <t>🔞森林资源</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://jkunzyapi.com/api.php/provide/vod</t>
+          <t>https://beiyong.slapibf.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -12711,22 +12625,18 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>pacopacomama-072023_880-</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>FTHTD-144FALENO学校训练营公共浴池</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>559</v>
+      </c>
+      <c r="F59" t="n">
+        <v>10991</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>快</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -12738,12 +12648,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AV-玉兔资源</t>
+          <t>AV-155资源</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://apiyutu.com/api.php/provide/vod</t>
+          <t>https://155api.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -12753,22 +12663,18 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>家庭旅馆偷拍性饥渴嫂子偷情小叔子裤子都没脱就主动</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>内裤走光后宫学园只有我一MOODYZ大崎広浩治沙</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>55</v>
+      </c>
+      <c r="F60" t="n">
+        <v>9523</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>快</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -12780,12 +12686,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AV-奥斯卡资源</t>
+          <t>🔞杏吧资源</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://aosikazy.com/api.php/provide/vod</t>
+          <t>https://xingba222.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -12795,39 +12701,35 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>真实与后妈乱伦9个月</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t xml:space="preserve">DASS-303 被派遣按摩師 按摩到敏感部位 </t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>476</v>
+      </c>
+      <c r="F61" t="n">
+        <v>7670</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>快</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AV-91麻豆</t>
+          <t>性吧资源</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://91md.me/api.php/provide/vod</t>
+          <t>https://xingba111.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -12837,22 +12739,18 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>被老师欺负的黑丝女高-桥本香菜</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t xml:space="preserve">DASS-303 被派遣按摩師 按摩到敏感部位 </t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>621</v>
+      </c>
+      <c r="F62" t="n">
+        <v>7620</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>快</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -12864,12 +12762,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AV-森林资源</t>
+          <t>AV-番号资源</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://slapibf.com/api.php/provide/vod</t>
+          <t>http://fhapi9.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -12879,39 +12777,35 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>FTHTD-144FALENO学校训练营公共浴池</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>[SSNI-666] 极品人妻被睡服，巨乳爆操内</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>624</v>
+      </c>
+      <c r="F63" t="n">
+        <v>6948</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>快</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AV-souav资源</t>
+          <t>AV-鲨鱼资源</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://api.souavzy.vip/api.php/provide/vod</t>
+          <t>https://shayuapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -12921,39 +12815,35 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>白嫩美女月月无套内射初体验</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>[瘦猴勾搭] 良家人妻被撩到腿软，眼睛妹妹骚穴求</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>9382</v>
+      </c>
+      <c r="F64" t="n">
+        <v>5048</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>快</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AV-精品资源</t>
+          <t>AV-辣椒资源</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://www.jingpinx.com/api.php/provide/vod</t>
+          <t>https://apilj.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -12963,22 +12853,18 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>純潔的輪舞曲_2</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>泌尿科的美人女医8人プラネットプラス伊织凉子,管</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>731</v>
+      </c>
+      <c r="F65" t="n">
+        <v>4988</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>快</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -13008,19 +12894,15 @@
           <t>[无码] 苗条人妻床上骚劲爆棚，风骚妩媚狂求内射</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E66" t="n">
+        <v>860</v>
+      </c>
+      <c r="F66" t="n">
+        <v>2018</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>快</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -13032,12 +12914,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AV-番号资源</t>
+          <t>🔞豆豆资源</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>http://fhapi9.com/api.php/provide/vod</t>
+          <t>https://api.douapi.cc/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -13047,39 +12929,35 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>[SSNI-666] 极品人妻被睡服，巨乳爆操内</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>美腿玉足控韩国水娃【Hella_cute】顶级吊</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>344</v>
+      </c>
+      <c r="F67" t="n">
+        <v>895</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>中</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AV-奶香香</t>
+          <t>🔞滴滴资源</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://Naixxzy.com/api.php/provide/vod</t>
+          <t>https://api.ddapi.cc/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -13089,39 +12967,35 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>[换脸]孙彩瑛 热热的骚逼..</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>双飞学生妹【蔡萝莉】SM捆绑~白丝足交~强制高潮</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>376</v>
+      </c>
+      <c r="F68" t="n">
+        <v>842</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>中</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AV-老色逼资源</t>
+          <t>AV-JKUN资源</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://apilsbzy1.com/api.php/provide/vod</t>
+          <t>https://jkunzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -13131,22 +13005,18 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>家庭旅馆偷拍性饥渴嫂子偷情小叔子裤子都没脱就主动</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>pacopacomama-072023_880-</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>69</v>
+      </c>
+      <c r="F69" t="n">
+        <v>651</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>中</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -13158,12 +13028,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>性吧资源</t>
+          <t>AV-老色逼资源</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://xingba111.com/api.php/provide/vod</t>
+          <t>https://apilsbzy1.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -13173,22 +13043,18 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">DASS-303 被派遣按摩師 按摩到敏感部位 </t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>家庭旅馆偷拍性饥渴嫂子偷情小叔子裤子都没脱就主动</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>583</v>
+      </c>
+      <c r="F70" t="n">
+        <v>453</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>中</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -13200,12 +13066,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>黄色资源啊啊</t>
+          <t>AV-玉兔资源</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://hsckzy888.com/api.php/provide/vod</t>
+          <t>https://apiyutu.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -13215,22 +13081,18 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>公共厕所肉便器 我二话 高岭千佳</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>家庭旅馆偷拍性饥渴嫂子偷情小叔子裤子都没脱就主动</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>372</v>
+      </c>
+      <c r="F71" t="n">
+        <v>436</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>中</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -13242,12 +13104,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AV-155资源</t>
+          <t>🔞桃花资源</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://155api.com/api.php/provide/vod</t>
+          <t>https://thzy1.me/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -13257,39 +13119,35 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>内裤走光后宫学园只有我一MOODYZ大崎広浩治沙</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>[HornyVerse]_Jane_Doe_Fu</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>475</v>
+      </c>
+      <c r="F72" t="n">
+        <v>365</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>中</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AV-辣椒资源</t>
+          <t>AV-奶香香</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://apilj.com/api.php/provide/vod</t>
+          <t>https://Naixxzy.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -13299,22 +13157,18 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>泌尿科的美人女医8人プラネットプラス伊织凉子,管</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>[换脸]孙彩瑛 热热的骚逼..</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>557</v>
+      </c>
+      <c r="F73" t="n">
+        <v>299</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>中</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -13326,12 +13180,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>🔞黄色仓库</t>
+          <t>🔞小鸡资源</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://hsckzy.xyz/api.php/provide/vod</t>
+          <t>https://api.xiaojizy.live/provide/vod</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -13341,39 +13195,35 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>公共厕所肉便器 我二话 高岭千佳</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>李素英合3</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>357</v>
+      </c>
+      <c r="F74" t="n">
+        <v>235</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>慢</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>🔞滴滴资源</t>
+          <t>🔞-大奶子-</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://api.ddapi.cc/api.php/provide/vod</t>
+          <t>https://apidanaizi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -13383,22 +13233,18 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>双飞学生妹【蔡萝莉】SM捆绑~白丝足交~强制高潮</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>【最新自录-清纯甜美二次元美少女】白裙情趣装罕见</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>540</v>
+      </c>
+      <c r="F75" t="n">
+        <v>227</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>慢</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -13410,12 +13256,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>🔞森林资源</t>
+          <t>AV-精品资源</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://beiyong.slapibf.com/api.php/provide/vod</t>
+          <t>https://www.jingpinx.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -13425,39 +13271,35 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>FTHTD-144FALENO学校训练营公共浴池</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>純潔的輪舞曲_2</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>392</v>
+      </c>
+      <c r="F76" t="n">
+        <v>198</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>慢</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>🔞豆豆资源</t>
+          <t>AV-奥斯卡资源</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://api.douapi.cc/api.php/provide/vod</t>
+          <t>https://aosikazy.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -13467,39 +13309,35 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>美腿玉足控韩国水娃【Hella_cute】顶级吊</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>真实与后妈乱伦9个月</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>655</v>
+      </c>
+      <c r="F77" t="n">
+        <v>184</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>慢</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>🔞-大奶子-</t>
+          <t>🔞黑料资源</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://apidanaizi.com/api.php/provide/vod</t>
+          <t>https://www.heiliaozyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -13509,39 +13347,35 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>【最新自录-清纯甜美二次元美少女】白裙情趣装罕见</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>绿播福利姬女神下海硬控你十分钟一看就高端货超美脸</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>934</v>
+      </c>
+      <c r="F78" t="n">
+        <v>134</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>慢</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>🔞色猫资源</t>
+          <t>AV-91麻豆</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://caiji.semaozy.net/inc/apijson_vod.php/provide/vod</t>
+          <t>https://91md.me/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -13549,20 +13383,20 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>被老师欺负的黑丝女高-桥本香菜</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>1092</v>
+      </c>
+      <c r="F79" t="n">
+        <v>115</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>慢</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -13574,12 +13408,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>🔞桃花资源</t>
+          <t>AV-souav资源</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://thzy1.me/api.php/provide/vod</t>
+          <t>https://api.souavzy.vip/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -13589,13 +13423,11 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>[HornyVerse]_Jane_Doe_Fu</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>白嫩美女月月无套内射初体验</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>926</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -13604,24 +13436,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>🔞杏吧资源</t>
+          <t>黄色资源啊啊</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://xingba222.com/api.php/provide/vod</t>
+          <t>https://hsckzy888.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -13631,7 +13463,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">DASS-303 被派遣按摩師 按摩到敏感部位 </t>
+          <t>公共厕所肉便器 我二话 高岭千佳</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -13658,12 +13490,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>🔞souavZY</t>
+          <t>🔞黄色仓库</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://api.souavzyw.net/api.php/provide/vod</t>
+          <t>https://hsckzy.xyz/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -13673,7 +13505,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>与儿子所在托儿所的巨乳人妻老师缠绵做爱～老师太过</t>
+          <t>公共厕所肉便器 我二话 高岭千佳</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -13700,12 +13532,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>🔞黑料资源</t>
+          <t>🔞souavZY</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://www.heiliaozyapi.com/api.php/provide/vod</t>
+          <t>https://api.souavzyw.net/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -13715,13 +13547,11 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>绿播福利姬女神下海硬控你十分钟一看就高端货超美脸</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>与儿子所在托儿所的巨乳人妻老师缠绵做爱～老师太过</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>566</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -13730,24 +13560,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AV-鲨鱼资源</t>
+          <t>🔞色猫资源</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://shayuapi.com/api.php/provide/vod</t>
+          <t>https://caiji.semaozy.net/inc/apijson_vod.php/provide/vod</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -13755,11 +13585,7 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>[瘦猴勾搭] 良家人妻被撩到腿软，眼睛妹妹骚穴求</t>
-        </is>
-      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -13777,7 +13603,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>

--- a/output/源清单.xlsx
+++ b/output/源清单.xlsx
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1361</v>
+        <v>798</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>265</v>
+        <v>72</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2277</v>
+        <v>2249</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>7679</v>
+        <v>280</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5053</v>
+        <v>269</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>507</v>
+        <v>425</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>87</v>
+        <v>429</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>677</v>
+        <v>416</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>497</v>
+        <v>232</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>504</v>
+        <v>266</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>4002</v>
+        <v>6811</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>476</v>
+        <v>382</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>270</v>
+        <v>436</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>281</v>
+        <v>57</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>646</v>
+        <v>415</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>860</v>
+        <v>978</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>830</v>
+        <v>804</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>821</v>
+        <v>719</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>395</v>
+        <v>378</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>233</v>
+        <v>87</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>364</v>
+        <v>138</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1567</v>
+        <v>1085</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>436</v>
+        <v>385</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1074</v>
+        <v>324</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>604</v>
+        <v>419</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>857</v>
+        <v>791</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>302</v>
+        <v>59</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>367</v>
+        <v>213</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>6352</v>
+        <v>1174</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>894</v>
+        <v>209</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>658</v>
+        <v>636</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>452</v>
+        <v>255</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>708</v>
+        <v>597</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>525</v>
+        <v>388</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>713</v>
+        <v>538</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>439</v>
+        <v>230</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>435</v>
+        <v>365</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>3344</v>
+        <v>1863</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>748</v>
+        <v>832</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>816</v>
+        <v>824</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>169</v>
+        <v>143</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="H53" s="2" t="n">
-        <v>643</v>
+        <v>1001</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="H55" s="2" t="n">
-        <v>379</v>
+        <v>64</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         </is>
       </c>
       <c r="H56" s="2" t="n">
-        <v>780</v>
+        <v>685</v>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         </is>
       </c>
       <c r="H57" s="2" t="n">
-        <v>842</v>
+        <v>719</v>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         </is>
       </c>
       <c r="H58" s="2" t="n">
-        <v>803</v>
+        <v>576</v>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="H59" s="2" t="n">
-        <v>1602</v>
+        <v>2148</v>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         </is>
       </c>
       <c r="H60" s="2" t="n">
-        <v>699</v>
+        <v>355</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         </is>
       </c>
       <c r="H61" s="2" t="n">
-        <v>948</v>
+        <v>586</v>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         </is>
       </c>
       <c r="H62" s="2" t="n">
-        <v>486</v>
+        <v>385</v>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         </is>
       </c>
       <c r="H63" s="2" t="n">
-        <v>758</v>
+        <v>610</v>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         </is>
       </c>
       <c r="H64" s="2" t="n">
-        <v>854</v>
+        <v>1013</v>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="H65" s="2" t="n">
-        <v>581</v>
+        <v>394</v>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         </is>
       </c>
       <c r="H66" s="2" t="n">
-        <v>4097</v>
+        <v>592</v>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="H67" s="2" t="n">
-        <v>626</v>
+        <v>497</v>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
@@ -4748,7 +4748,7 @@
         </is>
       </c>
       <c r="H70" s="2" t="n">
-        <v>753</v>
+        <v>802</v>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         </is>
       </c>
       <c r="H71" s="2" t="n">
-        <v>773</v>
+        <v>985</v>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
@@ -4861,20 +4861,22 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>分类实测</t>
+          <t>域名/标记</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>存活</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="n">
-        <v>3585</v>
+          <t>失活</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>18禁/动漫</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -4883,13 +4885,9 @@
         </is>
       </c>
       <c r="K72" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="L72" s="2" t="inlineStr">
-        <is>
-          <t>国产情色 | 日本无码 | AV明星 | 中文字幕 | 网红主播 | 成人动漫 | 欧美情色 | 国模私拍 | 长腿丝袜 | 邻家人妻 | 韩国伦理 | 香港伦理 | 精品推荐 | 原纱央莉 | 柚木TINA | 大桥未久 | AV明星1 | 仁科百华 | 天海翼 | 小川阿佐美</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
@@ -4933,7 +4931,7 @@
         </is>
       </c>
       <c r="H73" s="2" t="n">
-        <v>1774</v>
+        <v>455</v>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
@@ -4992,7 +4990,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>3547</v>
+        <v>871</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -5055,7 +5053,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>416</v>
+        <v>174</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -5171,7 +5169,7 @@
         </is>
       </c>
       <c r="H77" s="2" t="n">
-        <v>712</v>
+        <v>556</v>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
@@ -5394,7 +5392,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -5457,7 +5455,7 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>415</v>
+        <v>382</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -5515,7 +5513,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>369</v>
+        <v>350</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -5683,7 +5681,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>510</v>
+        <v>495</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -5737,7 +5735,7 @@
         </is>
       </c>
       <c r="H87" s="2" t="n">
-        <v>459</v>
+        <v>293</v>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
@@ -5800,7 +5798,7 @@
         </is>
       </c>
       <c r="H88" s="2" t="n">
-        <v>290</v>
+        <v>611</v>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
@@ -5858,7 +5856,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -5912,7 +5910,7 @@
         </is>
       </c>
       <c r="H90" s="2" t="n">
-        <v>756</v>
+        <v>702</v>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
@@ -5966,7 +5964,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>383</v>
+        <v>723</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -6024,7 +6022,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>1811</v>
+        <v>2725</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -6087,7 +6085,7 @@
         </is>
       </c>
       <c r="H93" s="2" t="n">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
@@ -6201,7 +6199,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>1303</v>
+        <v>327</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -6264,7 +6262,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -6327,7 +6325,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>583</v>
+        <v>556</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -6390,7 +6388,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>589</v>
+        <v>366</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -6453,7 +6451,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>756</v>
+        <v>565</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -6516,7 +6514,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>617</v>
+        <v>661</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -6579,7 +6577,7 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>1068</v>
+        <v>749</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -6642,7 +6640,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>254</v>
+        <v>105</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -6705,7 +6703,7 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>2810</v>
+        <v>2345</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -6768,7 +6766,7 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>2299</v>
+        <v>2722</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -6831,7 +6829,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>505</v>
+        <v>310</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -6894,7 +6892,7 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>547</v>
+        <v>766</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -6957,7 +6955,7 @@
         </is>
       </c>
       <c r="H107" s="2" t="n">
-        <v>407</v>
+        <v>273</v>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
@@ -7020,7 +7018,7 @@
         </is>
       </c>
       <c r="H108" s="2" t="n">
-        <v>707</v>
+        <v>543</v>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
@@ -7083,7 +7081,7 @@
         </is>
       </c>
       <c r="H109" s="2" t="n">
-        <v>805</v>
+        <v>366</v>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
@@ -7146,7 +7144,7 @@
         </is>
       </c>
       <c r="H110" s="2" t="n">
-        <v>364</v>
+        <v>340</v>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
@@ -7209,7 +7207,7 @@
         </is>
       </c>
       <c r="H111" s="2" t="n">
-        <v>542</v>
+        <v>323</v>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
@@ -7272,7 +7270,7 @@
         </is>
       </c>
       <c r="H112" s="2" t="n">
-        <v>808</v>
+        <v>691</v>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
@@ -7398,7 +7396,7 @@
         </is>
       </c>
       <c r="H114" s="2" t="n">
-        <v>605</v>
+        <v>447</v>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
@@ -7522,7 +7520,7 @@
         </is>
       </c>
       <c r="H116" s="2" t="n">
-        <v>593</v>
+        <v>486</v>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
@@ -7585,7 +7583,7 @@
         </is>
       </c>
       <c r="H117" s="2" t="n">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
@@ -7644,7 +7642,7 @@
         </is>
       </c>
       <c r="H118" s="2" t="n">
-        <v>758</v>
+        <v>236</v>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
@@ -7788,7 +7786,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>265</v>
+        <v>72</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -7911,7 +7909,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>643</v>
+        <v>1001</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -8029,7 +8027,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>379</v>
+        <v>64</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -8092,7 +8090,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>780</v>
+        <v>685</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -8155,7 +8153,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>842</v>
+        <v>719</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -8218,7 +8216,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>803</v>
+        <v>576</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -8281,7 +8279,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1602</v>
+        <v>2148</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -8344,7 +8342,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>699</v>
+        <v>355</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -8407,7 +8405,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>948</v>
+        <v>586</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -8465,7 +8463,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>486</v>
+        <v>385</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -8528,7 +8526,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>758</v>
+        <v>610</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -8591,7 +8589,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>854</v>
+        <v>1013</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -8649,7 +8647,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>581</v>
+        <v>394</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -8712,7 +8710,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>4097</v>
+        <v>592</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -8770,7 +8768,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>626</v>
+        <v>497</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -8953,7 +8951,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>753</v>
+        <v>802</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -9016,7 +9014,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>773</v>
+        <v>985</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -9065,20 +9063,22 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>分类实测</t>
+          <t>域名/标记</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>存活</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>3585</v>
+          <t>失活</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>18禁/动漫</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -9087,12 +9087,7 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>7</v>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>国产情色 | 日本无码 | AV明星 | 中文字幕 | 网红主播 | 成人动漫 | 欧美情色 | 国模私拍 | 长腿丝袜 | 邻家人妻 | 韩国伦理 | 香港伦理 | 精品推荐 | 原纱央莉 | 柚木TINA | 大桥未久 | AV明星1 | 仁科百华 | 天海翼 | 小川阿佐美</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -9137,7 +9132,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1774</v>
+        <v>455</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -9245,7 +9240,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>712</v>
+        <v>556</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -9303,7 +9298,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>459</v>
+        <v>293</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -9366,7 +9361,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>290</v>
+        <v>611</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -9424,7 +9419,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>756</v>
+        <v>702</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -9482,7 +9477,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -9540,7 +9535,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>407</v>
+        <v>273</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -9603,7 +9598,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>707</v>
+        <v>543</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -9666,7 +9661,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>805</v>
+        <v>366</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -9729,7 +9724,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>364</v>
+        <v>340</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -9792,7 +9787,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>542</v>
+        <v>323</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -9855,7 +9850,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>808</v>
+        <v>691</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -9981,7 +9976,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>605</v>
+        <v>447</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -10104,7 +10099,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>593</v>
+        <v>486</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -10167,7 +10162,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -10225,7 +10220,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>758</v>
+        <v>236</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -10262,7 +10257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H84"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10310,12 +10305,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TV-如意资源</t>
+          <t>如意资源(代理)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://cj.rycjapi.com/api.php/provide/vod</t>
+          <t>https://pz.v88.qzz.io/?url=https://cj.rycjapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -10329,10 +10324,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6564</v>
+        <v>1725</v>
       </c>
       <c r="F2" t="n">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -10341,19 +10336,19 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>如意资源(代理)</t>
+          <t>TV-360资源</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://pz.v88.qzz.io/?url=https://cj.rycjapi.com/api.php/provide/vod</t>
+          <t>https://360zy.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -10363,14 +10358,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>霹雳英雄战纪之塗附世界</t>
+          <t>某暗部的少女共栖</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3648</v>
+        <v>1354</v>
       </c>
       <c r="F3" t="n">
-        <v>341</v>
+        <v>266</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -10379,19 +10374,19 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TV-360资源</t>
+          <t>TV-百度云资源</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://360zy.com/api.php/provide/vod</t>
+          <t>https://api.apibdzy.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -10401,23 +10396,23 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>某暗部的少女共栖</t>
+          <t>玄苍路之初入宗门</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1288</v>
+        <v>277</v>
       </c>
       <c r="F4" t="n">
-        <v>277</v>
+        <v>244</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>慢</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -10443,10 +10438,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>505</v>
+        <v>556</v>
       </c>
       <c r="F5" t="n">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -10481,10 +10476,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>511</v>
+        <v>527</v>
       </c>
       <c r="F6" t="n">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -10519,10 +10514,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="F7" t="n">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -10538,12 +10533,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>iqiyi资源</t>
+          <t>🎬猫眼资源</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://www.iqiyizyapi.com/api.php/provide/vod</t>
+          <t>https://api.maoyanapi.top/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -10553,14 +10548,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>万物生灵第七季</t>
+          <t>斗罗大陆Ⅱ绝世唐门</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2845</v>
+        <v>716</v>
       </c>
       <c r="F8" t="n">
-        <v>178</v>
+        <v>145</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -10576,12 +10571,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TV-百度云资源</t>
+          <t>TV-樱花资源</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://api.apibdzy.com/api.php/provide/vod</t>
+          <t>https://m3u8.apiyhzy.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -10591,14 +10586,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>玄苍路之初入宗门</t>
+          <t>裴太太柔弱人设又翻车了</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>416</v>
+        <v>274</v>
       </c>
       <c r="F9" t="n">
-        <v>167</v>
+        <v>131</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -10633,10 +10628,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1641</v>
+        <v>1592</v>
       </c>
       <c r="F10" t="n">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -10652,12 +10647,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TV-樱花资源</t>
+          <t>iqiyi资源</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://m3u8.apiyhzy.com/api.php/provide/vod</t>
+          <t>https://www.iqiyizyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -10667,14 +10662,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>裴太太柔弱人设又翻车了</t>
+          <t>万物生灵第七季</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>133</v>
+        <v>1724</v>
       </c>
       <c r="F11" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -10683,19 +10678,19 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TV-魔都动漫</t>
+          <t>TV-如意资源</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://caiji.moduapi.cc/api.php/provide/vod</t>
+          <t>https://cj.rycjapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -10705,14 +10700,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>某暗部的少女共栖</t>
+          <t>霹雳英雄战纪之塗附世界</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1235</v>
+        <v>3268</v>
       </c>
       <c r="F12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -10721,19 +10716,19 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TV-魔都资源</t>
+          <t>TV-魔都动漫</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://www.mdzyapi.com/api.php/provide/vod</t>
+          <t>https://caiji.moduapi.cc/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -10747,7 +10742,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1207</v>
+        <v>719</v>
       </c>
       <c r="F13" t="n">
         <v>62</v>
@@ -10766,12 +10761,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TV-光速资源</t>
+          <t>TV-魔都资源</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://api.guangsuapi.com/api.php/provide/vod</t>
+          <t>https://www.mdzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -10781,22 +10776,18 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>方舟一号第三季</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>某暗部的少女共栖</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>651</v>
+      </c>
+      <c r="F14" t="n">
+        <v>62</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>慢</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -10850,12 +10841,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TV-U酷资源</t>
+          <t>TV-光速资源</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://api.ukuapi.com/api.php/provide/vod</t>
+          <t>https://api.guangsuapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -10865,7 +10856,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>谋杀奇闻 第一季</t>
+          <t>方舟一号第三季</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -10892,12 +10883,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TV-U酷资源88</t>
+          <t>TV-无尽资源</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://api.ukuapi88.com/api.php/provide/vod</t>
+          <t>https://api.wujinapi.me/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -10907,13 +10898,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>谋杀奇闻 第一季</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>穿越时空甩掉你</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>58</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -10922,7 +10911,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -10934,12 +10923,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TV-步步高资源</t>
+          <t>TV-wujinapi无尽</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://api.yparse.com/api/json</t>
+          <t>https://api.wujinapi.cc/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -10949,13 +10938,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Word is Bond</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>穿越时空甩掉你</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>46</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -10964,7 +10951,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -10995,7 +10982,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>457</v>
+        <v>57</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -11016,12 +11003,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TV-最大资源</t>
+          <t>TV-U酷资源88</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://api.zuidapi.com/api.php/provide/vod</t>
+          <t>https://api.ukuapi88.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -11031,11 +11018,13 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>可以爱你吗</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>74</v>
+          <t>谋杀奇闻 第一季</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -11044,7 +11033,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>未测出</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -11056,12 +11045,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TV-无尽资源</t>
+          <t>TV-U酷资源</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://api.wujinapi.me/api.php/provide/vod</t>
+          <t>https://api.ukuapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -11071,11 +11060,13 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>穿越时空甩掉你</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>60</v>
+          <t>谋杀奇闻 第一季</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -11084,7 +11075,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>未测出</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -11096,12 +11087,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TV-wujinapi无尽</t>
+          <t>TV-无尽资源</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://api.wujinapi.cc/api.php/provide/vod</t>
+          <t>https://api.wujinapi.net/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -11115,7 +11106,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>446</v>
+        <v>429</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -11136,12 +11127,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TV-最大点播</t>
+          <t>TV-最大资源</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>http://zuidazy.me/api.php/provide/vod</t>
+          <t>https://api.zuidapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -11155,7 +11146,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>677</v>
+        <v>74</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -11218,12 +11209,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TV-红牛资源</t>
+          <t>TV-丫丫点播</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://www.hongniuzy2.com/api.php/provide/vod</t>
+          <t>https://cj.yayazy.net/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -11233,13 +11224,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>药屋少女的呢喃第三季</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>可以爱你吗</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>684</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -11248,7 +11237,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -11260,12 +11249,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TV-虎牙资源</t>
+          <t>TV-红牛资源</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://www.huyaapi.com/api.php/provide/vod</t>
+          <t>https://www.hongniuzy2.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -11275,7 +11264,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>南瓜头怪2</t>
+          <t>药屋少女的呢喃第三季</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -11302,12 +11291,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TV-无尽资源</t>
+          <t>TV-牛牛点播</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://api.wujinapi.net/api.php/provide/vod</t>
+          <t>https://api.niuniuzy.me/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -11317,11 +11306,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>穿越时空甩掉你</t>
+          <t>可以爱你吗</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>432</v>
+        <v>548</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -11342,12 +11331,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TV-丫丫点播</t>
+          <t>TV-步步高资源</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://cj.yayazy.net/api.php/provide/vod</t>
+          <t>https://api.yparse.com/api/json</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -11357,11 +11346,13 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>可以爱你吗</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>766</v>
+          <t>Word is Bond</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -11370,7 +11361,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>未测出</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -11382,12 +11373,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TV-豪华资源</t>
+          <t>TV-索尼资源</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://hhzyapi.com/api.php/provide/vod</t>
+          <t>https://suoniapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -11397,13 +11388,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>方舟一号第三季</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>改造旧冷库后我住成了大别墅</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>70</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -11412,7 +11401,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -11424,12 +11413,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TV-速博资源</t>
+          <t>TV-虎牙资源</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://subocaiji.com/api.php/provide/vod</t>
+          <t>https://www.huyaapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -11439,7 +11428,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>方舟一号第三季</t>
+          <t>南瓜头怪2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -11466,12 +11455,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TV-金鹰资源</t>
+          <t>TV-速博资源</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://jyzyapi.com/api.php/provide/vod</t>
+          <t>https://subocaiji.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -11508,12 +11497,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TV-量子资源</t>
+          <t>TV-最大点播</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://cj.lziapi.com/api.php/provide/vod</t>
+          <t>http://zuidazy.me/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -11523,13 +11512,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>霹雳英雄战纪之塗附世界</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>可以爱你吗</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>712</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -11538,7 +11525,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -11550,12 +11537,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TV-豆瓣资源</t>
+          <t>TV-暴风资源</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://dbzy.tv/api.php/provide/vod</t>
+          <t>https://bfzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -11565,13 +11552,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>骑士情缘</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>乌鸦俱乐部</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1381</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -11580,24 +11565,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TV-金鹰点播</t>
+          <t>TV-豆瓣资源</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://jinyingzy.com/api.php/provide/vod</t>
+          <t>https://dbzy.tv/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -11607,7 +11592,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>方舟一号第三季</t>
+          <t>骑士情缘</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -11627,19 +11612,19 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TV-索尼资源</t>
+          <t>TV-量子资源</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://suoniapi.com/api.php/provide/vod</t>
+          <t>https://cj.lziapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -11649,11 +11634,13 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>改造旧冷库后我住成了大别墅</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>52</v>
+          <t>霹雳英雄战纪之塗附世界</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -11662,7 +11649,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>未测出</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -11674,12 +11661,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TV-闪电资源</t>
+          <t>TV-金鹰资源</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://sdzyapi.com/api.php/provide/vod</t>
+          <t>https://jyzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -11689,11 +11676,13 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>可以爱你吗</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>728</v>
+          <t>方舟一号第三季</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -11702,7 +11691,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>未测出</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -11714,12 +11703,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TV-牛牛点播</t>
+          <t>TV-金鹰点播</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://api.niuniuzy.me/api.php/provide/vod</t>
+          <t>https://jinyingzy.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -11729,11 +11718,13 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>可以爱你吗</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>731</v>
+          <t>方舟一号第三季</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -11742,7 +11733,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>未测出</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -11754,12 +11745,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TV-非凡资源</t>
+          <t>TV-豪华资源</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://cj.ffzyapi.com/api.php/provide/vod</t>
+          <t>https://hhzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -11769,7 +11760,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>我家的弟弟们真是让您费心了</t>
+          <t>方舟一号第三季</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -11789,19 +11780,19 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TV-暴风资源</t>
+          <t>TV-非凡资源</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://bfzyapi.com/api.php/provide/vod</t>
+          <t>https://cj.ffzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -11811,11 +11802,13 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>乌鸦俱乐部</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>716</v>
+          <t>我家的弟弟们真是让您费心了</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -11824,24 +11817,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>未测出</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TV-1080资源</t>
+          <t>🎬极速资源</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://api.1080zyku.com/inc/api_mac10.php</t>
+          <t>https://jszyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -11851,11 +11844,13 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>冰雪狙击</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>730</v>
+          <t>方舟一号第三季</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -11864,24 +11859,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>未测出</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TV-天涯资源</t>
+          <t>红牛资源3</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://tyyszy.com/api.php/provide/vod</t>
+          <t>https://www.hongniuzy3.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -11891,11 +11886,13 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>改造旧冷库后我住成了大别墅</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>264</v>
+          <t>药屋少女的呢喃第三季</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -11904,24 +11901,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>失败:ReadTimeout</t>
+          <t>未测出</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>🎬极速资源</t>
+          <t>金鹰资源采集网</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://jszyapi.com/api.php/provide/vod</t>
+          <t>https://jyzyapi.com/provide/vod</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -11958,12 +11955,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>金鹰资源采集网</t>
+          <t>非凡影视new</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://jyzyapi.com/provide/vod</t>
+          <t>https://api.ffzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -11973,7 +11970,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>方舟一号第三季</t>
+          <t>我家的弟弟们真是让您费心了</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -11993,19 +11990,19 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>红牛资源3</t>
+          <t>TV-神马云</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://www.hongniuzy3.com/api.php/provide/vod</t>
+          <t>https://api.1080zyku.com/inc/apijson.php</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -12015,13 +12012,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>药屋少女的呢喃第三季</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>绿头苍蝇</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>707</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -12030,7 +12025,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -12042,12 +12037,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>非凡影视new</t>
+          <t>非凡影视</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://api.ffzyapi.com/api.php/provide/vod</t>
+          <t>http://ffzy5.tv/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -12084,12 +12079,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>非凡影视</t>
+          <t>索尼-闪电资源</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>http://ffzy5.tv/api.php/provide/vod</t>
+          <t>https://xsd.sdzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -12099,13 +12094,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>我家的弟弟们真是让您费心了</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>可以爱你吗</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>698</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -12114,24 +12107,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>豪华资源(代理)</t>
+          <t>TV-天涯资源</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://pz.v88.qzz.io/?url=https://hhzyapi.com/api.php/provide/vod</t>
+          <t>https://tyyszy.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -12141,13 +12134,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>方舟一号第三季</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>改造旧冷库后我住成了大别墅</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>251</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -12156,7 +12147,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>失败:ReadTimeout</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -12210,12 +12201,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>索尼-闪电资源</t>
+          <t>豪华资源(代理)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://xsd.sdzyapi.com/api.php/provide/vod</t>
+          <t>https://pz.v88.qzz.io/?url=https://hhzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -12225,11 +12216,13 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>可以爱你吗</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>702</v>
+          <t>方舟一号第三季</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -12238,7 +12231,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>未测出</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -12334,12 +12327,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>TV-神马云</t>
+          <t>🎬快车资源</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://api.1080zyku.com/inc/apijson.php</t>
+          <t>https://caiji.kuaichezy.org/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -12349,11 +12342,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>绿头苍蝇</t>
+          <t>可以爱你吗</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>661</v>
+        <v>701</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -12367,19 +12360,19 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>🎬360 资源</t>
+          <t>TV-1080资源</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://360zyzz.com/api.php/provide/vod</t>
+          <t>https://api.1080zyku.com/inc/api_mac10.php</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -12389,11 +12382,11 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Doctor X：白色黑手党时代</t>
+          <t>冰雪狙击</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>621</v>
+        <v>563</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -12402,7 +12395,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>失败:ConnectionError</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -12414,12 +12407,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>🎬快车资源</t>
+          <t>🎬360 资源</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://caiji.kuaichezy.org/api.php/provide/vod</t>
+          <t>https://360zyzz.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -12429,11 +12422,11 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>可以爱你吗</t>
+          <t>Doctor X：白色黑手党时代</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>733</v>
+        <v>613</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -12447,19 +12440,19 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>艾旦影视(代理)</t>
+          <t>TV-闪电资源</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://pz.v88.qzz.io/?url=https://lovedan.net/api.php/provide/vod</t>
+          <t>https://sdzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -12469,11 +12462,11 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>伟大的长征</t>
+          <t>可以爱你吗</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3497</v>
+        <v>725</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -12482,7 +12475,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>失败:ReadTimeout</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -12534,12 +12527,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>🎬猫眼资源</t>
+          <t>艾旦影视(代理)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://api.maoyanapi.top/api.php/provide/vod</t>
+          <t>https://pz.v88.qzz.io/?url=https://lovedan.net/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -12547,11 +12540,13 @@
           <t>否</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>伟大的长征</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1647</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -12560,24 +12555,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>失败:ReadTimeout</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AV-森林资源</t>
+          <t>🔞森林资源</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://slapibf.com/api.php/provide/vod</t>
+          <t>https://beiyong.slapibf.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -12591,10 +12586,10 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>492</v>
+        <v>538</v>
       </c>
       <c r="F58" t="n">
-        <v>11175</v>
+        <v>11489</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -12610,12 +12605,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>🔞森林资源</t>
+          <t>AV-155资源</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://beiyong.slapibf.com/api.php/provide/vod</t>
+          <t>https://155api.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -12625,14 +12620,14 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>FTHTD-144FALENO学校训练营公共浴池</t>
+          <t>内裤走光后宫学园只有我一MOODYZ大崎広浩治沙</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>559</v>
+        <v>53</v>
       </c>
       <c r="F59" t="n">
-        <v>10991</v>
+        <v>11223</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -12648,12 +12643,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AV-155资源</t>
+          <t>AV-森林资源</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://155api.com/api.php/provide/vod</t>
+          <t>https://slapibf.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -12663,14 +12658,14 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>内裤走光后宫学园只有我一MOODYZ大崎広浩治沙</t>
+          <t>FTHTD-144FALENO学校训练营公共浴池</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>55</v>
+        <v>491</v>
       </c>
       <c r="F60" t="n">
-        <v>9523</v>
+        <v>11051</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -12686,12 +12681,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>🔞杏吧资源</t>
+          <t>AV-辣椒资源</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://xingba222.com/api.php/provide/vod</t>
+          <t>https://apilj.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -12701,14 +12696,14 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">DASS-303 被派遣按摩師 按摩到敏感部位 </t>
+          <t>泌尿科的美人女医8人プラネットプラス伊织凉子,管</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>476</v>
+        <v>4034</v>
       </c>
       <c r="F61" t="n">
-        <v>7670</v>
+        <v>9088</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -12717,19 +12712,19 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>性吧资源</t>
+          <t>🔞杏吧资源</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://xingba111.com/api.php/provide/vod</t>
+          <t>https://xingba222.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -12743,10 +12738,10 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>621</v>
+        <v>456</v>
       </c>
       <c r="F62" t="n">
-        <v>7620</v>
+        <v>7835</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -12781,10 +12776,10 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>624</v>
+        <v>617</v>
       </c>
       <c r="F63" t="n">
-        <v>6948</v>
+        <v>7485</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -12800,12 +12795,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AV-鲨鱼资源</t>
+          <t>性吧资源</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://shayuapi.com/api.php/provide/vod</t>
+          <t>https://xingba111.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -12815,14 +12810,14 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>[瘦猴勾搭] 良家人妻被撩到腿软，眼睛妹妹骚穴求</t>
+          <t xml:space="preserve">DASS-303 被派遣按摩師 按摩到敏感部位 </t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>9382</v>
+        <v>552</v>
       </c>
       <c r="F64" t="n">
-        <v>5048</v>
+        <v>6140</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -12831,19 +12826,19 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AV-辣椒资源</t>
+          <t>AV-乐播资源</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://apilj.com/api.php/provide/vod</t>
+          <t>https://lbapi9.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -12853,14 +12848,14 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>泌尿科的美人女医8人プラネットプラス伊织凉子,管</t>
+          <t>[无码] 苗条人妻床上骚劲爆棚，风骚妩媚狂求内射</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>731</v>
+        <v>873</v>
       </c>
       <c r="F65" t="n">
-        <v>4988</v>
+        <v>3360</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -12869,19 +12864,19 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AV-乐播资源</t>
+          <t>🔞滴滴资源</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://lbapi9.com/api.php/provide/vod</t>
+          <t>https://api.ddapi.cc/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -12891,18 +12886,18 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>[无码] 苗条人妻床上骚劲爆棚，风骚妩媚狂求内射</t>
+          <t>双飞学生妹【蔡萝莉】SM捆绑~白丝足交~强制高潮</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>860</v>
+        <v>375</v>
       </c>
       <c r="F66" t="n">
-        <v>2018</v>
+        <v>838</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>快</t>
+          <t>中</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -12933,10 +12928,10 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="F67" t="n">
-        <v>895</v>
+        <v>805</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -12952,12 +12947,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>🔞滴滴资源</t>
+          <t>AV-JKUN资源</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://api.ddapi.cc/api.php/provide/vod</t>
+          <t>https://jkunzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -12967,14 +12962,14 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>双飞学生妹【蔡萝莉】SM捆绑~白丝足交~强制高潮</t>
+          <t>pacopacomama-072023_880-</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>376</v>
+        <v>58</v>
       </c>
       <c r="F68" t="n">
-        <v>842</v>
+        <v>640</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -12990,12 +12985,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AV-JKUN资源</t>
+          <t>AV-玉兔资源</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://jkunzyapi.com/api.php/provide/vod</t>
+          <t>https://apiyutu.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -13005,14 +13000,14 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>pacopacomama-072023_880-</t>
+          <t>家庭旅馆偷拍性饥渴嫂子偷情小叔子裤子都没脱就主动</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>69</v>
+        <v>380</v>
       </c>
       <c r="F69" t="n">
-        <v>651</v>
+        <v>463</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -13047,7 +13042,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>583</v>
+        <v>231</v>
       </c>
       <c r="F70" t="n">
         <v>453</v>
@@ -13066,12 +13061,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AV-玉兔资源</t>
+          <t>AV-精品资源</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://apiyutu.com/api.php/provide/vod</t>
+          <t>https://www.jingpinx.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -13081,14 +13076,14 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>家庭旅馆偷拍性饥渴嫂子偷情小叔子裤子都没脱就主动</t>
+          <t>純潔的輪舞曲_2</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>372</v>
+        <v>397</v>
       </c>
       <c r="F71" t="n">
-        <v>436</v>
+        <v>413</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -13097,19 +13092,19 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>🔞桃花资源</t>
+          <t>AV-奶香香</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://thzy1.me/api.php/provide/vod</t>
+          <t>https://Naixxzy.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -13119,14 +13114,14 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>[HornyVerse]_Jane_Doe_Fu</t>
+          <t>[换脸]孙彩瑛 热热的骚逼..</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>475</v>
+        <v>558</v>
       </c>
       <c r="F72" t="n">
-        <v>365</v>
+        <v>295</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -13142,12 +13137,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AV-奶香香</t>
+          <t>🔞桃花资源</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://Naixxzy.com/api.php/provide/vod</t>
+          <t>https://thzy1.me/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -13157,14 +13152,14 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>[换脸]孙彩瑛 热热的骚逼..</t>
+          <t>[HornyVerse]_Jane_Doe_Fu</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>557</v>
+        <v>611</v>
       </c>
       <c r="F73" t="n">
-        <v>299</v>
+        <v>254</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -13180,12 +13175,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>🔞小鸡资源</t>
+          <t>🔞-大奶子-</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://api.xiaojizy.live/provide/vod</t>
+          <t>https://apidanaizi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -13195,14 +13190,14 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>李素英合3</t>
+          <t>【最新自录-清纯甜美二次元美少女】白裙情趣装罕见</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>357</v>
+        <v>563</v>
       </c>
       <c r="F74" t="n">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -13211,19 +13206,19 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>🔞-大奶子-</t>
+          <t>AV-奥斯卡资源</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://apidanaizi.com/api.php/provide/vod</t>
+          <t>https://aosikazy.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -13233,14 +13228,14 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>【最新自录-清纯甜美二次元美少女】白裙情趣装罕见</t>
+          <t>真实与后妈乱伦9个月</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>540</v>
+        <v>624</v>
       </c>
       <c r="F75" t="n">
-        <v>227</v>
+        <v>179</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -13249,19 +13244,19 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AV-精品资源</t>
+          <t>🔞小鸡资源</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://www.jingpinx.com/api.php/provide/vod</t>
+          <t>https://api.xiaojizy.live/provide/vod</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -13271,14 +13266,14 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>純潔的輪舞曲_2</t>
+          <t>李素英合3</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>392</v>
+        <v>310</v>
       </c>
       <c r="F76" t="n">
-        <v>198</v>
+        <v>169</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -13294,12 +13289,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AV-奥斯卡资源</t>
+          <t>AV-91麻豆</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://aosikazy.com/api.php/provide/vod</t>
+          <t>https://91md.me/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -13309,14 +13304,14 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>真实与后妈乱伦9个月</t>
+          <t>被老师欺负的黑丝女高-桥本香菜</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>655</v>
+        <v>1196</v>
       </c>
       <c r="F77" t="n">
-        <v>184</v>
+        <v>150</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -13325,7 +13320,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -13351,10 +13346,10 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>934</v>
+        <v>981</v>
       </c>
       <c r="F78" t="n">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -13370,12 +13365,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AV-91麻豆</t>
+          <t>AV-souav资源</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://91md.me/api.php/provide/vod</t>
+          <t>https://api.souavzy.vip/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -13385,18 +13380,20 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>被老师欺负的黑丝女高-桥本香菜</t>
+          <t>白嫩美女月月无套内射初体验</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1092</v>
-      </c>
-      <c r="F79" t="n">
-        <v>115</v>
+        <v>275</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>慢</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -13408,12 +13405,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AV-souav资源</t>
+          <t>黄色资源啊啊</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://api.souavzy.vip/api.php/provide/vod</t>
+          <t>https://hsckzy888.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -13423,11 +13420,13 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>白嫩美女月月无套内射初体验</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>926</v>
+          <t>公共厕所肉便器 我二话 高岭千佳</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -13436,7 +13435,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>未测出</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -13448,12 +13447,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>黄色资源啊啊</t>
+          <t>🔞黄色仓库</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://hsckzy888.com/api.php/provide/vod</t>
+          <t>https://hsckzy.xyz/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -13490,12 +13489,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>🔞黄色仓库</t>
+          <t>🔞souavZY</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://hsckzy.xyz/api.php/provide/vod</t>
+          <t>https://api.souavzyw.net/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -13505,13 +13504,11 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>公共厕所肉便器 我二话 高岭千佳</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>与儿子所在托儿所的巨乳人妻老师缠绵做爱～老师太过</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>456</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -13520,7 +13517,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -13532,12 +13529,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>🔞souavZY</t>
+          <t>🔞色猫资源</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://api.souavzyw.net/api.php/provide/vod</t>
+          <t>https://caiji.semaozy.net/inc/apijson_vod.php/provide/vod</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -13545,13 +13542,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>与儿子所在托儿所的巨乳人妻老师缠绵做爱～老师太过</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>566</v>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -13560,48 +13555,10 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>未测出</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>🔞色猫资源</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>https://caiji.semaozy.net/inc/apijson_vod.php/provide/vod</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>未测出</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
         <is>
           <t>是</t>
         </is>

--- a/output/源清单.xlsx
+++ b/output/源清单.xlsx
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>798</v>
+        <v>1630</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>72</v>
+        <v>251</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2249</v>
+        <v>2071</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>490</v>
+        <v>807</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>280</v>
+        <v>981</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>269</v>
+        <v>454</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>425</v>
+        <v>490</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>429</v>
+        <v>512</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>416</v>
+        <v>611</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>232</v>
+        <v>336</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>266</v>
+        <v>513</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>6811</v>
+        <v>7374</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>382</v>
+        <v>645</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>436</v>
+        <v>649</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>57</v>
+        <v>240</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>415</v>
+        <v>636</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>978</v>
+        <v>841</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>804</v>
+        <v>865</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>719</v>
+        <v>611</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>378</v>
+        <v>423</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>87</v>
+        <v>260</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>138</v>
+        <v>335</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1085</v>
+        <v>1575</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>385</v>
+        <v>432</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>324</v>
+        <v>1567</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>419</v>
+        <v>701</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>791</v>
+        <v>1284</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>59</v>
+        <v>196</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>213</v>
+        <v>471</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1174</v>
+        <v>1154</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>209</v>
+        <v>481</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>636</v>
+        <v>1017</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>255</v>
+        <v>518</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>597</v>
+        <v>618</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>388</v>
+        <v>586</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>538</v>
+        <v>696</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>230</v>
+        <v>550</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>365</v>
+        <v>511</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1863</v>
+        <v>7141</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>832</v>
+        <v>1027</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>824</v>
+        <v>987</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>143</v>
+        <v>90</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="H53" s="2" t="n">
-        <v>1001</v>
+        <v>700</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="H55" s="2" t="n">
-        <v>64</v>
+        <v>548</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         </is>
       </c>
       <c r="H56" s="2" t="n">
-        <v>685</v>
+        <v>777</v>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         </is>
       </c>
       <c r="H57" s="2" t="n">
-        <v>719</v>
+        <v>993</v>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         </is>
       </c>
       <c r="H58" s="2" t="n">
-        <v>576</v>
+        <v>888</v>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="H59" s="2" t="n">
-        <v>2148</v>
+        <v>2925</v>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         </is>
       </c>
       <c r="H60" s="2" t="n">
-        <v>355</v>
+        <v>784</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         </is>
       </c>
       <c r="H61" s="2" t="n">
-        <v>586</v>
+        <v>854</v>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         </is>
       </c>
       <c r="H62" s="2" t="n">
-        <v>385</v>
+        <v>577</v>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         </is>
       </c>
       <c r="H63" s="2" t="n">
-        <v>610</v>
+        <v>743</v>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         </is>
       </c>
       <c r="H64" s="2" t="n">
-        <v>1013</v>
+        <v>1217</v>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="H65" s="2" t="n">
-        <v>394</v>
+        <v>802</v>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         </is>
       </c>
       <c r="H66" s="2" t="n">
-        <v>592</v>
+        <v>1323</v>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="H67" s="2" t="n">
-        <v>497</v>
+        <v>712</v>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
@@ -4748,7 +4748,7 @@
         </is>
       </c>
       <c r="H70" s="2" t="n">
-        <v>802</v>
+        <v>1509</v>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         </is>
       </c>
       <c r="H71" s="2" t="n">
-        <v>985</v>
+        <v>1008</v>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         </is>
       </c>
       <c r="H73" s="2" t="n">
-        <v>455</v>
+        <v>663</v>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>871</v>
+        <v>2523</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>174</v>
+        <v>385</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="H77" s="2" t="n">
-        <v>556</v>
+        <v>773</v>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>573</v>
+        <v>766</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>382</v>
+        <v>588</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>350</v>
+        <v>236</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>495</v>
+        <v>521</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="H87" s="2" t="n">
-        <v>293</v>
+        <v>436</v>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         </is>
       </c>
       <c r="H88" s="2" t="n">
-        <v>611</v>
+        <v>312</v>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         </is>
       </c>
       <c r="H90" s="2" t="n">
-        <v>702</v>
+        <v>807</v>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>723</v>
+        <v>575</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -6013,34 +6013,31 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>分类实测</t>
+          <t>无法探测→按普通处理</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>存活</t>
-        </is>
-      </c>
-      <c r="H92" t="n">
-        <v>2725</v>
+          <t>失活</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>动漫/影视/短剧</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K92" t="n">
-        <v>1</v>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>国产动漫 | 日韩动漫 | 欧美动漫 | 港台动漫 | 动漫电影 | 里番动漫 | 电影 | 连续剧 | 综艺 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 惊悚片 | 家庭片 | 古装片 | 历史片</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
@@ -6085,7 +6082,7 @@
         </is>
       </c>
       <c r="H93" s="2" t="n">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
@@ -6199,7 +6196,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>327</v>
+        <v>696</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -6262,7 +6259,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -6325,7 +6322,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>556</v>
+        <v>620</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -6388,7 +6385,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>366</v>
+        <v>592</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -6451,7 +6448,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>565</v>
+        <v>664</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -6514,7 +6511,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>661</v>
+        <v>933</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -6577,7 +6574,7 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>749</v>
+        <v>737</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -6640,7 +6637,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>105</v>
+        <v>252</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -6703,7 +6700,7 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>2345</v>
+        <v>3411</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -6766,7 +6763,7 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>2722</v>
+        <v>1230</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -6829,7 +6826,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>310</v>
+        <v>420</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -6892,7 +6889,7 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>766</v>
+        <v>825</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -6955,7 +6952,7 @@
         </is>
       </c>
       <c r="H107" s="2" t="n">
-        <v>273</v>
+        <v>393</v>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
@@ -7018,7 +7015,7 @@
         </is>
       </c>
       <c r="H108" s="2" t="n">
-        <v>543</v>
+        <v>801</v>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
@@ -7081,7 +7078,7 @@
         </is>
       </c>
       <c r="H109" s="2" t="n">
-        <v>366</v>
+        <v>707</v>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
@@ -7144,7 +7141,7 @@
         </is>
       </c>
       <c r="H110" s="2" t="n">
-        <v>340</v>
+        <v>371</v>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
@@ -7207,7 +7204,7 @@
         </is>
       </c>
       <c r="H111" s="2" t="n">
-        <v>323</v>
+        <v>546</v>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
@@ -7270,7 +7267,7 @@
         </is>
       </c>
       <c r="H112" s="2" t="n">
-        <v>691</v>
+        <v>1143</v>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
@@ -7333,7 +7330,7 @@
         </is>
       </c>
       <c r="H113" s="2" t="n">
-        <v>496</v>
+        <v>524</v>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
@@ -7396,7 +7393,7 @@
         </is>
       </c>
       <c r="H114" s="2" t="n">
-        <v>447</v>
+        <v>2222</v>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
@@ -7520,7 +7517,7 @@
         </is>
       </c>
       <c r="H116" s="2" t="n">
-        <v>486</v>
+        <v>591</v>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
@@ -7583,7 +7580,7 @@
         </is>
       </c>
       <c r="H117" s="2" t="n">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
@@ -7642,7 +7639,7 @@
         </is>
       </c>
       <c r="H118" s="2" t="n">
-        <v>236</v>
+        <v>709</v>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
@@ -7786,7 +7783,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>72</v>
+        <v>251</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -7909,7 +7906,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1001</v>
+        <v>700</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -8027,7 +8024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>64</v>
+        <v>548</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -8090,7 +8087,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>685</v>
+        <v>777</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -8153,7 +8150,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>719</v>
+        <v>993</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -8216,7 +8213,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>576</v>
+        <v>888</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -8279,7 +8276,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2148</v>
+        <v>2925</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -8342,7 +8339,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>355</v>
+        <v>784</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -8405,7 +8402,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>586</v>
+        <v>854</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -8463,7 +8460,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>385</v>
+        <v>577</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -8526,7 +8523,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>610</v>
+        <v>743</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -8589,7 +8586,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1013</v>
+        <v>1217</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -8647,7 +8644,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>394</v>
+        <v>802</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -8710,7 +8707,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>592</v>
+        <v>1323</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -8768,7 +8765,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>497</v>
+        <v>712</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -8951,7 +8948,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>802</v>
+        <v>1509</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -9014,7 +9011,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>985</v>
+        <v>1008</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -9132,7 +9129,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>455</v>
+        <v>663</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -9240,7 +9237,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>556</v>
+        <v>773</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -9298,7 +9295,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>293</v>
+        <v>436</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -9361,7 +9358,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>611</v>
+        <v>312</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -9419,7 +9416,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>702</v>
+        <v>807</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -9477,7 +9474,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -9535,7 +9532,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>273</v>
+        <v>393</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -9598,7 +9595,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>543</v>
+        <v>801</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -9661,7 +9658,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>366</v>
+        <v>707</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -9724,7 +9721,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>340</v>
+        <v>371</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -9787,7 +9784,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>323</v>
+        <v>546</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -9850,7 +9847,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>691</v>
+        <v>1143</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -9913,7 +9910,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>496</v>
+        <v>524</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -9976,7 +9973,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>447</v>
+        <v>2222</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -10099,7 +10096,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>486</v>
+        <v>591</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -10162,7 +10159,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -10220,7 +10217,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>236</v>
+        <v>709</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -10257,7 +10254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H83"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10305,12 +10302,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>如意资源(代理)</t>
+          <t>🎬猫眼资源</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://pz.v88.qzz.io/?url=https://cj.rycjapi.com/api.php/provide/vod</t>
+          <t>https://api.maoyanapi.top/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -10320,14 +10317,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>霹雳英雄战纪之塗附世界</t>
+          <t>斗罗大陆Ⅱ绝世唐门</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1725</v>
+        <v>732</v>
       </c>
       <c r="F2" t="n">
-        <v>390</v>
+        <v>369</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -10336,19 +10333,19 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TV-360资源</t>
+          <t>如意资源(代理)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://360zy.com/api.php/provide/vod</t>
+          <t>https://pz.v88.qzz.io/?url=https://cj.rycjapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -10358,14 +10355,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>某暗部的少女共栖</t>
+          <t>霹雳英雄战纪之塗附世界</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1354</v>
+        <v>1534</v>
       </c>
       <c r="F3" t="n">
-        <v>266</v>
+        <v>324</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -10374,19 +10371,19 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TV-百度云资源</t>
+          <t>TV-360资源</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://api.apibdzy.com/api.php/provide/vod</t>
+          <t>https://360zy.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -10396,23 +10393,23 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>玄苍路之初入宗门</t>
+          <t>某暗部的少女共栖</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>277</v>
+        <v>1371</v>
       </c>
       <c r="F4" t="n">
-        <v>244</v>
+        <v>267</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>慢</t>
+          <t>中</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -10438,10 +10435,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>556</v>
+        <v>600</v>
       </c>
       <c r="F5" t="n">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -10476,10 +10473,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>527</v>
+        <v>516</v>
       </c>
       <c r="F6" t="n">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -10495,12 +10492,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TV-ikun资源</t>
+          <t>TV-百度云资源</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://ikunzyapi.com/api.php/provide/vod</t>
+          <t>https://api.apibdzy.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -10510,14 +10507,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>某暗部的少女共栖</t>
+          <t>玄苍路之初入宗门</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>548</v>
+        <v>1914</v>
       </c>
       <c r="F7" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -10533,12 +10530,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>🎬猫眼资源</t>
+          <t>TV-ikun资源</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://api.maoyanapi.top/api.php/provide/vod</t>
+          <t>https://ikunzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -10548,14 +10545,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>斗罗大陆Ⅱ绝世唐门</t>
+          <t>某暗部的少女共栖</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>716</v>
+        <v>519</v>
       </c>
       <c r="F8" t="n">
-        <v>145</v>
+        <v>195</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -10564,19 +10561,19 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TV-樱花资源</t>
+          <t>TV-茅台资源</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://m3u8.apiyhzy.com/api.php/provide/vod</t>
+          <t>https://caiji.maotaizy.cc/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -10586,14 +10583,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>裴太太柔弱人设又翻车了</t>
+          <t>梦想改造家 第13季</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>274</v>
+        <v>1540</v>
       </c>
       <c r="F9" t="n">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -10602,19 +10599,19 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TV-茅台资源</t>
+          <t>TV-如意资源</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://caiji.maotaizy.cc/api.php/provide/vod</t>
+          <t>https://cj.rycjapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -10624,14 +10621,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>梦想改造家 第13季</t>
+          <t>霹雳英雄战纪之塗附世界</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1592</v>
+        <v>4567</v>
       </c>
       <c r="F10" t="n">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -10647,12 +10644,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>iqiyi资源</t>
+          <t>TV-樱花资源</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://www.iqiyizyapi.com/api.php/provide/vod</t>
+          <t>https://m3u8.apiyhzy.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -10662,14 +10659,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>万物生灵第七季</t>
+          <t>裴太太柔弱人设又翻车了</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1724</v>
+        <v>113</v>
       </c>
       <c r="F11" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -10678,19 +10675,19 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TV-如意资源</t>
+          <t>TV-魔都资源</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://cj.rycjapi.com/api.php/provide/vod</t>
+          <t>https://www.mdzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -10700,14 +10697,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>霹雳英雄战纪之塗附世界</t>
+          <t>某暗部的少女共栖</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3268</v>
+        <v>974</v>
       </c>
       <c r="F12" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -10716,7 +10713,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -10742,10 +10739,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>719</v>
+        <v>988</v>
       </c>
       <c r="F13" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -10761,12 +10758,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TV-魔都资源</t>
+          <t>TV-U酷资源</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://www.mdzyapi.com/api.php/provide/vod</t>
+          <t>https://api.ukuapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -10776,18 +10773,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>某暗部的少女共栖</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>651</v>
-      </c>
-      <c r="F14" t="n">
-        <v>62</v>
+          <t>谋杀奇闻 第一季</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>慢</t>
+          <t>未测出</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -10799,12 +10800,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TV-新浪点播</t>
+          <t>TV-光速资源</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://api.xinlangapi.com/xinlangapi.php/provide/vod</t>
+          <t>https://api.guangsuapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -10841,12 +10842,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TV-光速资源</t>
+          <t>TV-新浪点播</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://api.guangsuapi.com/api.php/provide/vod</t>
+          <t>https://api.xinlangapi.com/xinlangapi.php/provide/vod</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -10883,12 +10884,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TV-无尽资源</t>
+          <t>TV-U酷资源88</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://api.wujinapi.me/api.php/provide/vod</t>
+          <t>https://api.ukuapi88.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -10898,11 +10899,13 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>穿越时空甩掉你</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>58</v>
+          <t>谋杀奇闻 第一季</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -10911,7 +10914,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>未测出</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -10923,12 +10926,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TV-wujinapi无尽</t>
+          <t>TV-步步高资源</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://api.wujinapi.cc/api.php/provide/vod</t>
+          <t>https://api.yparse.com/api/json</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -10938,11 +10941,13 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>穿越时空甩掉你</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>46</v>
+          <t>Word is Bond</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -10951,7 +10956,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>未测出</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -10963,12 +10968,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TV-无尽资源</t>
+          <t>TV-暴风资源</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://api.wujinapi.com/api.php/provide/vod</t>
+          <t>https://bfzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -10978,11 +10983,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>穿越时空甩掉你</t>
+          <t>乌鸦俱乐部</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>57</v>
+        <v>1025</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -11003,12 +11008,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TV-U酷资源88</t>
+          <t>TV-最大点播</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://api.ukuapi88.com/api.php/provide/vod</t>
+          <t>http://zuidazy.me/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -11018,13 +11023,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>谋杀奇闻 第一季</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>可以爱你吗</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>700</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -11033,7 +11036,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -11045,12 +11048,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TV-U酷资源</t>
+          <t>TV-无尽资源</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://api.ukuapi.com/api.php/provide/vod</t>
+          <t>https://api.wujinapi.me/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -11060,13 +11063,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>谋杀奇闻 第一季</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>穿越时空甩掉你</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -11075,7 +11076,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -11092,7 +11093,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://api.wujinapi.net/api.php/provide/vod</t>
+          <t>https://api.wujinapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -11106,7 +11107,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -11127,12 +11128,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TV-最大资源</t>
+          <t>TV-无尽资源</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://api.zuidapi.com/api.php/provide/vod</t>
+          <t>https://api.wujinapi.net/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -11142,11 +11143,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>可以爱你吗</t>
+          <t>穿越时空甩掉你</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>74</v>
+        <v>440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -11167,12 +11168,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TV-电影天堂资源</t>
+          <t>TV-最大资源</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>http://caiji.dyttzyapi.com/api.php/provide/vod</t>
+          <t>https://api.zuidapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -11182,13 +11183,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>霹雳英雄战纪之塗附世界</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>可以爱你吗</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>59</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -11197,24 +11196,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TV-丫丫点播</t>
+          <t>TV-电影天堂资源</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://cj.yayazy.net/api.php/provide/vod</t>
+          <t>http://caiji.dyttzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -11224,11 +11223,13 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>可以爱你吗</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>684</v>
+          <t>霹雳英雄战纪之塗附世界</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -11237,12 +11238,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>未测出</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -11291,12 +11292,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TV-牛牛点播</t>
+          <t>TV-丫丫点播</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://api.niuniuzy.me/api.php/provide/vod</t>
+          <t>https://cj.yayazy.net/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -11310,7 +11311,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>548</v>
+        <v>751</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -11331,12 +11332,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TV-步步高资源</t>
+          <t>TV-虎牙资源</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://api.yparse.com/api/json</t>
+          <t>https://www.huyaapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -11346,7 +11347,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Word is Bond</t>
+          <t>南瓜头怪2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -11373,12 +11374,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TV-索尼资源</t>
+          <t>TV-豪华资源</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://suoniapi.com/api.php/provide/vod</t>
+          <t>https://hhzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -11388,11 +11389,13 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>改造旧冷库后我住成了大别墅</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>70</v>
+          <t>方舟一号第三季</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -11401,7 +11404,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>未测出</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -11413,12 +11416,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TV-虎牙资源</t>
+          <t>TV-金鹰资源</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://www.huyaapi.com/api.php/provide/vod</t>
+          <t>https://jyzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -11428,7 +11431,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>南瓜头怪2</t>
+          <t>方舟一号第三季</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -11497,12 +11500,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TV-最大点播</t>
+          <t>TV-wujinapi无尽</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>http://zuidazy.me/api.php/provide/vod</t>
+          <t>https://api.wujinapi.cc/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -11512,11 +11515,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>可以爱你吗</t>
+          <t>穿越时空甩掉你</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>712</v>
+        <v>1273</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -11537,12 +11540,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TV-暴风资源</t>
+          <t>TV-豆瓣资源</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://bfzyapi.com/api.php/provide/vod</t>
+          <t>https://dbzy.tv/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -11552,11 +11555,13 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>乌鸦俱乐部</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>1381</v>
+          <t>骑士情缘</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -11565,24 +11570,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>未测出</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TV-豆瓣资源</t>
+          <t>TV-金鹰点播</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://dbzy.tv/api.php/provide/vod</t>
+          <t>https://jinyingzy.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -11592,7 +11597,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>骑士情缘</t>
+          <t>方舟一号第三季</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -11612,7 +11617,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -11661,12 +11666,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TV-金鹰资源</t>
+          <t>TV-牛牛点播</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://jyzyapi.com/api.php/provide/vod</t>
+          <t>https://api.niuniuzy.me/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -11676,13 +11681,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>方舟一号第三季</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>可以爱你吗</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>724</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -11691,7 +11694,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -11703,12 +11706,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TV-金鹰点播</t>
+          <t>TV-非凡资源</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://jinyingzy.com/api.php/provide/vod</t>
+          <t>https://cj.ffzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -11718,7 +11721,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>方舟一号第三季</t>
+          <t>金缮</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -11738,19 +11741,19 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TV-豪华资源</t>
+          <t>TV-闪电资源</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://hhzyapi.com/api.php/provide/vod</t>
+          <t>https://sdzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -11760,13 +11763,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>方舟一号第三季</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>可以爱你吗</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>513</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -11775,7 +11776,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -11787,12 +11788,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TV-非凡资源</t>
+          <t>TV-索尼资源</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://cj.ffzyapi.com/api.php/provide/vod</t>
+          <t>https://suoniapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -11802,13 +11803,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>我家的弟弟们真是让您费心了</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>改造旧冷库后我住成了大别墅</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>75</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -11817,12 +11816,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -11871,12 +11870,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>红牛资源3</t>
+          <t>TV-天涯资源</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://www.hongniuzy3.com/api.php/provide/vod</t>
+          <t>https://tyyszy.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -11886,13 +11885,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>药屋少女的呢喃第三季</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>梦醒时遇见你</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -11901,24 +11898,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>失败:ReadTimeout</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>金鹰资源采集网</t>
+          <t>非凡影视new</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://jyzyapi.com/provide/vod</t>
+          <t>https://api.ffzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -11928,7 +11925,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>方舟一号第三季</t>
+          <t>金缮</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -11948,19 +11945,19 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>非凡影视new</t>
+          <t>红牛资源3</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://api.ffzyapi.com/api.php/provide/vod</t>
+          <t>https://www.hongniuzy3.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -11970,7 +11967,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>我家的弟弟们真是让您费心了</t>
+          <t>药屋少女的呢喃第三季</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -11997,12 +11994,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TV-神马云</t>
+          <t>金鹰资源采集网</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://api.1080zyku.com/inc/apijson.php</t>
+          <t>https://jyzyapi.com/provide/vod</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -12012,11 +12009,13 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>绿头苍蝇</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>707</v>
+          <t>方舟一号第三季</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -12025,24 +12024,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>未测出</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>非凡影视</t>
+          <t>豪华资源(代理)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>http://ffzy5.tv/api.php/provide/vod</t>
+          <t>https://pz.v88.qzz.io/?url=https://hhzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -12052,7 +12051,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>我家的弟弟们真是让您费心了</t>
+          <t>方舟一号第三季</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -12072,19 +12071,19 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>索尼-闪电资源</t>
+          <t>🎬量子资源</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://xsd.sdzyapi.com/api.php/provide/vod</t>
+          <t>https://cj.lzcaiji.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -12094,11 +12093,13 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>可以爱你吗</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>698</v>
+          <t>霹雳英雄战纪之塗附世界</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -12107,7 +12108,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>未测出</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -12119,12 +12120,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TV-天涯资源</t>
+          <t>🎬豆瓣资源</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://tyyszy.com/api.php/provide/vod</t>
+          <t>https://caiji.dbzy5.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -12134,11 +12135,13 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>改造旧冷库后我住成了大别墅</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>251</v>
+          <t>骑士情缘</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -12147,24 +12150,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>失败:ReadTimeout</t>
+          <t>未测出</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>🎬量子资源</t>
+          <t>🎬金鹰点播</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://cj.lzcaiji.com/api.php/provide/vod</t>
+          <t>https://jyzyapi.com/provide/vod/from/jinyingyun/at/json</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -12174,7 +12177,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>霹雳英雄战纪之塗附世界</t>
+          <t>方舟一号第三季</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -12201,12 +12204,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>豪华资源(代理)</t>
+          <t>TV-1080资源</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://pz.v88.qzz.io/?url=https://hhzyapi.com/api.php/provide/vod</t>
+          <t>https://api.1080zyku.com/inc/api_mac10.php</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -12216,13 +12219,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>方舟一号第三季</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>冰雪狙击</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>741</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -12231,24 +12232,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>🎬金鹰点播</t>
+          <t>非凡影视</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://jyzyapi.com/provide/vod/from/jinyingyun/at/json</t>
+          <t>http://ffzy5.tv/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -12258,7 +12259,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>方舟一号第三季</t>
+          <t>金缮</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -12278,19 +12279,19 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>🎬豆瓣资源</t>
+          <t>索尼-闪电资源</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://caiji.dbzy5.com/api.php/provide/vod</t>
+          <t>https://xsd.sdzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -12300,13 +12301,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>骑士情缘</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>可以爱你吗</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>690</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -12315,24 +12314,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>🎬快车资源</t>
+          <t>🎬360 资源</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://caiji.kuaichezy.org/api.php/provide/vod</t>
+          <t>https://360zyzz.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -12342,11 +12341,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>可以爱你吗</t>
+          <t>Doctor X：白色黑手党时代</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>701</v>
+        <v>610</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -12360,19 +12359,19 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TV-1080资源</t>
+          <t>TV-神马云</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://api.1080zyku.com/inc/api_mac10.php</t>
+          <t>https://api.1080zyku.com/inc/apijson.php</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -12382,11 +12381,11 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>冰雪狙击</t>
+          <t>坠落的大力神</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>563</v>
+        <v>867</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -12395,7 +12394,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>失败:ConnectionError</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -12407,12 +12406,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>🎬360 资源</t>
+          <t>🎬快车资源</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://360zyzz.com/api.php/provide/vod</t>
+          <t>https://caiji.kuaichezy.org/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -12422,11 +12421,11 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Doctor X：白色黑手党时代</t>
+          <t>可以爱你吗</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>613</v>
+        <v>671</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -12440,19 +12439,19 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TV-闪电资源</t>
+          <t>艾旦影视(代理)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://sdzyapi.com/api.php/provide/vod</t>
+          <t>https://pz.v88.qzz.io/?url=https://lovedan.net/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -12462,11 +12461,11 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>可以爱你吗</t>
+          <t>伟大的长征</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>725</v>
+        <v>1411</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -12475,7 +12474,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>失败:ReadTimeout</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -12502,11 +12501,11 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>绿头苍蝇</t>
+          <t>坠落的大力神</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>867</v>
+        <v>2387</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -12527,35 +12526,33 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>艾旦影视(代理)</t>
+          <t>AV-森林资源</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://pz.v88.qzz.io/?url=https://lovedan.net/api.php/provide/vod</t>
+          <t>https://slapibf.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>伟大的长征</t>
+          <t>FTHTD-144FALENO学校训练营公共浴池</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1647</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>496</v>
+      </c>
+      <c r="F57" t="n">
+        <v>11334</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>快</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -12567,12 +12564,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>🔞森林资源</t>
+          <t>AV-155资源</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://beiyong.slapibf.com/api.php/provide/vod</t>
+          <t>https://155api.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -12582,14 +12579,14 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>FTHTD-144FALENO学校训练营公共浴池</t>
+          <t>内裤走光后宫学园只有我一MOODYZ大崎広浩治沙</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>538</v>
+        <v>52</v>
       </c>
       <c r="F58" t="n">
-        <v>11489</v>
+        <v>10787</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -12605,12 +12602,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AV-155资源</t>
+          <t>AV-辣椒资源</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://155api.com/api.php/provide/vod</t>
+          <t>https://apilj.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -12620,14 +12617,14 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>内裤走光后宫学园只有我一MOODYZ大崎広浩治沙</t>
+          <t>泌尿科的美人女医8人プラネットプラス伊织凉子,管</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>53</v>
+        <v>706</v>
       </c>
       <c r="F59" t="n">
-        <v>11223</v>
+        <v>8946</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -12636,19 +12633,19 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AV-森林资源</t>
+          <t>🔞森林资源</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://slapibf.com/api.php/provide/vod</t>
+          <t>https://beiyong.slapibf.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -12662,10 +12659,10 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="F60" t="n">
-        <v>11051</v>
+        <v>8144</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -12681,12 +12678,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AV-辣椒资源</t>
+          <t>性吧资源</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://apilj.com/api.php/provide/vod</t>
+          <t>https://xingba111.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -12696,14 +12693,14 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>泌尿科的美人女医8人プラネットプラス伊织凉子,管</t>
+          <t xml:space="preserve">DASS-303 被派遣按摩師 按摩到敏感部位 </t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4034</v>
+        <v>575</v>
       </c>
       <c r="F61" t="n">
-        <v>9088</v>
+        <v>7745</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -12712,7 +12709,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -12738,10 +12735,10 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>456</v>
+        <v>489</v>
       </c>
       <c r="F62" t="n">
-        <v>7835</v>
+        <v>7632</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -12776,10 +12773,10 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>617</v>
+        <v>594</v>
       </c>
       <c r="F63" t="n">
-        <v>7485</v>
+        <v>7439</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -12795,12 +12792,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>性吧资源</t>
+          <t>AV-乐播资源</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://xingba111.com/api.php/provide/vod</t>
+          <t>https://lbapi9.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -12810,14 +12807,14 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">DASS-303 被派遣按摩師 按摩到敏感部位 </t>
+          <t>[无码] 苗条人妻床上骚劲爆棚，风骚妩媚狂求内射</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>552</v>
+        <v>915</v>
       </c>
       <c r="F64" t="n">
-        <v>6140</v>
+        <v>4941</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -12833,12 +12830,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AV-乐播资源</t>
+          <t>🔞滴滴资源</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://lbapi9.com/api.php/provide/vod</t>
+          <t>https://api.ddapi.cc/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -12848,18 +12845,18 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>[无码] 苗条人妻床上骚劲爆棚，风骚妩媚狂求内射</t>
+          <t>双飞学生妹【蔡萝莉】SM捆绑~白丝足交~强制高潮</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>873</v>
+        <v>324</v>
       </c>
       <c r="F65" t="n">
-        <v>3360</v>
+        <v>885</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>快</t>
+          <t>中</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -12871,12 +12868,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>🔞滴滴资源</t>
+          <t>🔞豆豆资源</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://api.ddapi.cc/api.php/provide/vod</t>
+          <t>https://api.douapi.cc/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -12886,14 +12883,14 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>双飞学生妹【蔡萝莉】SM捆绑~白丝足交~强制高潮</t>
+          <t>美腿玉足控韩国水娃【Hella_cute】顶级吊</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>375</v>
+        <v>343</v>
       </c>
       <c r="F66" t="n">
-        <v>838</v>
+        <v>855</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -12909,12 +12906,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>🔞豆豆资源</t>
+          <t>AV-JKUN资源</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://api.douapi.cc/api.php/provide/vod</t>
+          <t>https://jkunzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -12924,14 +12921,14 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>美腿玉足控韩国水娃【Hella_cute】顶级吊</t>
+          <t>pacopacomama-072023_880-</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>334</v>
+        <v>262</v>
       </c>
       <c r="F67" t="n">
-        <v>805</v>
+        <v>639</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -12947,12 +12944,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AV-JKUN资源</t>
+          <t>AV-老色逼资源</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://jkunzyapi.com/api.php/provide/vod</t>
+          <t>https://apilsbzy1.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -12962,14 +12959,14 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>pacopacomama-072023_880-</t>
+          <t>家庭旅馆偷拍性饥渴嫂子偷情小叔子裤子都没脱就主动</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>58</v>
+        <v>502</v>
       </c>
       <c r="F68" t="n">
-        <v>640</v>
+        <v>442</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -13004,10 +13001,10 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="F69" t="n">
-        <v>463</v>
+        <v>442</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -13023,12 +13020,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AV-老色逼资源</t>
+          <t>🔞桃花资源</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://apilsbzy1.com/api.php/provide/vod</t>
+          <t>https://thzy1.me/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -13038,14 +13035,14 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>家庭旅馆偷拍性饥渴嫂子偷情小叔子裤子都没脱就主动</t>
+          <t>[HornyVerse]_Jane_Doe_Fu</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>231</v>
+        <v>462</v>
       </c>
       <c r="F70" t="n">
-        <v>453</v>
+        <v>375</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -13054,19 +13051,19 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AV-精品资源</t>
+          <t>AV-奶香香</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://www.jingpinx.com/api.php/provide/vod</t>
+          <t>https://Naixxzy.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -13076,14 +13073,14 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>純潔的輪舞曲_2</t>
+          <t>[换脸]孙彩瑛 热热的骚逼..</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>397</v>
+        <v>903</v>
       </c>
       <c r="F71" t="n">
-        <v>413</v>
+        <v>335</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -13099,12 +13096,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AV-奶香香</t>
+          <t>AV-精品资源</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://Naixxzy.com/api.php/provide/vod</t>
+          <t>https://www.jingpinx.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -13114,18 +13111,18 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>[换脸]孙彩瑛 热热的骚逼..</t>
+          <t>純潔的輪舞曲_2</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>558</v>
+        <v>480</v>
       </c>
       <c r="F72" t="n">
-        <v>295</v>
+        <v>238</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>慢</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -13137,12 +13134,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>🔞桃花资源</t>
+          <t>🔞-大奶子-</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://thzy1.me/api.php/provide/vod</t>
+          <t>https://apidanaizi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -13152,35 +13149,35 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>[HornyVerse]_Jane_Doe_Fu</t>
+          <t>【最新自录-清纯甜美二次元美少女】白裙情趣装罕见</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>611</v>
+        <v>542</v>
       </c>
       <c r="F73" t="n">
-        <v>254</v>
+        <v>222</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>慢</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>🔞-大奶子-</t>
+          <t>AV-奥斯卡资源</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://apidanaizi.com/api.php/provide/vod</t>
+          <t>https://aosikazy.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -13190,14 +13187,14 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>【最新自录-清纯甜美二次元美少女】白裙情趣装罕见</t>
+          <t>真实与后妈乱伦9个月</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>563</v>
+        <v>603</v>
       </c>
       <c r="F74" t="n">
-        <v>229</v>
+        <v>173</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -13206,19 +13203,19 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AV-奥斯卡资源</t>
+          <t>🔞小鸡资源</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://aosikazy.com/api.php/provide/vod</t>
+          <t>https://api.xiaojizy.live/provide/vod</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -13228,14 +13225,14 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>真实与后妈乱伦9个月</t>
+          <t>李素英合3</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>624</v>
+        <v>308</v>
       </c>
       <c r="F75" t="n">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -13251,12 +13248,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>🔞小鸡资源</t>
+          <t>🔞黑料资源</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://api.xiaojizy.live/provide/vod</t>
+          <t>https://www.heiliaozyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -13266,14 +13263,14 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>李素英合3</t>
+          <t>绿播福利姬女神下海硬控你十分钟一看就高端货超美脸</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>310</v>
+        <v>929</v>
       </c>
       <c r="F76" t="n">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -13308,10 +13305,10 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1196</v>
+        <v>1284</v>
       </c>
       <c r="F77" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -13327,12 +13324,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>🔞黑料资源</t>
+          <t>AV-souav资源</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://www.heiliaozyapi.com/api.php/provide/vod</t>
+          <t>https://api.souavzy.vip/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -13342,35 +13339,37 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>绿播福利姬女神下海硬控你十分钟一看就高端货超美脸</t>
+          <t>白嫩美女月月无套内射初体验</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>981</v>
-      </c>
-      <c r="F78" t="n">
-        <v>118</v>
+        <v>708</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>慢</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AV-souav资源</t>
+          <t>黄色资源啊啊</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://api.souavzy.vip/api.php/provide/vod</t>
+          <t>https://hsckzy888.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -13380,11 +13379,13 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>白嫩美女月月无套内射初体验</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>275</v>
+          <t>公共厕所肉便器 我二话 高岭千佳</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -13393,7 +13394,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>未测出</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -13405,12 +13406,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>黄色资源啊啊</t>
+          <t>🔞黄色仓库</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://hsckzy888.com/api.php/provide/vod</t>
+          <t>https://hsckzy.xyz/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -13447,12 +13448,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>🔞黄色仓库</t>
+          <t>🔞色猫资源</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://hsckzy.xyz/api.php/provide/vod</t>
+          <t>https://caiji.semaozy.net/inc/apijson_vod.php/provide/vod</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -13460,11 +13461,7 @@
           <t>是</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>公共厕所肉便器 我二话 高岭千佳</t>
-        </is>
-      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -13508,7 +13505,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>456</v>
+        <v>475</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -13521,44 +13518,6 @@
         </is>
       </c>
       <c r="H82" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>🔞色猫资源</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>https://caiji.semaozy.net/inc/apijson_vod.php/provide/vod</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>未测出</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
         <is>
           <t>是</t>
         </is>

--- a/output/源清单.xlsx
+++ b/output/源清单.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M118"/>
+  <dimension ref="A1:N118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.6" customWidth="1" min="1" max="1"/>
@@ -445,8 +445,9 @@
     <col width="12.8" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="60" customWidth="1" min="12" max="12"/>
-    <col width="52.8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="52.8" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -507,10 +508,15 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>归属</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>分类名</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
@@ -553,7 +559,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1630</v>
+        <v>3727</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -570,10 +576,15 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 台湾剧 | 韩国剧 | 欧美剧 | 香港剧 | 泰国剧 | 日本剧 | 福利 | 记录片</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置</t>
         </is>
@@ -616,7 +627,7 @@
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>251</v>
+        <v>291</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -633,10 +644,15 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
           <t>无码专区 | 麻豆传媒 | 制服诱惑 | 三级伦理 | AI换脸 | 中文字幕 | 卡通动漫 | 欧美系列 | 美女主播 | 国产自拍 | 熟女人妻 | 萝莉少女 | 女同性爱 | 多人群交 | 美乳巨乳 | 强奸乱伦 | 生活都市 | 不偷恋情 | 学生校园 | 人妻熟女</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -679,7 +695,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2071</v>
+        <v>2150</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -696,10 +712,15 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 伦理片 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 韩国剧 | 欧美剧 | 体育 | NBA | 惊悚片 | 家庭篇</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,cmliu配置</t>
         </is>
@@ -742,7 +763,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>807</v>
+        <v>523</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -759,10 +780,15 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
           <t>伦理片 | 教程</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -805,7 +831,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>981</v>
+        <v>937</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -822,10 +848,15 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 港澳剧 | 日剧 | 欧美剧 | 动漫电影 | 台湾剧 | 韩剧 | 泰剧 | 记录片</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库3,cmliu配置</t>
         </is>
@@ -868,7 +899,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>454</v>
+        <v>798</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -885,10 +916,15 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 港澳剧 | 日剧 | 欧美剧 | 动漫电影 | 台湾剧 | 韩剧 | 泰剧 | 记录片</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置,sp696</t>
         </is>
@@ -931,7 +967,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>490</v>
+        <v>633</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -948,10 +984,15 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 伦理片 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 惊悚片 | 家庭片 | 古装片 | 历史片 | 悬疑片 | 犯罪片 | 灾难片 | 记录片</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -989,7 +1030,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>512</v>
+        <v>540</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1006,10 +1047,15 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 资讯 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 台湾剧 | 美国剧 | 公告 | 头条 | 伦理片 | 纪录片</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置</t>
         </is>
@@ -1052,7 +1098,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>611</v>
+        <v>637</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1069,10 +1115,15 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 欧美剧 | 韩剧 | 日剧 | 港剧 | 台剧 | 泰剧 | 纪录片 | 海外剧</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置,sp696</t>
         </is>
@@ -1115,7 +1166,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>336</v>
+        <v>443</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1132,10 +1183,15 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 剧情片 | 恐怖片 | 战争片 | 大陆剧 | 欧美剧 | 港澳剧 | 韩剧 | 动漫电影 | 日剧 | 台湾剧 | 泰剧 | 记录片</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置,sp696</t>
         </is>
@@ -1178,7 +1234,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1193,7 +1249,12 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -1248,7 +1309,12 @@
       <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -1291,7 +1357,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1306,7 +1372,12 @@
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,sp696</t>
         </is>
@@ -1349,7 +1420,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>513</v>
+        <v>491</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1366,10 +1437,15 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 欧美剧 | 韩国剧 | 日本剧 | 港台剧 | 台湾剧 | 泰国剧 | 纪录片 | 海外剧</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,cmliu配置</t>
         </is>
@@ -1412,7 +1488,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>7374</v>
+        <v>5967</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1429,10 +1505,15 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
           <t>电影片 | 连续剧 | 综艺片 | 动漫片 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 韩国剧 | 欧美剧 | 记录片 | 台湾剧 | 日本剧 | 海外剧 | 泰国剧</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,sp696</t>
         </is>
@@ -1492,7 +1573,12 @@
       <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版</t>
         </is>
@@ -1535,7 +1621,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>645</v>
+        <v>500</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1552,10 +1638,15 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
           <t>电影 | 电视剧 | 动漫 | 综艺 | 纪录片 | 动作片 | 爱情片 | 科幻片 | 战争片 | 剧情片 | 恐怖片 | 喜剧片 | 大陆剧 | 港澳剧 | 台湾剧 | 欧美剧 | 动画片 | 韩剧 | 日剧 | 泰剧</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -1598,7 +1689,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>649</v>
+        <v>693</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1615,10 +1706,15 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 资讯 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 台湾剧 | 美国剧 | 公告 | 头条 | 伦理片 | 纪录片</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置,sp696</t>
         </is>
@@ -1661,7 +1757,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>240</v>
+        <v>67</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1678,10 +1774,15 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 资讯 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 台湾剧 | 美国剧 | 公告 | 头条 | 伦理片 | 纪录片</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -1719,7 +1820,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>636</v>
+        <v>418</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1736,10 +1837,15 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 资讯 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 台湾剧 | 美国剧 | 公告 | 头条 | 伦理片 | 纪录片</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置</t>
         </is>
@@ -1782,7 +1888,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>841</v>
+        <v>806</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1797,7 +1903,12 @@
       <c r="K22" t="n">
         <v>0</v>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,sp696</t>
         </is>
@@ -1840,7 +1951,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>865</v>
+        <v>678</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1855,7 +1966,12 @@
       <c r="K23" t="n">
         <v>0</v>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -1898,7 +2014,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>611</v>
+        <v>509</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1915,10 +2031,15 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
           <t>电影片 | 动作片 | 喜剧片 | 恐怖片 | 科幻片 | 爱情片 | 剧情片 | 战争片 | 纪录片 | 理论片 | 连续剧 | 国产剧 | 欧美剧 | 香港剧 | 韩国剧 | 台湾剧 | 日本剧 | 海外剧 | 泰国剧 | 动漫片</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -1961,7 +2082,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>423</v>
+        <v>402</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1978,10 +2099,15 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 欧美剧 | 韩剧 | 日剧 | 港剧 | 台剧 | 泰剧 | 纪录片 | 海外剧</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置,sp696</t>
         </is>
@@ -2024,7 +2150,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>260</v>
+        <v>284</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2041,10 +2167,15 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 欧美剧 | 韩剧 | 日剧 | 港剧 | 台剧 | 泰剧 | 纪录片 | 海外剧</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -2087,7 +2218,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>335</v>
+        <v>354</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2104,10 +2235,15 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 资讯 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 台湾剧 | 韩国剧 | 公告 | 头条 | 犯罪片 | 纪录片</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -2145,7 +2281,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1575</v>
+        <v>1685</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2162,10 +2298,15 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
           <t>动漫 | 综艺 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 战争片 | 国产剧 | 香港剧 | 欧美剧 | 日本剧 | 海外剧 | 台湾剧 | 韩国剧 | 泰国剧 | 剧情片 | 纪录片 | 动画片 | 微电影</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -2208,7 +2349,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2225,10 +2366,15 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 欧美剧 | 韩剧 | 日剧 | 港剧 | 台剧 | 泰剧 | 纪录片 | 海外剧</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置</t>
         </is>
@@ -2271,7 +2417,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1567</v>
+        <v>789</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2288,10 +2434,15 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
           <t>电影片 | 连续剧 | 综艺片 | 动漫片 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 韩国剧 | 欧美剧 | 记录片 | 台湾剧 | 日本剧 | 海外剧 | 泰国剧</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -2351,8 +2502,13 @@
       <c r="K31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="2" t="inlineStr">
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -2395,7 +2551,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>701</v>
+        <v>550</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2412,10 +2568,15 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 大陆剧 | 欧美剧 | 韩剧 | 日剧 | 港澳剧 | 台湾剧 | 泰剧 | 纪录片 | 其他剧</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库3,cmliu配置</t>
         </is>
@@ -2458,7 +2619,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1284</v>
+        <v>725</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2475,10 +2636,15 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 台湾剧 | 韩国剧 | 欧美剧 | 香港剧 | 泰国剧 | 日本剧 | 福利 | 记录片</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库3,cmliu配置</t>
         </is>
@@ -2521,7 +2687,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>196</v>
+        <v>290</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2538,10 +2704,15 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 欧美剧 | 韩剧 | 日剧 | 港剧 | 台剧 | 泰剧 | 纪录片 | 海外剧</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置,sp696</t>
         </is>
@@ -2584,7 +2755,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2601,10 +2772,15 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 港澳剧 | 日剧 | 欧美剧 | 台湾剧 | 泰剧 | 韩剧 | 纪录片 | 动漫电影</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -2647,7 +2823,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1154</v>
+        <v>1244</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2664,10 +2840,15 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
           <t>电影 | 连续剧 | 综艺片 | 动漫 | 纪录片 | 动作片 | 爱情片 | 喜剧片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 欧美剧 | 韩剧 | 动漫电影 | 泰国剧 | 日本剧 | 台湾剧</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,sp696</t>
         </is>
@@ -2710,7 +2891,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>481</v>
+        <v>684</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2727,10 +2908,15 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
           <t>电视剧 | 电影 | 欧美剧 | 香港剧 | 韩剧 | 日剧 | 马泰剧 | 伦理片 | 动作片 | 爱情片 | 喜剧片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 记录片 | 动漫 | 内地剧 | 动画片 | 中国动漫</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置,sp696</t>
         </is>
@@ -2790,7 +2976,12 @@
       <c r="K38" t="n">
         <v>0</v>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -2833,7 +3024,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1017</v>
+        <v>914</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2850,10 +3041,15 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
           <t>电影 | 连续剧 | 综艺片 | 动漫 | 纪录片 | 动作片 | 爱情片 | 喜剧片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 欧美剧 | 韩剧 | 动漫电影 | 泰国剧 | 日本剧 | 台湾剧</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,cmliu配置</t>
         </is>
@@ -2896,7 +3092,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>518</v>
+        <v>386</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2913,10 +3109,15 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
           <t>电视剧 | 电影 | 欧美剧 | 香港剧 | 韩剧 | 日剧 | 马泰剧 | 伦理片 | 动作片 | 爱情片 | 喜剧片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 记录片 | 动漫 | 内地剧 | 动画片 | 中国动漫</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -2959,7 +3160,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>618</v>
+        <v>806</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2976,10 +3177,15 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
           <t>电影 | 电视剧 | 动漫 | 综艺 | 纪录片 | 动作片 | 爱情片 | 科幻片 | 战争片 | 剧情片 | 恐怖片 | 喜剧片 | 动漫电影 | 大陆剧 | 台湾剧 | 韩剧 | 美剧 | 港澳剧 | 日剧 | 泰剧</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -3022,7 +3228,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>586</v>
+        <v>614</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -3039,10 +3245,15 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
           <t>电影片 | 连续剧 | 综艺片 | 动漫片 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 韩国剧 | 欧美剧 | 记录片 | 台湾剧 | 日本剧 | 海外剧 | 泰国剧</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -3085,7 +3296,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>696</v>
+        <v>720</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3102,10 +3313,15 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
           <t>电视剧 | 电影 | 欧美剧 | 香港剧 | 韩剧 | 日剧 | 马泰剧 | 伦理片 | 动作片 | 爱情片 | 喜剧片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 记录片 | 动漫 | 内地剧 | 动画片 | 中国动漫</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -3148,7 +3364,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>550</v>
+        <v>524</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3165,10 +3381,15 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
           <t>电视剧 | 电影 | 欧美剧 | 香港剧 | 韩剧 | 日剧 | 马泰剧 | 伦理片 | 动作片 | 爱情片 | 喜剧片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 记录片 | 动漫 | 内地剧 | 动画片 | 中国动漫</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置</t>
         </is>
@@ -3211,7 +3432,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>511</v>
+        <v>530</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3228,10 +3449,15 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 欧美剧 | 韩剧 | 日剧 | 港剧 | 台剧 | 泰剧 | 纪录片 | 海外剧</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置</t>
         </is>
@@ -3265,36 +3491,36 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>分类实测</t>
+          <t>无法探测→按普通处理</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>存活</t>
+          <t>存活/非标准</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>7141</v>
+        <v>2388</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>动漫/影视/短剧</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>电影片 | 连续剧 | 综艺片 | 动漫片 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 韩国剧 | 欧美剧 | 记录片 | 台湾剧 | 日本剧 | 海外剧 | 泰国剧</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -3354,7 +3580,12 @@
       <c r="K47" t="n">
         <v>0</v>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -3414,7 +3645,12 @@
       <c r="K48" t="n">
         <v>0</v>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3</t>
         </is>
@@ -3457,7 +3693,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1027</v>
+        <v>628</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3474,10 +3710,15 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
           <t>国产动漫 | 日韩动漫 | 欧美动漫 | 港台动漫 | 动漫电影 | 里番动漫 | 电影 | 连续剧 | 综艺 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 惊悚片 | 家庭片 | 古装片 | 历史片</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置,sp696</t>
         </is>
@@ -3520,7 +3761,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>987</v>
+        <v>956</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3537,10 +3778,15 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
           <t>国产动漫 | 日韩动漫 | 欧美动漫 | 港台动漫 | 动漫电影 | 里番动漫 | 电影 | 连续剧 | 综艺 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 惊悚片 | 家庭片 | 古装片 | 历史片</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -3583,7 +3829,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>90</v>
+        <v>154</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3598,7 +3844,12 @@
       <c r="K51" t="n">
         <v>0</v>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版</t>
         </is>
@@ -3641,7 +3892,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>105</v>
+        <v>171</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3656,7 +3907,12 @@
       <c r="K52" t="n">
         <v>0</v>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -3699,7 +3955,7 @@
         </is>
       </c>
       <c r="H53" s="2" t="n">
-        <v>700</v>
+        <v>1060</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
@@ -3716,10 +3972,15 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
           <t>麻豆视频 | 91制片厂 | 天美传媒 | 蜜桃传媒 | 皇家华人 | 星空传媒 | 精东影业 | 海角社区 | 成人头条 | 乌鸦传媒 | 兔子先生 | 杏吧原创 | 玩偶姐姐 | mini传媒 | 大象传媒 | 91视频 | PsychoPorn | 糖心Vlog | 萝莉社 | 性视界</t>
         </is>
       </c>
-      <c r="M53" s="2" t="inlineStr">
+      <c r="N53" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -3775,8 +4036,13 @@
       <c r="K54" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L54" s="2" t="inlineStr"/>
-      <c r="M54" s="2" t="inlineStr">
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -3819,7 +4085,7 @@
         </is>
       </c>
       <c r="H55" s="2" t="n">
-        <v>548</v>
+        <v>195</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
@@ -3836,10 +4102,15 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
           <t>中文字幕 | 日本有码 | 日本无码 | AV解说 | cosplay | 都市激情 | 校园情事 | 人妻纵情 | 风俗伦理 | 另类小说 | 武侠古典 | 长篇连载 | 黑丝诱惑 | SWAG | 自拍偷拍 | 激情动漫 | 网红主播 | 探花系列 | 三级伦理 | VR视角</t>
         </is>
       </c>
-      <c r="M55" s="2" t="inlineStr">
+      <c r="N55" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -3882,7 +4153,7 @@
         </is>
       </c>
       <c r="H56" s="2" t="n">
-        <v>777</v>
+        <v>793</v>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
@@ -3899,10 +4170,15 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
           <t>中文传媒 | 国产 | 欧美AV | 日本AV | 传媒-麻豆传媒 | 传媒-精东影业 | 传媒-蜜桃传媒 | 传媒-果冻传媒 | 传媒-星空无限传媒 | 传媒-SA国际传媒 | 传媒-性视界传媒 | 国产-自拍 | 国产-偷拍 | 国产-探花 | 国产-主播 | 传媒-天美传媒 | 欧美-高清无码 | 欧美-高清有码 | 日本-中文字幕 | 日本-无码流出</t>
         </is>
       </c>
-      <c r="M56" s="2" t="inlineStr">
+      <c r="N56" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -3945,7 +4221,7 @@
         </is>
       </c>
       <c r="H57" s="2" t="n">
-        <v>993</v>
+        <v>947</v>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
@@ -3962,10 +4238,15 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
           <t>亚洲情色 | 国产主播 | 国产自拍 | 无码专区 | 欧美性爱 | 熟女人妻 | 强奸乱伦 | 巨乳美乳 | 中文字幕 | 制服诱惑 | 女同性恋 | 卡通动画 | 视频伦理 | 少女萝莉 | 重口色情 | 人兽性交 | 福利姬</t>
         </is>
       </c>
-      <c r="M57" s="2" t="inlineStr">
+      <c r="N57" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -4008,7 +4289,7 @@
         </is>
       </c>
       <c r="H58" s="2" t="n">
-        <v>888</v>
+        <v>1028</v>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
@@ -4025,10 +4306,15 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
           <t>国产视频 | 中文字幕 | 国产传媒 | 日本有码 | 日本无码 | 欧美无码 | 强奸乱伦 | 制服诱惑 | 国产主播 | 激情动漫 | 明星换脸 | 抖阴视频 | 女优明星 | 视频一区 | 视频二区 | 网曝黑料 | 视频三区 | 伦理三级 | AV解说 | SM调教</t>
         </is>
       </c>
-      <c r="M58" s="2" t="inlineStr">
+      <c r="N58" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -4071,7 +4357,7 @@
         </is>
       </c>
       <c r="H59" s="2" t="n">
-        <v>2925</v>
+        <v>1013</v>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
@@ -4088,10 +4374,15 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
           <t>精品国产 | 精品日韩 | 精品综合 | 精品小说 | 精品美图 | 国产自拍 | 主播诱惑 | 探花约炮 | 偷拍偷窥 | 网曝吃瓜 | 抖阴短片 | 传媒剧情 | 日韩主播 | 日韩无码 | 中文字幕 | AV解说 | 换脸明星 | 强奸乱伦 | 女优明星 | 欧美激情</t>
         </is>
       </c>
-      <c r="M59" s="2" t="inlineStr">
+      <c r="N59" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -4134,7 +4425,7 @@
         </is>
       </c>
       <c r="H60" s="2" t="n">
-        <v>784</v>
+        <v>753</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
@@ -4151,10 +4442,15 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
           <t>精品推荐 | 国产色情 | 主播直播 | 亚洲无码 | 亚洲有码 | 中文字幕 | 巨乳美乳 | 人妻熟女 | 强奸乱伦 | 欧美精品 | 萝莉少女 | 伦理三级 | 成人动漫 | 自拍偷拍 | 制服丝袜 | 口交颜射 | 日本精品 | Cosplay | 素人自拍 | 台湾辣妹</t>
         </is>
       </c>
-      <c r="M60" s="2" t="inlineStr">
+      <c r="N60" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置</t>
         </is>
@@ -4197,7 +4493,7 @@
         </is>
       </c>
       <c r="H61" s="2" t="n">
-        <v>854</v>
+        <v>1266</v>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
@@ -4212,8 +4508,13 @@
       <c r="K61" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L61" s="2" t="inlineStr"/>
-      <c r="M61" s="2" t="inlineStr">
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -4256,7 +4557,7 @@
         </is>
       </c>
       <c r="H62" s="2" t="n">
-        <v>577</v>
+        <v>602</v>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
@@ -4273,10 +4574,15 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
           <t>精品推荐 | 国产精品 | 主播秀色 | 日本有码 | 日本无码 | 中文字幕 | 童颜巨乳 | 性感人妻 | 强奸乱伦 | 欧美情色 | 三级伦理 | 卡通动漫 | 丝袜OL | 自拍偷拍 | 日本片商 | 剧情介绍 | 网曝系列 | 麻豆传媒 | 明星换脸 | 国产乱伦</t>
         </is>
       </c>
-      <c r="M62" s="2" t="inlineStr">
+      <c r="N62" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -4319,7 +4625,7 @@
         </is>
       </c>
       <c r="H63" s="2" t="n">
-        <v>743</v>
+        <v>726</v>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
@@ -4336,10 +4642,15 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
           <t>制服丝袜 | 群交淫乱 | 无码专区 | 偷拍自拍 | 卡通动漫 | 中文字幕 | 欧美性爱 | 巨乳美乳 | 国产裸聊 | 国产自拍 | 国产盗摄 | 伦理三级 | 女同性恋 | 少女萝莉 | 人妖系列 | 虚拟VR | 亚州图片 | 欧美图片 | 美腿丝袜 | 网友自拍</t>
         </is>
       </c>
-      <c r="M63" s="2" t="inlineStr">
+      <c r="N63" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -4382,7 +4693,7 @@
         </is>
       </c>
       <c r="H64" s="2" t="n">
-        <v>1217</v>
+        <v>1038</v>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
@@ -4397,8 +4708,13 @@
       <c r="K64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L64" s="2" t="inlineStr"/>
-      <c r="M64" s="2" t="inlineStr">
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -4441,7 +4757,7 @@
         </is>
       </c>
       <c r="H65" s="2" t="n">
-        <v>802</v>
+        <v>594</v>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
@@ -4458,10 +4774,15 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
           <t>国产 | 日本 | 欧美 | 动漫 | 偷拍自拍 | 国产大制作 | 乱伦毁三观 | 嫖妓全过程 | 淫乱学生妹 | 黑料不打烊 | 监控摄像头 | 主播网红 | 高清无码 | 中文字幕 | 成人综艺 | 媚黑母狗 | 为国争光 | 少女破处 | 人兽典藏 | 中文剧情</t>
         </is>
       </c>
-      <c r="M65" s="2" t="inlineStr">
+      <c r="N65" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -4504,7 +4825,7 @@
         </is>
       </c>
       <c r="H66" s="2" t="n">
-        <v>1323</v>
+        <v>804</v>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
@@ -4519,8 +4840,13 @@
       <c r="K66" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L66" s="2" t="inlineStr"/>
-      <c r="M66" s="2" t="inlineStr">
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -4563,7 +4889,7 @@
         </is>
       </c>
       <c r="H67" s="2" t="n">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
@@ -4580,10 +4906,15 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
           <t>精品推荐 | 国产精品 | 主播秀色 | 日本有码 | 日本无码 | 中文字幕 | 童颜巨乳 | 性感人妻 | 强奸乱伦 | 欧美情色 | 三级伦理 | 卡通动漫 | 丝袜OL | 自拍偷拍 | 日本片商 | 剧情介绍 | 网曝系列 | 麻豆传媒 | 明星换脸 | 国产乱伦</t>
         </is>
       </c>
-      <c r="M67" s="2" t="inlineStr">
+      <c r="N67" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -4643,8 +4974,13 @@
       <c r="K68" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L68" s="2" t="inlineStr"/>
-      <c r="M68" s="2" t="inlineStr">
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -4704,8 +5040,13 @@
       <c r="K69" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L69" s="2" t="inlineStr"/>
-      <c r="M69" s="2" t="inlineStr">
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -4748,7 +5089,7 @@
         </is>
       </c>
       <c r="H70" s="2" t="n">
-        <v>1509</v>
+        <v>829</v>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
@@ -4765,10 +5106,15 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
           <t>国产自拍 | 欧美极品 | 日韩无码 | AV明星 | 公告 | 头条 | 中文字幕 | 动漫精品 | 极骚萝莉 | 人妖视频 | 重咸口味 | 三级自慰 | 强奸乱伦 | 独家擂台格斗 | 辣椒GIGA | HEYZO | 独家DMM | HEY诱惑 | 童颜巨乳 | 高潮喷吹</t>
         </is>
       </c>
-      <c r="M70" s="2" t="inlineStr">
+      <c r="N70" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -4811,7 +5157,7 @@
         </is>
       </c>
       <c r="H71" s="2" t="n">
-        <v>1008</v>
+        <v>871</v>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
@@ -4826,8 +5172,13 @@
       <c r="K71" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L71" s="2" t="inlineStr"/>
-      <c r="M71" s="2" t="inlineStr">
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -4887,8 +5238,13 @@
       <c r="K72" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L72" s="2" t="inlineStr"/>
-      <c r="M72" s="2" t="inlineStr">
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -4931,7 +5287,7 @@
         </is>
       </c>
       <c r="H73" s="2" t="n">
-        <v>663</v>
+        <v>720</v>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
@@ -4946,8 +5302,13 @@
       <c r="K73" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L73" s="2" t="inlineStr"/>
-      <c r="M73" s="2" t="inlineStr">
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -4990,7 +5351,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>2523</v>
+        <v>2264</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -5007,10 +5368,15 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
           <t>电影片 | 连续剧 | 综艺片 | 动漫片 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 韩国剧 | 欧美剧 | 记录片 | 台湾剧 | 日本剧 | 海外剧 | 泰国剧</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -5053,7 +5419,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>385</v>
+        <v>298</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -5070,10 +5436,15 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
           <t>电视剧 | 电影 | 欧美剧 | 香港剧 | 韩剧 | 日剧 | 马泰剧 | 伦理片 | 动作片 | 爱情片 | 喜剧片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 记录片 | 动漫 | 内地剧 | 动画片 | 中国动漫</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -5129,8 +5500,13 @@
       <c r="K76" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L76" s="2" t="inlineStr"/>
-      <c r="M76" s="2" t="inlineStr">
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -5169,7 +5545,7 @@
         </is>
       </c>
       <c r="H77" s="2" t="n">
-        <v>773</v>
+        <v>687</v>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
@@ -5186,10 +5562,15 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
           <t>视频一区 | 日韩无码 | 国产主播 | 视频三区 | 日韩精品 | 欧美劲爆 | 成人动漫 | 自拍偷拍 | 伦理影片 | 中文字幕 | 人妻系列 | 制服诱惑 | 强奸乱伦 | AV明星 | SM重味 | 视频二区 | 巨乳尤物 | 颜射系列 | 口交视频 | 自慰系列</t>
         </is>
       </c>
-      <c r="M77" s="2" t="inlineStr">
+      <c r="N77" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置</t>
         </is>
@@ -5244,117 +5625,136 @@
       <c r="K78" t="n">
         <v>0</v>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>huawei8</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>华为吧资源</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
         <is>
           <t>https://huawei8.live/api.php/provide/vod</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>无法探测→按普通处理</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
+      <c r="D79" s="2" t="inlineStr"/>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>名称关键词</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>失活</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K79" t="n">
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>taopianapi</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>淘片资源</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
         <is>
           <t>https://taopianapi.com/cjapi/sda/vod</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>无法探测→按普通处理</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
+      <c r="D80" s="2" t="inlineStr"/>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>名称关键词</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>失活</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K80" t="n">
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -5392,7 +5792,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>766</v>
+        <v>617</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -5409,10 +5809,15 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 港澳剧 | 日剧 | 欧美剧 | 台湾剧 | 泰剧 | 韩剧 | 纪录片 | 动漫电影</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="N81" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置</t>
         </is>
@@ -5455,7 +5860,7 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>588</v>
+        <v>621</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -5472,10 +5877,15 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 欧美剧 | 韩剧 | 日剧 | 港剧 | 台剧 | 泰剧 | 纪录片 | 海外剧</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置,sp696</t>
         </is>
@@ -5513,7 +5923,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>236</v>
+        <v>342</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -5530,10 +5940,15 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
           <t>电视剧 | 电影 | 欧美剧 | 香港剧 | 韩剧 | 日剧 | 马泰剧 | 伦理片 | 动作片 | 爱情片 | 喜剧片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 记录片 | 动漫 | 内地剧 | 动画片 | 中国动漫</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
+      <c r="N83" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -5588,7 +6003,12 @@
       <c r="K84" t="n">
         <v>0</v>
       </c>
-      <c r="M84" t="inlineStr">
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -5643,7 +6063,12 @@
       <c r="K85" t="n">
         <v>0</v>
       </c>
-      <c r="M85" t="inlineStr">
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -5681,7 +6106,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>521</v>
+        <v>535</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -5696,7 +6121,12 @@
       <c r="K86" t="n">
         <v>0</v>
       </c>
-      <c r="M86" t="inlineStr">
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -5735,7 +6165,7 @@
         </is>
       </c>
       <c r="H87" s="2" t="n">
-        <v>436</v>
+        <v>406</v>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
@@ -5752,10 +6182,15 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
           <t>国产区 | AV区 | 欧美区 | 动漫区 | 网红主播 | 国产传媒 | 探花系列 | 人妻熟女 | 日本无码 | 美乳巨乳 | 强制侵犯 | 制服诱惑 | 绝色佳人 | 风俗泡泡浴 | 家庭乱伦 | AV解说 | 三级电影 | 少女萝莉 | SM调教 | 绝顶潮吹</t>
         </is>
       </c>
-      <c r="M87" s="2" t="inlineStr">
+      <c r="N87" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -5798,7 +6233,7 @@
         </is>
       </c>
       <c r="H88" s="2" t="n">
-        <v>312</v>
+        <v>474</v>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
@@ -5815,10 +6250,15 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
           <t>国产自拍 | 日韩AV | 欧美精品 | 异族风情 | 动漫专栏 | 强奸迷奸 | 丝袜制服 | 国产厂牌 | SM调教 | 乱伦 | 网曝黑料 | 主播网红 | 自拍偷拍 | 口交自慰 | 群交多P | AI换脸 | 素人特摄 | 无码高清 | 经典有码 | 中文字幕</t>
         </is>
       </c>
-      <c r="M88" s="2" t="inlineStr">
+      <c r="N88" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -5856,7 +6296,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -5871,7 +6311,12 @@
       <c r="K89" t="n">
         <v>0</v>
       </c>
-      <c r="M89" t="inlineStr">
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -5910,7 +6355,7 @@
         </is>
       </c>
       <c r="H90" s="2" t="n">
-        <v>807</v>
+        <v>3854</v>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
@@ -5925,8 +6370,13 @@
       <c r="K90" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L90" s="2" t="inlineStr"/>
-      <c r="M90" s="2" t="inlineStr">
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -5964,7 +6414,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>575</v>
+        <v>845</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -5979,7 +6429,12 @@
       <c r="K91" t="n">
         <v>0</v>
       </c>
-      <c r="M91" t="inlineStr">
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -6018,17 +6473,15 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>失活</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>存活/非标准</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>1711</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6039,7 +6492,12 @@
       <c r="K92" t="n">
         <v>0</v>
       </c>
-      <c r="M92" t="inlineStr">
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置,sp696</t>
         </is>
@@ -6082,7 +6540,7 @@
         </is>
       </c>
       <c r="H93" s="2" t="n">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
@@ -6097,8 +6555,13 @@
       <c r="K93" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L93" s="2" t="inlineStr"/>
-      <c r="M93" s="2" t="inlineStr">
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -6153,7 +6616,12 @@
       <c r="K94" t="n">
         <v>0</v>
       </c>
-      <c r="M94" t="inlineStr">
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -6196,7 +6664,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>696</v>
+        <v>2227</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -6213,10 +6681,15 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
           <t>电影片 | 连续剧 | 综艺片 | 动漫片 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 韩国剧 | 欧美剧 | 记录片 | 台湾剧 | 日本剧 | 海外剧 | 泰国剧</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr">
+      <c r="N95" t="inlineStr">
         <is>
           <t>仓库2-基础版</t>
         </is>
@@ -6259,7 +6732,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>386</v>
+        <v>271</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -6276,10 +6749,15 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 欧美剧 | 韩剧 | 日剧 | 港剧 | 台剧 | 泰剧 | 纪录片 | 海外剧</t>
         </is>
       </c>
-      <c r="M96" t="inlineStr">
+      <c r="N96" t="inlineStr">
         <is>
           <t>cmliu配置,sp696</t>
         </is>
@@ -6322,7 +6800,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>620</v>
+        <v>633</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -6339,10 +6817,15 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 伦理片 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 韩国剧 | 欧美剧 | 体育 | NBA | 惊悚片 | 家庭篇</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr">
+      <c r="N97" t="inlineStr">
         <is>
           <t>cmliu配置,sp696</t>
         </is>
@@ -6385,7 +6868,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>592</v>
+        <v>2207</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -6402,10 +6885,15 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
           <t>电影片 | 连续剧 | 综艺片 | 动漫片 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 韩国剧 | 欧美剧 | 记录片 | 台湾剧 | 日本剧 | 海外剧 | 泰国剧</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr">
+      <c r="N98" t="inlineStr">
         <is>
           <t>cmliu配置,sp696</t>
         </is>
@@ -6448,7 +6936,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -6465,10 +6953,15 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 伦理片 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 韩国剧 | 欧美剧 | 体育 | NBA | 惊悚片 | 家庭篇</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr">
+      <c r="N99" t="inlineStr">
         <is>
           <t>cmliu配置,sp696</t>
         </is>
@@ -6511,7 +7004,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>933</v>
+        <v>790</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -6528,10 +7021,15 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 台湾剧 | 韩国剧 | 欧美剧 | 香港剧 | 泰国剧 | 日本剧 | 福利 | 记录片</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr">
+      <c r="N100" t="inlineStr">
         <is>
           <t>cmliu配置,sp696</t>
         </is>
@@ -6574,7 +7072,7 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>737</v>
+        <v>648</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -6591,10 +7089,15 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
           <t>电影 | 连续剧 | 综艺片 | 动漫 | 纪录片 | 动作片 | 爱情片 | 喜剧片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 欧美剧 | 韩剧 | 动漫电影 | 泰国剧 | 日本剧 | 台湾剧</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr">
+      <c r="N101" t="inlineStr">
         <is>
           <t>cmliu配置,sp696</t>
         </is>
@@ -6637,7 +7140,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -6654,10 +7157,15 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
           <t>电视剧 | 电影 | 欧美剧 | 香港剧 | 韩剧 | 日剧 | 马泰剧 | 伦理片 | 动作片 | 爱情片 | 喜剧片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 记录片 | 动漫 | 内地剧 | 动画片 | 中国动漫</t>
         </is>
       </c>
-      <c r="M102" t="inlineStr">
+      <c r="N102" t="inlineStr">
         <is>
           <t>cmliu配置</t>
         </is>
@@ -6700,7 +7208,7 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>3411</v>
+        <v>1395</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -6717,10 +7225,15 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 福利视频 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 犯罪片 | 战争片 | 国产剧 | 港台剧 | 日韩剧 | 欧美剧 | 三级伦理 | 网红主播 | 动画电影 | 剧情片</t>
         </is>
       </c>
-      <c r="M103" t="inlineStr">
+      <c r="N103" t="inlineStr">
         <is>
           <t>cmliu配置,sp696</t>
         </is>
@@ -6763,7 +7276,7 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>1230</v>
+        <v>1595</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -6780,10 +7293,15 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
           <t>电影片 | 连续剧 | 综艺片 | 动漫片 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 韩国剧 | 欧美剧 | 记录片 | 台湾剧 | 日本剧 | 海外剧 | 泰国剧</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr">
+      <c r="N104" t="inlineStr">
         <is>
           <t>cmliu配置</t>
         </is>
@@ -6826,7 +7344,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>420</v>
+        <v>465</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -6843,10 +7361,15 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 大陆剧 | 欧美剧 | 韩剧 | 日剧 | 港澳剧 | 台湾剧 | 泰剧 | 纪录片 | 其他剧</t>
         </is>
       </c>
-      <c r="M105" t="inlineStr">
+      <c r="N105" t="inlineStr">
         <is>
           <t>cmliu配置,sp696</t>
         </is>
@@ -6889,7 +7412,7 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>825</v>
+        <v>764</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -6906,10 +7429,15 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
+          <t>仅完整版</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
           <t>电视剧 | 电影 | 欧美剧 | 香港剧 | 韩剧 | 日剧 | 马泰剧 | 伦理片 | 动作片 | 爱情片 | 喜剧片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 记录片 | 动漫 | 内地剧 | 动画片 | 中国动漫</t>
         </is>
       </c>
-      <c r="M106" t="inlineStr">
+      <c r="N106" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -6952,7 +7480,7 @@
         </is>
       </c>
       <c r="H107" s="2" t="n">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
@@ -6969,10 +7497,15 @@
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
           <t>国产区 | AV区 | 欧美区 | 动漫区 | 网红主播 | 国产传媒 | 探花系列 | 人妻熟女 | 日本无码 | 美乳巨乳 | 强制侵犯 | 制服诱惑 | 绝色佳人 | 风俗泡泡浴 | 家庭乱伦 | AV解说 | 三级电影 | 少女萝莉 | SM调教 | 绝顶潮吹</t>
         </is>
       </c>
-      <c r="M107" s="2" t="inlineStr">
+      <c r="N107" s="2" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -7015,7 +7548,7 @@
         </is>
       </c>
       <c r="H108" s="2" t="n">
-        <v>801</v>
+        <v>762</v>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
@@ -7032,10 +7565,15 @@
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
           <t>视频一区 | 视频二区 | 视频三区 | 视频四区 | 精品推荐 | 国产主播 | 国产乱伦 | 自拍偷拍 | 制服丝袜 | 网曝事件 | 传媒探花 | 清纯学生 | A V 解说 | 淫妻作乐 | 港台辣妹 | 足浴撩妹 | 反差母狗 | A I 换脸 | V R 视角 | 重口性癖</t>
         </is>
       </c>
-      <c r="M108" s="2" t="inlineStr">
+      <c r="N108" s="2" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -7078,7 +7616,7 @@
         </is>
       </c>
       <c r="H109" s="2" t="n">
-        <v>707</v>
+        <v>793</v>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
@@ -7095,10 +7633,15 @@
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
           <t>精品推荐 | 国产色情 | 主播直播 | 亚洲无码 | 亚洲有码 | 中文字幕 | 巨乳美乳 | 人妻熟女 | 强奸乱伦 | 欧美精品 | 萝莉少女 | 伦理三级 | 成人动漫 | 自拍偷拍 | 制服丝袜 | 口交颜射 | 日本精品 | Cosplay | 素人自拍 | 台湾辣妹</t>
         </is>
       </c>
-      <c r="M109" s="2" t="inlineStr">
+      <c r="N109" s="2" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -7141,7 +7684,7 @@
         </is>
       </c>
       <c r="H110" s="2" t="n">
-        <v>371</v>
+        <v>472</v>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
@@ -7158,10 +7701,15 @@
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
           <t>采集教程 | 国产视频 | 国产传媒 | 国产探花 | 极品学生 | 野战户外 | 网曝黑料 | 日本有码 | 主播大秀 | 校园春色 | SM虐待 | 巨乳系列 | 偷拍自拍 | 强奸乱伦 | 制服诱惑 | 欧美精品 | 三级伦理 | AV解说 | 成人动漫 | 日本无码</t>
         </is>
       </c>
-      <c r="M110" s="2" t="inlineStr">
+      <c r="N110" s="2" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -7204,7 +7752,7 @@
         </is>
       </c>
       <c r="H111" s="2" t="n">
-        <v>546</v>
+        <v>371</v>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
@@ -7221,10 +7769,15 @@
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
           <t>国产专区 | 国产厂商 | 主播视讯 | 日本无码 | 日本有码 | 中文字幕 | 中字无码 | 中字有码 | 水果派解说 | 麻豆传媒 | 91制片厂 | 蜜桃影像传媒 | 天美传媒 | 精东影业 | 星空无限传媒 | 台湾swag | 其他传媒 | 三级伦理 | 美女写真 | 卡通动漫</t>
         </is>
       </c>
-      <c r="M111" s="2" t="inlineStr">
+      <c r="N111" s="2" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -7267,7 +7820,7 @@
         </is>
       </c>
       <c r="H112" s="2" t="n">
-        <v>1143</v>
+        <v>1255</v>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
@@ -7284,10 +7837,15 @@
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
           <t>中文字幕 | 日本有码 | 日本无码 | AV解说 | cosplay | 都市激情 | 校园情事 | 人妻纵情 | 风俗伦理 | 另类小说 | 武侠古典 | 长篇连载 | 黑丝诱惑 | SWAG | 自拍偷拍 | 激情动漫 | 网红主播 | 探花系列 | 三级伦理 | VR视角</t>
         </is>
       </c>
-      <c r="M112" s="2" t="inlineStr">
+      <c r="N112" s="2" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -7330,7 +7888,7 @@
         </is>
       </c>
       <c r="H113" s="2" t="n">
-        <v>524</v>
+        <v>793</v>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
@@ -7347,10 +7905,15 @@
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
           <t>视频1区 | 国产精品 | 华语AV | 黑料吃瓜 | 欧美 | 禁漫 | 视频2区 | 学生 | 乱伦 | 探花 | 日本无码 | 日本有码 | 主播网红 | 日本素人 | AI短剧</t>
         </is>
       </c>
-      <c r="M113" s="2" t="inlineStr">
+      <c r="N113" s="2" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -7393,7 +7956,7 @@
         </is>
       </c>
       <c r="H114" s="2" t="n">
-        <v>2222</v>
+        <v>2256</v>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
@@ -7410,10 +7973,15 @@
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
           <t>中文传媒 | 国产 | 欧美AV | 日本AV | 传媒-麻豆传媒 | 传媒-精东影业 | 传媒-蜜桃传媒 | 传媒-果冻传媒 | 传媒-星空无限传媒 | 传媒-SA国际传媒 | 传媒-性视界传媒 | 国产-自拍 | 国产-偷拍 | 国产-探花 | 国产-主播 | 传媒-天美传媒 | 欧美-高清无码 | 欧美-高清有码 | 日本-中文字幕 | 日本-无码流出</t>
         </is>
       </c>
-      <c r="M114" s="2" t="inlineStr">
+      <c r="N114" s="2" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -7473,8 +8041,13 @@
       <c r="K115" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L115" s="2" t="inlineStr"/>
-      <c r="M115" s="2" t="inlineStr">
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr"/>
+      <c r="N115" s="2" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -7517,7 +8090,7 @@
         </is>
       </c>
       <c r="H116" s="2" t="n">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
@@ -7534,10 +8107,15 @@
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
           <t>视频一区 | 日韩无码 | 国产主播 | 视频三区 | 日韩精品 | 欧美劲爆 | 成人动漫 | 自拍偷拍 | 伦理影片 | 中文字幕 | 人妻系列 | 制服诱惑 | 强奸乱伦 | AV明星 | SM重味 | 视频二区 | 巨乳尤物 | 颜射系列 | 口交视频 | 自慰系列</t>
         </is>
       </c>
-      <c r="M116" s="2" t="inlineStr">
+      <c r="N116" s="2" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -7580,7 +8158,7 @@
         </is>
       </c>
       <c r="H117" s="2" t="n">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
@@ -7595,8 +8173,13 @@
       <c r="K117" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L117" s="2" t="inlineStr"/>
-      <c r="M117" s="2" t="inlineStr">
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr"/>
+      <c r="N117" s="2" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -7639,7 +8222,7 @@
         </is>
       </c>
       <c r="H118" s="2" t="n">
-        <v>709</v>
+        <v>731</v>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
@@ -7656,10 +8239,15 @@
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
           <t>国产自拍 | 日本无码 | 日本有码 | 中文字幕 | 欧美精品 | 成人动漫 | 日本素人 | 高清名优 | 三级伦理 | 网红主播 | 映画传媒 | 人妻熟女 | 口爆颜射 | 萝莉少女 | SM调教 | 美乳巨乳 | 短视频 | 制服诱惑 | 女同性爱 | AI换脸</t>
         </is>
       </c>
-      <c r="M118" s="2" t="inlineStr">
+      <c r="N118" s="2" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -7676,7 +8264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7737,10 +8325,15 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>归属</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>分类名</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
@@ -7783,7 +8376,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>251</v>
+        <v>291</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -7800,10 +8393,15 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>无码专区 | 麻豆传媒 | 制服诱惑 | 三级伦理 | AI换脸 | 中文字幕 | 卡通动漫 | 欧美系列 | 美女主播 | 国产自拍 | 熟女人妻 | 萝莉少女 | 女同性爱 | 多人群交 | 美乳巨乳 | 强奸乱伦 | 生活都市 | 不偷恋情 | 学生校园 | 人妻熟女</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -7863,7 +8461,12 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -7906,7 +8509,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>700</v>
+        <v>1060</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -7923,10 +8526,15 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>麻豆视频 | 91制片厂 | 天美传媒 | 蜜桃传媒 | 皇家华人 | 星空传媒 | 精东影业 | 海角社区 | 成人头条 | 乌鸦传媒 | 兔子先生 | 杏吧原创 | 玩偶姐姐 | mini传媒 | 大象传媒 | 91视频 | PsychoPorn | 糖心Vlog | 萝莉社 | 性视界</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -7981,7 +8589,12 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -8024,7 +8637,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>548</v>
+        <v>195</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -8041,10 +8654,15 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>中文字幕 | 日本有码 | 日本无码 | AV解说 | cosplay | 都市激情 | 校园情事 | 人妻纵情 | 风俗伦理 | 另类小说 | 武侠古典 | 长篇连载 | 黑丝诱惑 | SWAG | 自拍偷拍 | 激情动漫 | 网红主播 | 探花系列 | 三级伦理 | VR视角</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -8087,7 +8705,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>777</v>
+        <v>793</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -8104,10 +8722,15 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
           <t>中文传媒 | 国产 | 欧美AV | 日本AV | 传媒-麻豆传媒 | 传媒-精东影业 | 传媒-蜜桃传媒 | 传媒-果冻传媒 | 传媒-星空无限传媒 | 传媒-SA国际传媒 | 传媒-性视界传媒 | 国产-自拍 | 国产-偷拍 | 国产-探花 | 国产-主播 | 传媒-天美传媒 | 欧美-高清无码 | 欧美-高清有码 | 日本-中文字幕 | 日本-无码流出</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -8150,7 +8773,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>993</v>
+        <v>947</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -8167,10 +8790,15 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
           <t>亚洲情色 | 国产主播 | 国产自拍 | 无码专区 | 欧美性爱 | 熟女人妻 | 强奸乱伦 | 巨乳美乳 | 中文字幕 | 制服诱惑 | 女同性恋 | 卡通动画 | 视频伦理 | 少女萝莉 | 重口色情 | 人兽性交 | 福利姬</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -8213,7 +8841,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>888</v>
+        <v>1028</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -8230,10 +8858,15 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
           <t>国产视频 | 中文字幕 | 国产传媒 | 日本有码 | 日本无码 | 欧美无码 | 强奸乱伦 | 制服诱惑 | 国产主播 | 激情动漫 | 明星换脸 | 抖阴视频 | 女优明星 | 视频一区 | 视频二区 | 网曝黑料 | 视频三区 | 伦理三级 | AV解说 | SM调教</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -8276,7 +8909,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2925</v>
+        <v>1013</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -8293,10 +8926,15 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
           <t>精品国产 | 精品日韩 | 精品综合 | 精品小说 | 精品美图 | 国产自拍 | 主播诱惑 | 探花约炮 | 偷拍偷窥 | 网曝吃瓜 | 抖阴短片 | 传媒剧情 | 日韩主播 | 日韩无码 | 中文字幕 | AV解说 | 换脸明星 | 强奸乱伦 | 女优明星 | 欧美激情</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -8339,7 +8977,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>784</v>
+        <v>753</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -8356,10 +8994,15 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
           <t>精品推荐 | 国产色情 | 主播直播 | 亚洲无码 | 亚洲有码 | 中文字幕 | 巨乳美乳 | 人妻熟女 | 强奸乱伦 | 欧美精品 | 萝莉少女 | 伦理三级 | 成人动漫 | 自拍偷拍 | 制服丝袜 | 口交颜射 | 日本精品 | Cosplay | 素人自拍 | 台湾辣妹</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置</t>
         </is>
@@ -8402,7 +9045,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>854</v>
+        <v>1266</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -8417,7 +9060,12 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -8460,7 +9108,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>577</v>
+        <v>602</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -8477,10 +9125,15 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
           <t>精品推荐 | 国产精品 | 主播秀色 | 日本有码 | 日本无码 | 中文字幕 | 童颜巨乳 | 性感人妻 | 强奸乱伦 | 欧美情色 | 三级伦理 | 卡通动漫 | 丝袜OL | 自拍偷拍 | 日本片商 | 剧情介绍 | 网曝系列 | 麻豆传媒 | 明星换脸 | 国产乱伦</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -8523,7 +9176,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>743</v>
+        <v>726</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -8540,10 +9193,15 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
           <t>制服丝袜 | 群交淫乱 | 无码专区 | 偷拍自拍 | 卡通动漫 | 中文字幕 | 欧美性爱 | 巨乳美乳 | 国产裸聊 | 国产自拍 | 国产盗摄 | 伦理三级 | 女同性恋 | 少女萝莉 | 人妖系列 | 虚拟VR | 亚州图片 | 欧美图片 | 美腿丝袜 | 网友自拍</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -8586,7 +9244,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1217</v>
+        <v>1038</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -8601,7 +9259,12 @@
       <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -8644,7 +9307,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>802</v>
+        <v>594</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -8661,10 +9324,15 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
           <t>国产 | 日本 | 欧美 | 动漫 | 偷拍自拍 | 国产大制作 | 乱伦毁三观 | 嫖妓全过程 | 淫乱学生妹 | 黑料不打烊 | 监控摄像头 | 主播网红 | 高清无码 | 中文字幕 | 成人综艺 | 媚黑母狗 | 为国争光 | 少女破处 | 人兽典藏 | 中文剧情</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -8707,7 +9375,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1323</v>
+        <v>804</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -8722,7 +9390,12 @@
       <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -8765,7 +9438,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -8782,10 +9455,15 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
           <t>精品推荐 | 国产精品 | 主播秀色 | 日本有码 | 日本无码 | 中文字幕 | 童颜巨乳 | 性感人妻 | 强奸乱伦 | 欧美情色 | 三级伦理 | 卡通动漫 | 丝袜OL | 自拍偷拍 | 日本片商 | 剧情介绍 | 网曝系列 | 麻豆传媒 | 明星换脸 | 国产乱伦</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -8845,7 +9523,12 @@
       <c r="K19" t="n">
         <v>0</v>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -8905,7 +9588,12 @@
       <c r="K20" t="n">
         <v>0</v>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -8948,7 +9636,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1509</v>
+        <v>829</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -8965,10 +9653,15 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
           <t>国产自拍 | 欧美极品 | 日韩无码 | AV明星 | 公告 | 头条 | 中文字幕 | 动漫精品 | 极骚萝莉 | 人妖视频 | 重咸口味 | 三级自慰 | 强奸乱伦 | 独家擂台格斗 | 辣椒GIGA | HEYZO | 独家DMM | HEY诱惑 | 童颜巨乳 | 高潮喷吹</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -9011,7 +9704,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1008</v>
+        <v>871</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -9026,7 +9719,12 @@
       <c r="K22" t="n">
         <v>0</v>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -9086,7 +9784,12 @@
       <c r="K23" t="n">
         <v>0</v>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -9129,7 +9832,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>663</v>
+        <v>720</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -9144,7 +9847,12 @@
       <c r="K24" t="n">
         <v>0</v>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -9199,7 +9907,12 @@
       <c r="K25" t="n">
         <v>0</v>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -9237,7 +9950,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>773</v>
+        <v>687</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -9254,10 +9967,15 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
           <t>视频一区 | 日韩无码 | 国产主播 | 视频三区 | 日韩精品 | 欧美劲爆 | 成人动漫 | 自拍偷拍 | 伦理影片 | 中文字幕 | 人妻系列 | 制服诱惑 | 强奸乱伦 | AV明星 | SM重味 | 视频二区 | 巨乳尤物 | 颜射系列 | 口交视频 | 自慰系列</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置</t>
         </is>
@@ -9266,17 +9984,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>hsckzy888</t>
+          <t>huawei8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>黄色资源啊啊</t>
+          <t>华为吧资源</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://hsckzy888.com/api.php/provide/vod</t>
+          <t>https://huawei8.live/api.php/provide/vod</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -9286,20 +10004,22 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>上游标记</t>
+          <t>名称关键词</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>存活</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
-        <v>436</v>
+          <t>失活</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>动漫/影视/短剧</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -9308,14 +10028,14 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>国产区 | AV区 | 欧美区 | 动漫区 | 网红主播 | 国产传媒 | 探花系列 | 人妻熟女 | 日本无码 | 美乳巨乳 | 强制侵犯 | 制服诱惑 | 绝色佳人 | 风俗泡泡浴 | 家庭乱伦 | AV解说 | 三级电影 | 少女萝莉 | SM调教 | 绝顶潮吹</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -9324,22 +10044,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>xiaojizy</t>
+          <t>taopianapi</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>🔞小鸡资源</t>
+          <t>淘片资源</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://api.xiaojizy.live/provide/vod</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>https://xiaojizy.live</t>
+          <t>https://taopianapi.com/cjapi/sda/vod</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -9349,20 +10064,22 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>上游标记</t>
+          <t>名称关键词</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>存活</t>
-        </is>
-      </c>
-      <c r="H28" t="n">
-        <v>312</v>
+          <t>失活</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>动漫</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -9371,33 +10088,33 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>国产自拍 | 日韩AV | 欧美精品 | 异族风情 | 动漫专栏 | 强奸迷奸 | 丝袜制服 | 国产厂牌 | SM调教 | 乱伦 | 网曝黑料 | 主播网红 | 自拍偷拍 | 口交自慰 | 群交多P | AI换脸 | 素人特摄 | 无码高清 | 经典有码 | 中文字幕</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>仓库1-增强版,sp696</t>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>仓库1-增强版</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>apilj_provide</t>
+          <t>hsckzy888</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>辣椒资源黄黄</t>
+          <t>黄色资源啊啊</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://apilj.com/api.php/provide</t>
+          <t>https://hsckzy888.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -9407,20 +10124,20 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>域名/标记</t>
+          <t>上游标记</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>存活/非标准</t>
+          <t>存活</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>807</v>
+        <v>406</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>动漫/影视/短剧</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -9429,9 +10146,19 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>18禁版</t>
+        </is>
       </c>
       <c r="M29" t="inlineStr">
+        <is>
+          <t>国产区 | AV区 | 欧美区 | 动漫区 | 网红主播 | 国产传媒 | 探花系列 | 人妻熟女 | 日本无码 | 美乳巨乳 | 强制侵犯 | 制服诱惑 | 绝色佳人 | 风俗泡泡浴 | 家庭乱伦 | AV解说 | 三级电影 | 少女萝莉 | SM调教 | 绝顶潮吹</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -9440,22 +10167,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>xxibaozyw</t>
+          <t>xiaojizy</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>细胞采集黄色</t>
+          <t>🔞小鸡资源</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://www.xxibaozyw.com/api.php/provide/vod</t>
+          <t>https://api.xiaojizy.live/provide/vod</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.xxibaozyw.com</t>
+          <t>https://xiaojizy.live</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -9465,20 +10192,20 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>域名/标记</t>
+          <t>上游标记</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>存活/非标准</t>
+          <t>存活</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>522</v>
+        <v>474</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>动漫</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -9487,9 +10214,19 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>18禁版</t>
+        </is>
       </c>
       <c r="M30" t="inlineStr">
+        <is>
+          <t>国产自拍 | 日韩AV | 欧美精品 | 异族风情 | 动漫专栏 | 强奸迷奸 | 丝袜制服 | 国产厂牌 | SM调教 | 乱伦 | 网曝黑料 | 主播网红 | 自拍偷拍 | 口交自慰 | 群交多P | AI换脸 | 素人特摄 | 无码高清 | 经典有码 | 中文字幕</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -9498,22 +10235,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>hsckzy_xyz</t>
+          <t>apilj_provide</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>🔞黄色仓库</t>
+          <t>辣椒资源黄黄</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://hsckzy.xyz/api.php/provide/vod</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>https://hsckzy.xyz</t>
+          <t>https://apilj.com/api.php/provide</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -9523,20 +10255,20 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>上游标记</t>
+          <t>域名/标记</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>存活</t>
+          <t>存活/非标准</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>393</v>
+        <v>3854</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>动漫/影视/短剧</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -9545,38 +10277,38 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>国产区 | AV区 | 欧美区 | 动漫区 | 网红主播 | 国产传媒 | 探花系列 | 人妻熟女 | 日本无码 | 美乳巨乳 | 强制侵犯 | 制服诱惑 | 绝色佳人 | 风俗泡泡浴 | 家庭乱伦 | AV解说 | 三级电影 | 少女萝莉 | SM调教 | 绝顶潮吹</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>sp696</t>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>仓库1-增强版</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>apidanaizi_com</t>
+          <t>xxibaozyw</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>🔞-大奶子-</t>
+          <t>细胞采集黄色</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://apidanaizi.com/api.php/provide/vod</t>
+          <t>https://www.xxibaozyw.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://apidanaizi.com</t>
+          <t>https://www.xxibaozyw.com</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -9586,20 +10318,20 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>上游标记</t>
+          <t>域名/标记</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>存活</t>
+          <t>存活/非标准</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>801</v>
+        <v>527</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>动漫</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -9608,38 +10340,38 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>视频一区 | 视频二区 | 视频三区 | 视频四区 | 精品推荐 | 国产主播 | 国产乱伦 | 自拍偷拍 | 制服丝袜 | 网曝事件 | 传媒探花 | 清纯学生 | A V 解说 | 淫妻作乐 | 港台辣妹 | 足浴撩妹 | 反差母狗 | A I 换脸 | V R 视角 | 重口性癖</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>sp696</t>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>仓库1-增强版,sp696</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>slapibf_com</t>
+          <t>hsckzy_xyz</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>🔞森林资源</t>
+          <t>🔞黄色仓库</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://beiyong.slapibf.com/api.php/provide/vod</t>
+          <t>https://hsckzy.xyz/api.php/provide/vod</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://slapibf.com</t>
+          <t>https://hsckzy.xyz</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -9649,7 +10381,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>分类实测</t>
+          <t>上游标记</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9658,11 +10390,11 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>707</v>
+        <v>378</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>18禁/动漫</t>
+          <t>动漫/影视/短剧</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -9671,14 +10403,19 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>精品推荐 | 国产色情 | 主播直播 | 亚洲无码 | 亚洲有码 | 中文字幕 | 巨乳美乳 | 人妻熟女 | 强奸乱伦 | 欧美精品 | 萝莉少女 | 伦理三级 | 成人动漫 | 自拍偷拍 | 制服丝袜 | 口交颜射 | 日本精品 | Cosplay | 素人自拍 | 台湾辣妹</t>
+          <t>18禁版</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
+        <is>
+          <t>国产区 | AV区 | 欧美区 | 动漫区 | 网红主播 | 国产传媒 | 探花系列 | 人妻熟女 | 日本无码 | 美乳巨乳 | 强制侵犯 | 制服诱惑 | 绝色佳人 | 风俗泡泡浴 | 家庭乱伦 | AV解说 | 三级电影 | 少女萝莉 | SM调教 | 绝顶潮吹</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -9687,22 +10424,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>doudouzy_com</t>
+          <t>apidanaizi_com</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>🔞豆豆资源</t>
+          <t>🔞-大奶子-</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://api.douapi.cc/api.php/provide/vod</t>
+          <t>https://apidanaizi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://doudouzy.com</t>
+          <t>https://apidanaizi.com</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -9712,7 +10449,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>分类实测</t>
+          <t>上游标记</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9721,11 +10458,11 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>371</v>
+        <v>762</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>18禁/动漫</t>
+          <t>动漫</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -9734,14 +10471,19 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>采集教程 | 国产视频 | 国产传媒 | 国产探花 | 极品学生 | 野战户外 | 网曝黑料 | 日本有码 | 主播大秀 | 校园春色 | SM虐待 | 巨乳系列 | 偷拍自拍 | 强奸乱伦 | 制服诱惑 | 欧美精品 | 三级伦理 | AV解说 | 成人动漫 | 日本无码</t>
+          <t>18禁版</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
+        <is>
+          <t>视频一区 | 视频二区 | 视频三区 | 视频四区 | 精品推荐 | 国产主播 | 国产乱伦 | 自拍偷拍 | 制服丝袜 | 网曝事件 | 传媒探花 | 清纯学生 | A V 解说 | 淫妻作乐 | 港台辣妹 | 足浴撩妹 | 反差母狗 | A I 换脸 | V R 视角 | 重口性癖</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -9750,22 +10492,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>didizy_com</t>
+          <t>slapibf_com</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>🔞滴滴资源</t>
+          <t>🔞森林资源</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://api.ddapi.cc/api.php/provide/vod</t>
+          <t>https://beiyong.slapibf.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://didizy.com</t>
+          <t>https://slapibf.com</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -9784,7 +10526,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>546</v>
+        <v>793</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -9797,14 +10539,19 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>国产专区 | 国产厂商 | 主播视讯 | 日本无码 | 日本有码 | 中文字幕 | 中字无码 | 中字有码 | 水果派解说 | 麻豆传媒 | 91制片厂 | 蜜桃影像传媒 | 天美传媒 | 精东影业 | 星空无限传媒 | 台湾swag | 其他传媒 | 三级伦理 | 美女写真 | 卡通动漫</t>
+          <t>18禁版</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
+        <is>
+          <t>精品推荐 | 国产色情 | 主播直播 | 亚洲无码 | 亚洲有码 | 中文字幕 | 巨乳美乳 | 人妻熟女 | 强奸乱伦 | 欧美精品 | 萝莉少女 | 伦理三级 | 成人动漫 | 自拍偷拍 | 制服丝袜 | 口交颜射 | 日本精品 | Cosplay | 素人自拍 | 台湾辣妹</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -9813,22 +10560,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>heiliaozy_cc</t>
+          <t>doudouzy_com</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>🔞黑料资源</t>
+          <t>🔞豆豆资源</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://www.heiliaozyapi.com/api.php/provide/vod</t>
+          <t>https://api.douapi.cc/api.php/provide/vod</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://heiliaozy.cc</t>
+          <t>https://doudouzy.com</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -9847,7 +10594,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1143</v>
+        <v>472</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -9860,14 +10607,19 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>中文字幕 | 日本有码 | 日本无码 | AV解说 | cosplay | 都市激情 | 校园情事 | 人妻纵情 | 风俗伦理 | 另类小说 | 武侠古典 | 长篇连载 | 黑丝诱惑 | SWAG | 自拍偷拍 | 激情动漫 | 网红主播 | 探花系列 | 三级伦理 | VR视角</t>
+          <t>18禁版</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
+        <is>
+          <t>采集教程 | 国产视频 | 国产传媒 | 国产探花 | 极品学生 | 野战户外 | 网曝黑料 | 日本有码 | 主播大秀 | 校园春色 | SM虐待 | 巨乳系列 | 偷拍自拍 | 强奸乱伦 | 制服诱惑 | 欧美精品 | 三级伦理 | AV解说 | 成人动漫 | 日本无码</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -9876,22 +10628,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>thzy8_me</t>
+          <t>didizy_com</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>🔞桃花资源</t>
+          <t>🔞滴滴资源</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://thzy1.me/api.php/provide/vod</t>
+          <t>https://api.ddapi.cc/api.php/provide/vod</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://thzy8.me</t>
+          <t>https://didizy.com</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -9901,7 +10653,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>上游标记</t>
+          <t>分类实测</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9910,11 +10662,11 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>524</v>
+        <v>371</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>短剧</t>
+          <t>18禁/动漫</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -9923,14 +10675,19 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>视频1区 | 国产精品 | 华语AV | 黑料吃瓜 | 欧美 | 禁漫 | 视频2区 | 学生 | 乱伦 | 探花 | 日本无码 | 日本有码 | 主播网红 | 日本素人 | AI短剧</t>
+          <t>18禁版</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
+        <is>
+          <t>国产专区 | 国产厂商 | 主播视讯 | 日本无码 | 日本有码 | 中文字幕 | 中字无码 | 中字有码 | 水果派解说 | 麻豆传媒 | 91制片厂 | 蜜桃影像传媒 | 天美传媒 | 精东影业 | 星空无限传媒 | 台湾swag | 其他传媒 | 三级伦理 | 美女写真 | 卡通动漫</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -9939,22 +10696,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>souavzyw_com</t>
+          <t>heiliaozy_cc</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>🔞souavZY</t>
+          <t>🔞黑料资源</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://api.souavzyw.net/api.php/provide/vod</t>
+          <t>https://www.heiliaozyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://api.souavzyw.net</t>
+          <t>https://heiliaozy.cc</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -9973,7 +10730,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>2222</v>
+        <v>1255</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -9986,14 +10743,19 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>中文传媒 | 国产 | 欧美AV | 日本AV | 传媒-麻豆传媒 | 传媒-精东影业 | 传媒-蜜桃传媒 | 传媒-果冻传媒 | 传媒-星空无限传媒 | 传媒-SA国际传媒 | 传媒-性视界传媒 | 国产-自拍 | 国产-偷拍 | 国产-探花 | 国产-主播 | 传媒-天美传媒 | 欧美-高清无码 | 欧美-高清有码 | 日本-中文字幕 | 日本-无码流出</t>
+          <t>18禁版</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
+        <is>
+          <t>中文字幕 | 日本有码 | 日本无码 | AV解说 | cosplay | 都市激情 | 校园情事 | 人妻纵情 | 风俗伦理 | 另类小说 | 武侠古典 | 长篇连载 | 黑丝诱惑 | SWAG | 自拍偷拍 | 激情动漫 | 网红主播 | 探花系列 | 三级伦理 | VR视角</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -10002,22 +10764,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>xiangjiaozyw_com</t>
+          <t>thzy8_me</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>🔞香蕉资源</t>
+          <t>🔞桃花资源</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://www.xiangjiaozyw.com/api.php/provide/vod</t>
+          <t>https://thzy1.me/api.php/provide/vod</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.xiangjiaozyw.com</t>
+          <t>https://thzy8.me</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -10027,22 +10789,20 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>域名/标记</t>
+          <t>上游标记</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>失活</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>存活</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>793</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>短剧</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -10051,9 +10811,19 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>18禁版</t>
+        </is>
       </c>
       <c r="M39" t="inlineStr">
+        <is>
+          <t>视频1区 | 国产精品 | 华语AV | 黑料吃瓜 | 欧美 | 禁漫 | 视频2区 | 学生 | 乱伦 | 探花 | 日本无码 | 日本有码 | 主播网红 | 日本素人 | AI短剧</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -10062,22 +10832,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>xingba111_com</t>
+          <t>souavzyw_com</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>🔞杏吧资源</t>
+          <t>🔞souavZY</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://xingba222.com/api.php/provide/vod</t>
+          <t>https://api.souavzyw.net/api.php/provide/vod</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://xingba111.com</t>
+          <t>https://api.souavzyw.net</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -10096,7 +10866,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>591</v>
+        <v>2256</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -10109,14 +10879,19 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>视频一区 | 日韩无码 | 国产主播 | 视频三区 | 日韩精品 | 欧美劲爆 | 成人动漫 | 自拍偷拍 | 伦理影片 | 中文字幕 | 人妻系列 | 制服诱惑 | 强奸乱伦 | AV明星 | SM重味 | 视频二区 | 巨乳尤物 | 颜射系列 | 口交视频 | 自慰系列</t>
+          <t>18禁版</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
+        <is>
+          <t>中文传媒 | 国产 | 欧美AV | 日本AV | 传媒-麻豆传媒 | 传媒-精东影业 | 传媒-蜜桃传媒 | 传媒-果冻传媒 | 传媒-星空无限传媒 | 传媒-SA国际传媒 | 传媒-性视界传媒 | 国产-自拍 | 国产-偷拍 | 国产-探花 | 国产-主播 | 传媒-天美传媒 | 欧美-高清无码 | 欧美-高清有码 | 日本-中文字幕 | 日本-无码流出</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -10125,22 +10900,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>dadizy11_com</t>
+          <t>xiangjiaozyw_com</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>🔞大地资源</t>
+          <t>🔞香蕉资源</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://dadiapi.com/feifei</t>
+          <t>https://www.xiangjiaozyw.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://dadizy11.com</t>
+          <t>https://www.xiangjiaozyw.com</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -10155,15 +10930,17 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>存活/非标准</t>
-        </is>
-      </c>
-      <c r="H41" t="n">
-        <v>648</v>
+          <t>失活</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -10174,7 +10951,12 @@
       <c r="K41" t="n">
         <v>0</v>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -10183,61 +10965,197 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>xingba111_com</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>🔞杏吧资源</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://xingba222.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://xingba111.com</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>分类实测</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>存活</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>599</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>18禁/动漫</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>18</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>视频一区 | 日韩无码 | 国产主播 | 视频三区 | 日韩精品 | 欧美劲爆 | 成人动漫 | 自拍偷拍 | 伦理影片 | 中文字幕 | 人妻系列 | 制服诱惑 | 强奸乱伦 | AV明星 | SM重味 | 视频二区 | 巨乳尤物 | 颜射系列 | 口交视频 | 自慰系列</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>sp696</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>dadizy11_com</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>🔞大地资源</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://dadiapi.com/feifei</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://dadizy11.com</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>域名/标记</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>存活/非标准</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>656</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>sp696</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>semaozy1_com</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>🔞色猫资源</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>https://caiji.semaozy.net/inc/apijson_vod.php/provide/vod</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>https://semaozy1.com</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>分类实测</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>存活</t>
         </is>
       </c>
-      <c r="H42" t="n">
-        <v>709</v>
-      </c>
-      <c r="I42" t="inlineStr">
+      <c r="H44" t="n">
+        <v>731</v>
+      </c>
+      <c r="I44" t="inlineStr">
         <is>
           <t>18禁/动漫</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K42" t="n">
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
         <v>12</v>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>18禁版</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t>国产自拍 | 日本无码 | 日本有码 | 中文字幕 | 欧美精品 | 成人动漫 | 日本素人 | 高清名优 | 三级伦理 | 网红主播 | 映画传媒 | 人妻熟女 | 口爆颜射 | 萝莉少女 | SM调教 | 美乳巨乳 | 短视频 | 制服诱惑 | 女同性爱 | AI换脸</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -10254,7 +11172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10302,12 +11220,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>🎬猫眼资源</t>
+          <t>TV-CK资源</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://api.maoyanapi.top/api.php/provide/vod</t>
+          <t>https://ckzy.me/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -10317,14 +11235,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>斗罗大陆Ⅱ绝世唐门</t>
+          <t>如果感激的话就回报到下半身吧</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>732</v>
+        <v>572</v>
       </c>
       <c r="F2" t="n">
-        <v>369</v>
+        <v>490</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -10333,19 +11251,19 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>如意资源(代理)</t>
+          <t>TV-ikun资源</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://pz.v88.qzz.io/?url=https://cj.rycjapi.com/api.php/provide/vod</t>
+          <t>https://ikunzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -10355,14 +11273,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>霹雳英雄战纪之塗附世界</t>
+          <t>某暗部的少女共栖</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1534</v>
+        <v>556</v>
       </c>
       <c r="F3" t="n">
-        <v>324</v>
+        <v>448</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -10378,12 +11296,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TV-360资源</t>
+          <t>🎬猫眼资源</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://360zy.com/api.php/provide/vod</t>
+          <t>https://api.maoyanapi.top/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -10393,14 +11311,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>某暗部的少女共栖</t>
+          <t>斗罗大陆Ⅱ绝世唐门</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1371</v>
+        <v>745</v>
       </c>
       <c r="F4" t="n">
-        <v>267</v>
+        <v>438</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -10416,12 +11334,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>百度云zy(代理)</t>
+          <t>如意资源(代理)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://pz.v88.qzz.io/?url=https://api.apibdzy.com/api.php/provide/vod</t>
+          <t>https://pz.v88.qzz.io/?url=https://cj.rycjapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -10431,18 +11349,18 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>玄苍路之初入宗门</t>
+          <t>霹雳英雄战纪之塗附世界</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>600</v>
+        <v>2138</v>
       </c>
       <c r="F5" t="n">
-        <v>241</v>
+        <v>369</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>慢</t>
+          <t>中</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -10454,12 +11372,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TV-CK资源</t>
+          <t>TV-360资源</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://ckzy.me/api.php/provide/vod</t>
+          <t>https://360zy.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -10469,14 +11387,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>如果感激的话就回报到下半身吧</t>
+          <t>某暗部的少女共栖</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>516</v>
+        <v>1369</v>
       </c>
       <c r="F6" t="n">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -10485,19 +11403,19 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TV-百度云资源</t>
+          <t>百度云zy(代理)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://api.apibdzy.com/api.php/provide/vod</t>
+          <t>https://pz.v88.qzz.io/?url=https://api.apibdzy.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -10511,10 +11429,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1914</v>
+        <v>440</v>
       </c>
       <c r="F7" t="n">
-        <v>200</v>
+        <v>244</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -10530,12 +11448,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TV-ikun资源</t>
+          <t>TV-百度云资源</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://ikunzyapi.com/api.php/provide/vod</t>
+          <t>https://api.apibdzy.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -10545,14 +11463,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>某暗部的少女共栖</t>
+          <t>玄苍路之初入宗门</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>519</v>
+        <v>1552</v>
       </c>
       <c r="F8" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -10587,10 +11505,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1540</v>
+        <v>1578</v>
       </c>
       <c r="F9" t="n">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -10606,12 +11524,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TV-如意资源</t>
+          <t>TV-樱花资源</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://cj.rycjapi.com/api.php/provide/vod</t>
+          <t>https://m3u8.apiyhzy.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -10621,14 +11539,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>霹雳英雄战纪之塗附世界</t>
+          <t>裴太太柔弱人设又翻车了</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4567</v>
+        <v>130</v>
       </c>
       <c r="F10" t="n">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -10637,19 +11555,19 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TV-樱花资源</t>
+          <t>TV-如意资源</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://m3u8.apiyhzy.com/api.php/provide/vod</t>
+          <t>https://cj.rycjapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -10659,14 +11577,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>裴太太柔弱人设又翻车了</t>
+          <t>霹雳英雄战纪之塗附世界</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>113</v>
+        <v>2739</v>
       </c>
       <c r="F11" t="n">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -10675,7 +11593,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -10701,10 +11619,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>974</v>
+        <v>1190</v>
       </c>
       <c r="F12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -10739,10 +11657,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>988</v>
+        <v>628</v>
       </c>
       <c r="F13" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -10758,12 +11676,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TV-U酷资源</t>
+          <t>TV-光速资源</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://api.ukuapi.com/api.php/provide/vod</t>
+          <t>https://api.guangsuapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -10773,7 +11691,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>谋杀奇闻 第一季</t>
+          <t>方舟一号第三季</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -10800,12 +11718,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TV-光速资源</t>
+          <t>TV-新浪点播</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://api.guangsuapi.com/api.php/provide/vod</t>
+          <t>https://api.xinlangapi.com/xinlangapi.php/provide/vod</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -10842,12 +11760,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TV-新浪点播</t>
+          <t>TV-U酷资源88</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://api.xinlangapi.com/xinlangapi.php/provide/vod</t>
+          <t>https://api.ukuapi88.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -10857,7 +11775,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>方舟一号第三季</t>
+          <t>谋杀奇闻 第一季</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -10884,12 +11802,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TV-U酷资源88</t>
+          <t>TV-最大资源</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://api.ukuapi88.com/api.php/provide/vod</t>
+          <t>https://api.zuidapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -10899,13 +11817,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>谋杀奇闻 第一季</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>可以爱你吗</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>72</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -10914,7 +11830,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -10926,12 +11842,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TV-步步高资源</t>
+          <t>TV-丫丫点播</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://api.yparse.com/api/json</t>
+          <t>https://cj.yayazy.net/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -10941,13 +11857,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Word is Bond</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>可以爱你吗</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>732</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -10956,7 +11870,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -10968,12 +11882,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TV-暴风资源</t>
+          <t>TV-最大点播</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://bfzyapi.com/api.php/provide/vod</t>
+          <t>http://zuidazy.me/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -10983,11 +11897,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>乌鸦俱乐部</t>
+          <t>可以爱你吗</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1025</v>
+        <v>729</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -11008,12 +11922,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TV-最大点播</t>
+          <t>TV-暴风资源</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>http://zuidazy.me/api.php/provide/vod</t>
+          <t>https://bfzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -11023,11 +11937,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>可以爱你吗</t>
+          <t>乌鸦俱乐部</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>700</v>
+        <v>741</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -11053,7 +11967,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://api.wujinapi.me/api.php/provide/vod</t>
+          <t>https://api.wujinapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -11067,7 +11981,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222</v>
+        <v>1989</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -11093,7 +12007,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://api.wujinapi.com/api.php/provide/vod</t>
+          <t>https://api.wujinapi.net/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -11107,7 +12021,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>417</v>
+        <v>489</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -11128,12 +12042,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TV-无尽资源</t>
+          <t>TV-红牛资源</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://api.wujinapi.net/api.php/provide/vod</t>
+          <t>https://www.hongniuzy2.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -11143,11 +12057,13 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>穿越时空甩掉你</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>440</v>
+          <t>药屋少女的呢喃第三季</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -11156,7 +12072,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>未测出</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -11168,12 +12084,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TV-最大资源</t>
+          <t>TV-步步高资源</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://api.zuidapi.com/api.php/provide/vod</t>
+          <t>https://api.yparse.com/api/json</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -11183,11 +12099,13 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>可以爱你吗</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>59</v>
+          <t>Word is Bond</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -11196,7 +12114,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>未测出</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -11208,12 +12126,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TV-电影天堂资源</t>
+          <t>TV-虎牙资源</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>http://caiji.dyttzyapi.com/api.php/provide/vod</t>
+          <t>https://www.huyaapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -11223,7 +12141,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>霹雳英雄战纪之塗附世界</t>
+          <t>南瓜头怪2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -11243,19 +12161,19 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TV-红牛资源</t>
+          <t>TV-豆瓣资源</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://www.hongniuzy2.com/api.php/provide/vod</t>
+          <t>https://dbzy.tv/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -11265,7 +12183,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>药屋少女的呢喃第三季</t>
+          <t>骑士情缘</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -11285,19 +12203,19 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TV-丫丫点播</t>
+          <t>TV-豪华资源</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://cj.yayazy.net/api.php/provide/vod</t>
+          <t>https://hhzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -11307,11 +12225,13 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>可以爱你吗</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>751</v>
+          <t>方舟一号第三季</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -11320,7 +12240,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>未测出</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -11332,12 +12252,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TV-虎牙资源</t>
+          <t>TV-速博资源</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://www.huyaapi.com/api.php/provide/vod</t>
+          <t>https://subocaiji.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -11347,7 +12267,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>南瓜头怪2</t>
+          <t>方舟一号第三季</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -11374,12 +12294,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TV-豪华资源</t>
+          <t>TV-量子资源</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://hhzyapi.com/api.php/provide/vod</t>
+          <t>https://cj.lziapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -11389,7 +12309,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>方舟一号第三季</t>
+          <t>霹雳英雄战纪之塗附世界</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -11416,12 +12336,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TV-金鹰资源</t>
+          <t>TV-金鹰点播</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://jyzyapi.com/api.php/provide/vod</t>
+          <t>https://jinyingzy.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -11458,12 +12378,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TV-速博资源</t>
+          <t>TV-金鹰资源</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://subocaiji.com/api.php/provide/vod</t>
+          <t>https://jyzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -11500,12 +12420,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TV-wujinapi无尽</t>
+          <t>TV-电影天堂资源</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://api.wujinapi.cc/api.php/provide/vod</t>
+          <t>http://caiji.dyttzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -11515,11 +12435,13 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>穿越时空甩掉你</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>1273</v>
+          <t>霹雳英雄战纪之塗附世界</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -11528,24 +12450,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>未测出</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TV-豆瓣资源</t>
+          <t>TV-无尽资源</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://dbzy.tv/api.php/provide/vod</t>
+          <t>https://api.wujinapi.me/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -11555,13 +12477,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>骑士情缘</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>穿越时空甩掉你</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>62</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -11570,24 +12490,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TV-金鹰点播</t>
+          <t>TV-牛牛点播</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://jinyingzy.com/api.php/provide/vod</t>
+          <t>https://api.niuniuzy.me/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -11597,13 +12517,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>方舟一号第三季</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>可以爱你吗</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>748</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -11612,7 +12530,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -11624,12 +12542,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TV-量子资源</t>
+          <t>TV-闪电资源</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://cj.lziapi.com/api.php/provide/vod</t>
+          <t>https://sdzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -11639,13 +12557,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>霹雳英雄战纪之塗附世界</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>可以爱你吗</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>712</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -11654,7 +12570,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -11666,12 +12582,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TV-牛牛点播</t>
+          <t>TV-wujinapi无尽</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://api.niuniuzy.me/api.php/provide/vod</t>
+          <t>https://api.wujinapi.cc/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -11681,11 +12597,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>可以爱你吗</t>
+          <t>穿越时空甩掉你</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>724</v>
+        <v>454</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -11706,12 +12622,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TV-非凡资源</t>
+          <t>TV-天涯资源</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://cj.ffzyapi.com/api.php/provide/vod</t>
+          <t>https://tyyszy.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -11721,13 +12637,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>金缮</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>梦醒时遇见你</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>271</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -11736,24 +12650,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>失败:ReadTimeout</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TV-闪电资源</t>
+          <t>TV-索尼资源</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://sdzyapi.com/api.php/provide/vod</t>
+          <t>https://suoniapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -11763,11 +12677,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>可以爱你吗</t>
+          <t>改造旧冷库后我住成了大别墅</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>513</v>
+        <v>69</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -11788,12 +12702,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TV-索尼资源</t>
+          <t>🎬极速资源</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://suoniapi.com/api.php/provide/vod</t>
+          <t>https://jszyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -11803,11 +12717,13 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>改造旧冷库后我住成了大别墅</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>75</v>
+          <t>方舟一号第三季</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -11816,7 +12732,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>未测出</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -11828,12 +12744,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>🎬极速资源</t>
+          <t>TV-神马云</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://jszyapi.com/api.php/provide/vod</t>
+          <t>https://api.1080zyku.com/inc/apijson.php</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -11843,13 +12759,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>方舟一号第三季</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>坠落的大力神</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>895</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -11858,24 +12772,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TV-天涯资源</t>
+          <t>红牛资源3</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://tyyszy.com/api.php/provide/vod</t>
+          <t>https://www.hongniuzy3.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -11885,11 +12799,13 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>梦醒时遇见你</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>296</v>
+          <t>药屋少女的呢喃第三季</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -11898,24 +12814,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>失败:ReadTimeout</t>
+          <t>未测出</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>非凡影视new</t>
+          <t>TV-1080资源</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://api.ffzyapi.com/api.php/provide/vod</t>
+          <t>https://api.1080zyku.com/inc/api_mac10.php</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -11925,13 +12841,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>金缮</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>冰雪狙击</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>697</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -11940,7 +12854,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -11952,12 +12866,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>红牛资源3</t>
+          <t>非凡影视</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://www.hongniuzy3.com/api.php/provide/vod</t>
+          <t>http://ffzy5.tv/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -11967,7 +12881,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>药屋少女的呢喃第三季</t>
+          <t>我与你在一起的理由 特别篇：关岛所赐、那一天的延</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -12078,12 +12992,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>🎬量子资源</t>
+          <t>TV-U酷资源</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://cj.lzcaiji.com/api.php/provide/vod</t>
+          <t>https://api.ukuapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -12093,7 +13007,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>霹雳英雄战纪之塗附世界</t>
+          <t>谋杀奇闻 第一季</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -12120,12 +13034,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>🎬豆瓣资源</t>
+          <t>非凡影视new</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://caiji.dbzy5.com/api.php/provide/vod</t>
+          <t>https://api.ffzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -12135,7 +13049,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>骑士情缘</t>
+          <t>金缮</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -12162,12 +13076,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>🎬金鹰点播</t>
+          <t>索尼-闪电资源</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://jyzyapi.com/provide/vod/from/jinyingyun/at/json</t>
+          <t>https://xsd.sdzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -12177,13 +13091,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>方舟一号第三季</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>可以爱你吗</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>679</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -12192,7 +13104,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -12204,12 +13116,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>TV-1080资源</t>
+          <t>🎬豆瓣资源</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://api.1080zyku.com/inc/api_mac10.php</t>
+          <t>https://caiji.dbzy5.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -12219,11 +13131,13 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>冰雪狙击</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>741</v>
+          <t>骑士情缘</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -12232,7 +13146,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>未测出</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -12244,12 +13158,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>非凡影视</t>
+          <t>🎬金鹰点播</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>http://ffzy5.tv/api.php/provide/vod</t>
+          <t>https://jyzyapi.com/provide/vod/from/jinyingyun/at/json</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -12259,7 +13173,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>金缮</t>
+          <t>方舟一号第三季</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -12279,19 +13193,19 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>索尼-闪电资源</t>
+          <t>🎬360 资源</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://xsd.sdzyapi.com/api.php/provide/vod</t>
+          <t>https://360zyzz.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -12301,11 +13215,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>可以爱你吗</t>
+          <t>Doctor X：白色黑手党时代</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>690</v>
+        <v>606</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -12319,19 +13233,19 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>🎬360 资源</t>
+          <t>艾旦影视(代理)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://360zyzz.com/api.php/provide/vod</t>
+          <t>https://pz.v88.qzz.io/?url=https://lovedan.net/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -12341,11 +13255,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Doctor X：白色黑手党时代</t>
+          <t>伟大的长征</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>610</v>
+        <v>1536</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -12359,19 +13273,19 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TV-神马云</t>
+          <t>🎬量子资源</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://api.1080zyku.com/inc/apijson.php</t>
+          <t>https://cj.lzcaiji.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -12381,11 +13295,13 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>坠落的大力神</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>867</v>
+          <t>霹雳英雄战纪之塗附世界</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -12394,24 +13310,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>未测出</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>🎬快车资源</t>
+          <t>🎬优质资源</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://caiji.kuaichezy.org/api.php/provide/vod</t>
+          <t>https://api.yzzy-api.com/inc/apijson.php</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -12421,11 +13337,11 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>可以爱你吗</t>
+          <t>坠落的大力神</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>671</v>
+        <v>910</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -12439,19 +13355,19 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>艾旦影视(代理)</t>
+          <t>🎬快车资源</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://pz.v88.qzz.io/?url=https://lovedan.net/api.php/provide/vod</t>
+          <t>https://caiji.kuaichezy.org/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -12461,11 +13377,11 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>伟大的长征</t>
+          <t>可以爱你吗</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1411</v>
+        <v>560</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -12486,35 +13402,33 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>🎬优质资源</t>
+          <t>AV-辣椒资源</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://api.yzzy-api.com/inc/apijson.php</t>
+          <t>https://apilj.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>坠落的大力神</t>
+          <t>泌尿科的美人女医8人プラネットプラス伊织凉子,管</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2387</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>691</v>
+      </c>
+      <c r="F56" t="n">
+        <v>11428</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>快</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -12526,12 +13440,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AV-森林资源</t>
+          <t>🔞森林资源</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://slapibf.com/api.php/provide/vod</t>
+          <t>https://beiyong.slapibf.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -12545,10 +13459,10 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="F57" t="n">
-        <v>11334</v>
+        <v>11350</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -12583,10 +13497,10 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="F58" t="n">
-        <v>10787</v>
+        <v>11045</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -12602,12 +13516,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AV-辣椒资源</t>
+          <t>性吧资源</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://apilj.com/api.php/provide/vod</t>
+          <t>https://xingba111.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -12617,14 +13531,14 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>泌尿科的美人女医8人プラネットプラス伊织凉子,管</t>
+          <t xml:space="preserve">DASS-303 被派遣按摩師 按摩到敏感部位 </t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>706</v>
+        <v>545</v>
       </c>
       <c r="F59" t="n">
-        <v>8946</v>
+        <v>7924</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -12633,19 +13547,19 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>🔞森林资源</t>
+          <t>AV-番号资源</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://beiyong.slapibf.com/api.php/provide/vod</t>
+          <t>http://fhapi9.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -12655,14 +13569,14 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>FTHTD-144FALENO学校训练营公共浴池</t>
+          <t>[SSNI-666] 极品人妻被睡服，巨乳爆操内</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>488</v>
+        <v>605</v>
       </c>
       <c r="F60" t="n">
-        <v>8144</v>
+        <v>7269</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -12671,19 +13585,19 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>性吧资源</t>
+          <t>🔞杏吧资源</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://xingba111.com/api.php/provide/vod</t>
+          <t>https://xingba222.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -12697,10 +13611,10 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>575</v>
+        <v>528</v>
       </c>
       <c r="F61" t="n">
-        <v>7745</v>
+        <v>6395</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -12716,12 +13630,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>🔞杏吧资源</t>
+          <t>AV-乐播资源</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://xingba222.com/api.php/provide/vod</t>
+          <t>https://lbapi9.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -12731,14 +13645,14 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">DASS-303 被派遣按摩師 按摩到敏感部位 </t>
+          <t>[无码] 苗条人妻床上骚劲爆棚，风骚妩媚狂求内射</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>489</v>
+        <v>714</v>
       </c>
       <c r="F62" t="n">
-        <v>7632</v>
+        <v>5055</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -12754,12 +13668,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AV-番号资源</t>
+          <t>AV-森林资源</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>http://fhapi9.com/api.php/provide/vod</t>
+          <t>https://slapibf.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -12769,14 +13683,14 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>[SSNI-666] 极品人妻被睡服，巨乳爆操内</t>
+          <t>FTHTD-144FALENO学校训练营公共浴池</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>594</v>
+        <v>390</v>
       </c>
       <c r="F63" t="n">
-        <v>7439</v>
+        <v>3419</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -12785,19 +13699,19 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AV-乐播资源</t>
+          <t>🔞豆豆资源</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://lbapi9.com/api.php/provide/vod</t>
+          <t>https://api.douapi.cc/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -12807,18 +13721,18 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>[无码] 苗条人妻床上骚劲爆棚，风骚妩媚狂求内射</t>
+          <t>美腿玉足控韩国水娃【Hella_cute】顶级吊</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>915</v>
+        <v>338</v>
       </c>
       <c r="F64" t="n">
-        <v>4941</v>
+        <v>855</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>快</t>
+          <t>中</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -12849,10 +13763,10 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="F65" t="n">
-        <v>885</v>
+        <v>838</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -12868,12 +13782,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>🔞豆豆资源</t>
+          <t>AV-JKUN资源</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://api.douapi.cc/api.php/provide/vod</t>
+          <t>https://jkunzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -12883,14 +13797,14 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>美腿玉足控韩国水娃【Hella_cute】顶级吊</t>
+          <t>pacopacomama-072023_880-</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>343</v>
+        <v>48</v>
       </c>
       <c r="F66" t="n">
-        <v>855</v>
+        <v>642</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -12906,12 +13820,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AV-JKUN资源</t>
+          <t>AV-玉兔资源</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://jkunzyapi.com/api.php/provide/vod</t>
+          <t>https://apiyutu.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -12921,14 +13835,14 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>pacopacomama-072023_880-</t>
+          <t>家庭旅馆偷拍性饥渴嫂子偷情小叔子裤子都没脱就主动</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>262</v>
+        <v>375</v>
       </c>
       <c r="F67" t="n">
-        <v>639</v>
+        <v>471</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -12963,10 +13877,10 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>502</v>
+        <v>225</v>
       </c>
       <c r="F68" t="n">
-        <v>442</v>
+        <v>466</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -12982,12 +13896,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AV-玉兔资源</t>
+          <t>AV-奶香香</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://apiyutu.com/api.php/provide/vod</t>
+          <t>https://Naixxzy.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -12997,14 +13911,14 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>家庭旅馆偷拍性饥渴嫂子偷情小叔子裤子都没脱就主动</t>
+          <t>[换脸]孙彩瑛 热热的骚逼..</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>375</v>
+        <v>565</v>
       </c>
       <c r="F69" t="n">
-        <v>442</v>
+        <v>326</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -13013,7 +13927,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -13039,14 +13953,14 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>462</v>
+        <v>522</v>
       </c>
       <c r="F70" t="n">
-        <v>375</v>
+        <v>248</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>慢</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -13058,12 +13972,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AV-奶香香</t>
+          <t>🔞-大奶子-</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://Naixxzy.com/api.php/provide/vod</t>
+          <t>https://apidanaizi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -13073,35 +13987,35 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>[换脸]孙彩瑛 热热的骚逼..</t>
+          <t>【最新自录-清纯甜美二次元美少女】白裙情趣装罕见</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>903</v>
+        <v>571</v>
       </c>
       <c r="F71" t="n">
-        <v>335</v>
+        <v>223</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>慢</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AV-精品资源</t>
+          <t>AV-奥斯卡资源</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://www.jingpinx.com/api.php/provide/vod</t>
+          <t>https://aosikazy.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -13111,14 +14025,14 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>純潔的輪舞曲_2</t>
+          <t>真实与后妈乱伦9个月</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>480</v>
+        <v>665</v>
       </c>
       <c r="F72" t="n">
-        <v>238</v>
+        <v>178</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -13134,12 +14048,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>🔞-大奶子-</t>
+          <t>🔞小鸡资源</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://apidanaizi.com/api.php/provide/vod</t>
+          <t>https://api.xiaojizy.live/provide/vod</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -13149,14 +14063,14 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>【最新自录-清纯甜美二次元美少女】白裙情趣装罕见</t>
+          <t>李素英合3</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>542</v>
+        <v>281</v>
       </c>
       <c r="F73" t="n">
-        <v>222</v>
+        <v>176</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -13165,19 +14079,19 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AV-奥斯卡资源</t>
+          <t>🔞黑料资源</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://aosikazy.com/api.php/provide/vod</t>
+          <t>https://www.heiliaozyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -13187,14 +14101,14 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>真实与后妈乱伦9个月</t>
+          <t>绿播福利姬女神下海硬控你十分钟一看就高端货超美脸</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>603</v>
+        <v>985</v>
       </c>
       <c r="F74" t="n">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -13210,12 +14124,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>🔞小鸡资源</t>
+          <t>AV-91麻豆</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://api.xiaojizy.live/provide/vod</t>
+          <t>https://91md.me/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -13225,14 +14139,14 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>李素英合3</t>
+          <t>被老师欺负的黑丝女高-桥本香菜</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>308</v>
+        <v>2328</v>
       </c>
       <c r="F75" t="n">
-        <v>170</v>
+        <v>129</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -13241,19 +14155,19 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>🔞黑料资源</t>
+          <t>AV-精品资源</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://www.heiliaozyapi.com/api.php/provide/vod</t>
+          <t>https://www.jingpinx.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -13263,14 +14177,14 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>绿播福利姬女神下海硬控你十分钟一看就高端货超美脸</t>
+          <t>純潔的輪舞曲_2</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>929</v>
+        <v>444</v>
       </c>
       <c r="F76" t="n">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -13286,12 +14200,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AV-91麻豆</t>
+          <t>AV-souav资源</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://91md.me/api.php/provide/vod</t>
+          <t>https://api.souavzy.vip/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -13301,18 +14215,20 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>被老师欺负的黑丝女高-桥本香菜</t>
+          <t>白嫩美女月月无套内射初体验</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1284</v>
-      </c>
-      <c r="F77" t="n">
-        <v>130</v>
+        <v>307</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>慢</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -13324,12 +14240,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AV-souav资源</t>
+          <t>黄色资源啊啊</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://api.souavzy.vip/api.php/provide/vod</t>
+          <t>https://hsckzy888.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -13339,11 +14255,13 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>白嫩美女月月无套内射初体验</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>708</v>
+          <t>公共厕所肉便器 我二话 高岭千佳</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -13352,7 +14270,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>未测出</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -13364,12 +14282,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>黄色资源啊啊</t>
+          <t>🔞黄色仓库</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://hsckzy888.com/api.php/provide/vod</t>
+          <t>https://hsckzy.xyz/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -13406,12 +14324,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>🔞黄色仓库</t>
+          <t>🔞souavZY</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://hsckzy.xyz/api.php/provide/vod</t>
+          <t>https://api.souavzyw.net/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -13421,13 +14339,11 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>公共厕所肉便器 我二话 高岭千佳</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>与儿子所在托儿所的巨乳人妻老师缠绵做爱～老师太过</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>455</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -13436,7 +14352,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -13478,46 +14394,6 @@
         </is>
       </c>
       <c r="H81" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>🔞souavZY</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>https://api.souavzyw.net/api.php/provide/vod</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>与儿子所在托儿所的巨乳人妻老师缠绵做爱～老师太过</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>475</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>样例过小</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
         <is>
           <t>是</t>
         </is>

--- a/output/源清单.xlsx
+++ b/output/源清单.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N118"/>
+  <dimension ref="A1:O118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.6" customWidth="1" min="1" max="1"/>
@@ -446,8 +446,9 @@
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="60" customWidth="1" min="13" max="13"/>
-    <col width="52.8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="52.8" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -508,15 +509,20 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>软性栏目数</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>归属</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>分类名</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
@@ -559,7 +565,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3727</v>
+        <v>1017</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -568,23 +574,26 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>仅完整版</t>
-        </is>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 台湾剧 | 韩国剧 | 欧美剧 | 香港剧 | 泰国剧 | 日本剧 | 福利 | 记录片</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置</t>
         </is>
@@ -627,7 +636,7 @@
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -642,17 +651,20 @@
       <c r="K3" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>无码专区 | 麻豆传媒 | 制服诱惑 | 三级伦理 | AI换脸 | 中文字幕 | 卡通动漫 | 欧美系列 | 美女主播 | 国产自拍 | 熟女人妻 | 萝莉少女 | 女同性爱 | 多人群交 | 美乳巨乳 | 强奸乱伦 | 生活都市 | 不偷恋情 | 学生校园 | 人妻熟女</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -695,7 +707,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2150</v>
+        <v>2109</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -704,23 +716,26 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
         <v>1</v>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>仅完整版</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 伦理片 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 韩国剧 | 欧美剧 | 体育 | NBA | 惊悚片 | 家庭篇</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,cmliu配置</t>
         </is>
@@ -763,7 +778,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>523</v>
+        <v>501</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -772,23 +787,26 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
         <v>1</v>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>仅完整版</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>伦理片 | 教程</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -831,7 +849,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>937</v>
+        <v>871</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -840,23 +858,26 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>仅完整版</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 港澳剧 | 日剧 | 欧美剧 | 动漫电影 | 台湾剧 | 韩剧 | 泰剧 | 记录片</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库3,cmliu配置</t>
         </is>
@@ -899,7 +920,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>798</v>
+        <v>865</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -908,23 +929,26 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>仅完整版</t>
-        </is>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 港澳剧 | 日剧 | 欧美剧 | 动漫电影 | 台湾剧 | 韩剧 | 泰剧 | 记录片</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置,sp696</t>
         </is>
@@ -967,7 +991,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>633</v>
+        <v>287</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -976,23 +1000,26 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>是(硬核)</t>
         </is>
       </c>
       <c r="K8" t="n">
         <v>1</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>仅完整版</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 伦理片 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 惊悚片 | 家庭片 | 古装片 | 历史片 | 悬疑片 | 犯罪片 | 灾难片 | 记录片</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -1030,7 +1057,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>540</v>
+        <v>65</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1039,23 +1066,26 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>是(硬核)</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
-      </c>
-      <c r="L9" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4</v>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>仅完整版</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 资讯 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 台湾剧 | 美国剧 | 公告 | 头条 | 伦理片 | 纪录片</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置</t>
         </is>
@@ -1098,7 +1128,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>637</v>
+        <v>652</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1107,23 +1137,26 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>是(硬核)</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>6</v>
-      </c>
-      <c r="L10" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>4</v>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>仅完整版</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 欧美剧 | 韩剧 | 日剧 | 港剧 | 台剧 | 泰剧 | 纪录片 | 海外剧</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置,sp696</t>
         </is>
@@ -1166,7 +1199,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1175,23 +1208,26 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>1</v>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>仅完整版</t>
-        </is>
-      </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 剧情片 | 恐怖片 | 战争片 | 大陆剧 | 欧美剧 | 港澳剧 | 韩剧 | 动漫电影 | 日剧 | 台湾剧 | 泰剧 | 记录片</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置,sp696</t>
         </is>
@@ -1234,7 +1270,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1249,12 +1285,15 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>人版</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -1309,12 +1348,15 @@
       <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>人版</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -1357,7 +1399,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1372,12 +1414,15 @@
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t>人版</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,sp696</t>
         </is>
@@ -1420,7 +1465,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>491</v>
+        <v>376</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1429,23 +1474,26 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>仅完整版</t>
-        </is>
-      </c>
       <c r="M15" t="inlineStr">
         <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 欧美剧 | 韩国剧 | 日本剧 | 港台剧 | 台湾剧 | 泰国剧 | 纪录片 | 海外剧</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,cmliu配置</t>
         </is>
@@ -1488,7 +1536,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5967</v>
+        <v>2804</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1497,23 +1545,26 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>仅完整版</t>
-        </is>
-      </c>
       <c r="M16" t="inlineStr">
         <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
           <t>电影片 | 连续剧 | 综艺片 | 动漫片 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 韩国剧 | 欧美剧 | 记录片 | 台湾剧 | 日本剧 | 海外剧 | 泰国剧</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,sp696</t>
         </is>
@@ -1573,12 +1624,15 @@
       <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t>人版</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版</t>
         </is>
@@ -1621,7 +1675,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1630,23 +1684,26 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>仅完整版</t>
-        </is>
-      </c>
       <c r="M18" t="inlineStr">
         <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
           <t>电影 | 电视剧 | 动漫 | 综艺 | 纪录片 | 动作片 | 爱情片 | 科幻片 | 战争片 | 剧情片 | 恐怖片 | 喜剧片 | 大陆剧 | 港澳剧 | 台湾剧 | 欧美剧 | 动画片 | 韩剧 | 日剧 | 泰剧</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -1689,7 +1746,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>693</v>
+        <v>167</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1698,23 +1755,26 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>是(硬核)</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
-      </c>
-      <c r="L19" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>4</v>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t>仅完整版</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 资讯 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 台湾剧 | 美国剧 | 公告 | 头条 | 伦理片 | 纪录片</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置,sp696</t>
         </is>
@@ -1757,7 +1817,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>67</v>
+        <v>399</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1766,23 +1826,26 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>是(硬核)</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>6</v>
-      </c>
-      <c r="L20" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>4</v>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t>仅完整版</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 资讯 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 台湾剧 | 美国剧 | 公告 | 头条 | 伦理片 | 纪录片</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -1820,7 +1883,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>418</v>
+        <v>597</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1829,23 +1892,26 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>是(硬核)</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>6</v>
-      </c>
-      <c r="L21" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>4</v>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t>仅完整版</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 资讯 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 台湾剧 | 美国剧 | 公告 | 头条 | 伦理片 | 纪录片</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置</t>
         </is>
@@ -1888,7 +1954,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>806</v>
+        <v>871</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1903,12 +1969,15 @@
       <c r="K22" t="n">
         <v>0</v>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t>人版</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,sp696</t>
         </is>
@@ -1951,7 +2020,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>678</v>
+        <v>957</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1966,12 +2035,15 @@
       <c r="K23" t="n">
         <v>0</v>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t>人版</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -2014,7 +2086,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>509</v>
+        <v>600</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2023,23 +2095,26 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>仅完整版</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>2</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
           <t>电影片 | 动作片 | 喜剧片 | 恐怖片 | 科幻片 | 爱情片 | 剧情片 | 战争片 | 纪录片 | 理论片 | 连续剧 | 国产剧 | 欧美剧 | 香港剧 | 韩国剧 | 台湾剧 | 日本剧 | 海外剧 | 泰国剧 | 动漫片</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -2091,23 +2166,26 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>是(硬核)</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>6</v>
-      </c>
-      <c r="L25" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="L25" t="n">
+        <v>4</v>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t>仅完整版</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 欧美剧 | 韩剧 | 日剧 | 港剧 | 台剧 | 泰剧 | 纪录片 | 海外剧</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置,sp696</t>
         </is>
@@ -2150,7 +2228,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2159,23 +2237,26 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>是(硬核)</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>6</v>
-      </c>
-      <c r="L26" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="L26" t="n">
+        <v>4</v>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t>仅完整版</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 欧美剧 | 韩剧 | 日剧 | 港剧 | 台剧 | 泰剧 | 纪录片 | 海外剧</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -2218,7 +2299,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2227,23 +2308,26 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>1</v>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>仅完整版</t>
-        </is>
-      </c>
       <c r="M27" t="inlineStr">
         <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 资讯 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 台湾剧 | 韩国剧 | 公告 | 头条 | 犯罪片 | 纪录片</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -2281,7 +2365,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1685</v>
+        <v>1603</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2290,23 +2374,26 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
         <v>2</v>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>仅完整版</t>
-        </is>
-      </c>
       <c r="M28" t="inlineStr">
         <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
           <t>动漫 | 综艺 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 战争片 | 国产剧 | 香港剧 | 欧美剧 | 日本剧 | 海外剧 | 台湾剧 | 韩国剧 | 泰国剧 | 剧情片 | 纪录片 | 动画片 | 微电影</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -2349,7 +2436,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>429</v>
+        <v>411</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2358,23 +2445,26 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>是(硬核)</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>6</v>
-      </c>
-      <c r="L29" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="L29" t="n">
+        <v>4</v>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t>仅完整版</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 欧美剧 | 韩剧 | 日剧 | 港剧 | 台剧 | 泰剧 | 纪录片 | 海外剧</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置</t>
         </is>
@@ -2417,7 +2507,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>789</v>
+        <v>629</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2426,23 +2516,26 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>仅完整版</t>
-        </is>
-      </c>
       <c r="M30" t="inlineStr">
         <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
           <t>电影片 | 连续剧 | 综艺片 | 动漫片 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 韩国剧 | 欧美剧 | 记录片 | 台湾剧 | 日本剧 | 海外剧 | 泰国剧</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -2502,13 +2595,16 @@
       <c r="K31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="L31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -2551,7 +2647,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>550</v>
+        <v>664</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2560,23 +2656,26 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>是(硬核)</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>6</v>
-      </c>
-      <c r="L32" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="L32" t="n">
+        <v>4</v>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t>仅完整版</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 大陆剧 | 欧美剧 | 韩剧 | 日剧 | 港澳剧 | 台湾剧 | 泰剧 | 纪录片 | 其他剧</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库3,cmliu配置</t>
         </is>
@@ -2619,7 +2718,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>725</v>
+        <v>900</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2628,23 +2727,26 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
         <v>1</v>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>仅完整版</t>
-        </is>
-      </c>
       <c r="M33" t="inlineStr">
         <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 台湾剧 | 韩国剧 | 欧美剧 | 香港剧 | 泰国剧 | 日本剧 | 福利 | 记录片</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库3,cmliu配置</t>
         </is>
@@ -2687,7 +2789,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2696,23 +2798,26 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>是(硬核)</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>6</v>
-      </c>
-      <c r="L34" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="L34" t="n">
+        <v>4</v>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t>仅完整版</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 欧美剧 | 韩剧 | 日剧 | 港剧 | 台剧 | 泰剧 | 纪录片 | 海外剧</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置,sp696</t>
         </is>
@@ -2755,7 +2860,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>459</v>
+        <v>548</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2764,23 +2869,26 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
         <v>1</v>
       </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>仅完整版</t>
-        </is>
-      </c>
       <c r="M35" t="inlineStr">
         <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 港澳剧 | 日剧 | 欧美剧 | 台湾剧 | 泰剧 | 韩剧 | 纪录片 | 动漫电影</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -2823,7 +2931,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1244</v>
+        <v>1297</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2832,23 +2940,26 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
         <v>1</v>
       </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>仅完整版</t>
-        </is>
-      </c>
       <c r="M36" t="inlineStr">
         <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
           <t>电影 | 连续剧 | 综艺片 | 动漫 | 纪录片 | 动作片 | 爱情片 | 喜剧片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 欧美剧 | 韩剧 | 动漫电影 | 泰国剧 | 日本剧 | 台湾剧</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,sp696</t>
         </is>
@@ -2891,7 +3002,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>684</v>
+        <v>727</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2900,23 +3011,26 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
         <v>1</v>
       </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>仅完整版</t>
-        </is>
-      </c>
       <c r="M37" t="inlineStr">
         <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
           <t>电视剧 | 电影 | 欧美剧 | 香港剧 | 韩剧 | 日剧 | 马泰剧 | 伦理片 | 动作片 | 爱情片 | 喜剧片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 记录片 | 动漫 | 内地剧 | 动画片 | 中国动漫</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置,sp696</t>
         </is>
@@ -2976,12 +3090,15 @@
       <c r="K38" t="n">
         <v>0</v>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t>人版</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -3024,7 +3141,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>914</v>
+        <v>989</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -3033,23 +3150,26 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
         <v>1</v>
       </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>仅完整版</t>
-        </is>
-      </c>
       <c r="M39" t="inlineStr">
         <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
           <t>电影 | 连续剧 | 综艺片 | 动漫 | 纪录片 | 动作片 | 爱情片 | 喜剧片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 欧美剧 | 韩剧 | 动漫电影 | 泰国剧 | 日本剧 | 台湾剧</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,cmliu配置</t>
         </is>
@@ -3092,7 +3212,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -3101,23 +3221,26 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
         <v>1</v>
       </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>仅完整版</t>
-        </is>
-      </c>
       <c r="M40" t="inlineStr">
         <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
           <t>电视剧 | 电影 | 欧美剧 | 香港剧 | 韩剧 | 日剧 | 马泰剧 | 伦理片 | 动作片 | 爱情片 | 喜剧片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 记录片 | 动漫 | 内地剧 | 动画片 | 中国动漫</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -3160,7 +3283,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -3169,23 +3292,26 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
         <v>1</v>
       </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>仅完整版</t>
-        </is>
-      </c>
       <c r="M41" t="inlineStr">
         <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
           <t>电影 | 电视剧 | 动漫 | 综艺 | 纪录片 | 动作片 | 爱情片 | 科幻片 | 战争片 | 剧情片 | 恐怖片 | 喜剧片 | 动漫电影 | 大陆剧 | 台湾剧 | 韩剧 | 美剧 | 港澳剧 | 日剧 | 泰剧</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -3228,7 +3354,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>614</v>
+        <v>1023</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -3237,23 +3363,26 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
         <v>1</v>
       </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>仅完整版</t>
-        </is>
-      </c>
       <c r="M42" t="inlineStr">
         <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
           <t>电影片 | 连续剧 | 综艺片 | 动漫片 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 韩国剧 | 欧美剧 | 记录片 | 台湾剧 | 日本剧 | 海外剧 | 泰国剧</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -3296,7 +3425,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3305,23 +3434,26 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
         <v>1</v>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>仅完整版</t>
-        </is>
-      </c>
       <c r="M43" t="inlineStr">
         <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
           <t>电视剧 | 电影 | 欧美剧 | 香港剧 | 韩剧 | 日剧 | 马泰剧 | 伦理片 | 动作片 | 爱情片 | 喜剧片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 记录片 | 动漫 | 内地剧 | 动画片 | 中国动漫</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -3364,7 +3496,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>524</v>
+        <v>1102</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3373,23 +3505,26 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
         <v>1</v>
       </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>仅完整版</t>
-        </is>
-      </c>
       <c r="M44" t="inlineStr">
         <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
           <t>电视剧 | 电影 | 欧美剧 | 香港剧 | 韩剧 | 日剧 | 马泰剧 | 伦理片 | 动作片 | 爱情片 | 喜剧片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 记录片 | 动漫 | 内地剧 | 动画片 | 中国动漫</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置</t>
         </is>
@@ -3432,7 +3567,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>530</v>
+        <v>549</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3441,23 +3576,26 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>是(硬核)</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>6</v>
-      </c>
-      <c r="L45" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="L45" t="n">
+        <v>4</v>
+      </c>
+      <c r="M45" t="inlineStr">
         <is>
           <t>仅完整版</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 欧美剧 | 韩剧 | 日剧 | 港剧 | 台剧 | 泰剧 | 纪录片 | 海外剧</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置</t>
         </is>
@@ -3491,20 +3629,20 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>无法探测→按普通处理</t>
+          <t>分类实测</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>存活/非标准</t>
+          <t>存活</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>2388</v>
+        <v>3529</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>动漫/影视/短剧</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3515,12 +3653,20 @@
       <c r="K46" t="n">
         <v>0</v>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="L46" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t>人版</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
+        <is>
+          <t>电影片 | 连续剧 | 综艺片 | 动漫片 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 韩国剧 | 欧美剧 | 记录片 | 台湾剧 | 日本剧 | 海外剧 | 泰国剧</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -3580,12 +3726,15 @@
       <c r="K47" t="n">
         <v>0</v>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="inlineStr">
         <is>
           <t>人版</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -3645,12 +3794,15 @@
       <c r="K48" t="n">
         <v>0</v>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t>人版</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3</t>
         </is>
@@ -3693,7 +3845,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>628</v>
+        <v>1018</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3702,23 +3854,26 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>是(硬核)</t>
         </is>
       </c>
       <c r="K49" t="n">
         <v>1</v>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="L49" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t>仅完整版</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>国产动漫 | 日韩动漫 | 欧美动漫 | 港台动漫 | 动漫电影 | 里番动漫 | 电影 | 连续剧 | 综艺 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 惊悚片 | 家庭片 | 古装片 | 历史片</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置,sp696</t>
         </is>
@@ -3761,7 +3916,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>956</v>
+        <v>1010</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3770,23 +3925,26 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>是(硬核)</t>
         </is>
       </c>
       <c r="K50" t="n">
         <v>1</v>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="L50" t="n">
+        <v>1</v>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t>仅完整版</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>国产动漫 | 日韩动漫 | 欧美动漫 | 港台动漫 | 动漫电影 | 里番动漫 | 电影 | 连续剧 | 综艺 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 惊悚片 | 家庭片 | 古装片 | 历史片</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -3829,7 +3987,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3844,12 +4002,15 @@
       <c r="K51" t="n">
         <v>0</v>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t>人版</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版</t>
         </is>
@@ -3892,7 +4053,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3907,12 +4068,15 @@
       <c r="K52" t="n">
         <v>0</v>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="inlineStr">
         <is>
           <t>人版</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -3955,7 +4119,7 @@
         </is>
       </c>
       <c r="H53" s="2" t="n">
-        <v>1060</v>
+        <v>776</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
@@ -3970,17 +4134,20 @@
       <c r="K53" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="L53" s="2" t="inlineStr">
+      <c r="L53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M53" s="2" t="inlineStr">
+      <c r="N53" s="2" t="inlineStr">
         <is>
           <t>麻豆视频 | 91制片厂 | 天美传媒 | 蜜桃传媒 | 皇家华人 | 星空传媒 | 精东影业 | 海角社区 | 成人头条 | 乌鸦传媒 | 兔子先生 | 杏吧原创 | 玩偶姐姐 | mini传媒 | 大象传媒 | 91视频 | PsychoPorn | 糖心Vlog | 萝莉社 | 性视界</t>
         </is>
       </c>
-      <c r="N53" s="2" t="inlineStr">
+      <c r="O53" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -4036,13 +4203,16 @@
       <c r="K54" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L54" s="2" t="inlineStr">
+      <c r="L54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M54" s="2" t="inlineStr"/>
-      <c r="N54" s="2" t="inlineStr">
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -4085,7 +4255,7 @@
         </is>
       </c>
       <c r="H55" s="2" t="n">
-        <v>195</v>
+        <v>275</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
@@ -4100,17 +4270,20 @@
       <c r="K55" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="L55" s="2" t="inlineStr">
+      <c r="L55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M55" s="2" t="inlineStr">
+      <c r="N55" s="2" t="inlineStr">
         <is>
           <t>中文字幕 | 日本有码 | 日本无码 | AV解说 | cosplay | 都市激情 | 校园情事 | 人妻纵情 | 风俗伦理 | 另类小说 | 武侠古典 | 长篇连载 | 黑丝诱惑 | SWAG | 自拍偷拍 | 激情动漫 | 网红主播 | 探花系列 | 三级伦理 | VR视角</t>
         </is>
       </c>
-      <c r="N55" s="2" t="inlineStr">
+      <c r="O55" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -4153,7 +4326,7 @@
         </is>
       </c>
       <c r="H56" s="2" t="n">
-        <v>793</v>
+        <v>761</v>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
@@ -4166,19 +4339,22 @@
         </is>
       </c>
       <c r="K56" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
+        <v>36</v>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M56" s="2" t="inlineStr">
+      <c r="N56" s="2" t="inlineStr">
         <is>
           <t>中文传媒 | 国产 | 欧美AV | 日本AV | 传媒-麻豆传媒 | 传媒-精东影业 | 传媒-蜜桃传媒 | 传媒-果冻传媒 | 传媒-星空无限传媒 | 传媒-SA国际传媒 | 传媒-性视界传媒 | 国产-自拍 | 国产-偷拍 | 国产-探花 | 国产-主播 | 传媒-天美传媒 | 欧美-高清无码 | 欧美-高清有码 | 日本-中文字幕 | 日本-无码流出</t>
         </is>
       </c>
-      <c r="N56" s="2" t="inlineStr">
+      <c r="O56" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -4221,7 +4397,7 @@
         </is>
       </c>
       <c r="H57" s="2" t="n">
-        <v>947</v>
+        <v>840</v>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
@@ -4234,19 +4410,22 @@
         </is>
       </c>
       <c r="K57" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M57" s="2" t="inlineStr">
+      <c r="N57" s="2" t="inlineStr">
         <is>
           <t>亚洲情色 | 国产主播 | 国产自拍 | 无码专区 | 欧美性爱 | 熟女人妻 | 强奸乱伦 | 巨乳美乳 | 中文字幕 | 制服诱惑 | 女同性恋 | 卡通动画 | 视频伦理 | 少女萝莉 | 重口色情 | 人兽性交 | 福利姬</t>
         </is>
       </c>
-      <c r="N57" s="2" t="inlineStr">
+      <c r="O57" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -4289,7 +4468,7 @@
         </is>
       </c>
       <c r="H58" s="2" t="n">
-        <v>1028</v>
+        <v>798</v>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
@@ -4304,17 +4483,20 @@
       <c r="K58" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="L58" s="2" t="inlineStr">
+      <c r="L58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M58" s="2" t="inlineStr">
+      <c r="N58" s="2" t="inlineStr">
         <is>
           <t>国产视频 | 中文字幕 | 国产传媒 | 日本有码 | 日本无码 | 欧美无码 | 强奸乱伦 | 制服诱惑 | 国产主播 | 激情动漫 | 明星换脸 | 抖阴视频 | 女优明星 | 视频一区 | 视频二区 | 网曝黑料 | 视频三区 | 伦理三级 | AV解说 | SM调教</t>
         </is>
       </c>
-      <c r="N58" s="2" t="inlineStr">
+      <c r="O58" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -4357,7 +4539,7 @@
         </is>
       </c>
       <c r="H59" s="2" t="n">
-        <v>1013</v>
+        <v>1587</v>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
@@ -4370,19 +4552,22 @@
         </is>
       </c>
       <c r="K59" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
+        <v>11</v>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M59" s="2" t="inlineStr">
+      <c r="N59" s="2" t="inlineStr">
         <is>
           <t>精品国产 | 精品日韩 | 精品综合 | 精品小说 | 精品美图 | 国产自拍 | 主播诱惑 | 探花约炮 | 偷拍偷窥 | 网曝吃瓜 | 抖阴短片 | 传媒剧情 | 日韩主播 | 日韩无码 | 中文字幕 | AV解说 | 换脸明星 | 强奸乱伦 | 女优明星 | 欧美激情</t>
         </is>
       </c>
-      <c r="N59" s="2" t="inlineStr">
+      <c r="O59" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -4425,7 +4610,7 @@
         </is>
       </c>
       <c r="H60" s="2" t="n">
-        <v>753</v>
+        <v>2193</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
@@ -4440,17 +4625,20 @@
       <c r="K60" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="L60" s="2" t="inlineStr">
+      <c r="L60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M60" s="2" t="inlineStr">
+      <c r="N60" s="2" t="inlineStr">
         <is>
           <t>精品推荐 | 国产色情 | 主播直播 | 亚洲无码 | 亚洲有码 | 中文字幕 | 巨乳美乳 | 人妻熟女 | 强奸乱伦 | 欧美精品 | 萝莉少女 | 伦理三级 | 成人动漫 | 自拍偷拍 | 制服丝袜 | 口交颜射 | 日本精品 | Cosplay | 素人自拍 | 台湾辣妹</t>
         </is>
       </c>
-      <c r="N60" s="2" t="inlineStr">
+      <c r="O60" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置</t>
         </is>
@@ -4493,7 +4681,7 @@
         </is>
       </c>
       <c r="H61" s="2" t="n">
-        <v>1266</v>
+        <v>884</v>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
@@ -4508,13 +4696,16 @@
       <c r="K61" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L61" s="2" t="inlineStr">
+      <c r="L61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M61" s="2" t="inlineStr"/>
-      <c r="N61" s="2" t="inlineStr">
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -4557,7 +4748,7 @@
         </is>
       </c>
       <c r="H62" s="2" t="n">
-        <v>602</v>
+        <v>406</v>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
@@ -4572,17 +4763,20 @@
       <c r="K62" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="L62" s="2" t="inlineStr">
+      <c r="L62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M62" s="2" t="inlineStr">
+      <c r="N62" s="2" t="inlineStr">
         <is>
           <t>精品推荐 | 国产精品 | 主播秀色 | 日本有码 | 日本无码 | 中文字幕 | 童颜巨乳 | 性感人妻 | 强奸乱伦 | 欧美情色 | 三级伦理 | 卡通动漫 | 丝袜OL | 自拍偷拍 | 日本片商 | 剧情介绍 | 网曝系列 | 麻豆传媒 | 明星换脸 | 国产乱伦</t>
         </is>
       </c>
-      <c r="N62" s="2" t="inlineStr">
+      <c r="O62" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -4625,7 +4819,7 @@
         </is>
       </c>
       <c r="H63" s="2" t="n">
-        <v>726</v>
+        <v>881</v>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
@@ -4640,17 +4834,20 @@
       <c r="K63" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="L63" s="2" t="inlineStr">
+      <c r="L63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M63" s="2" t="inlineStr">
+      <c r="N63" s="2" t="inlineStr">
         <is>
           <t>制服丝袜 | 群交淫乱 | 无码专区 | 偷拍自拍 | 卡通动漫 | 中文字幕 | 欧美性爱 | 巨乳美乳 | 国产裸聊 | 国产自拍 | 国产盗摄 | 伦理三级 | 女同性恋 | 少女萝莉 | 人妖系列 | 虚拟VR | 亚州图片 | 欧美图片 | 美腿丝袜 | 网友自拍</t>
         </is>
       </c>
-      <c r="N63" s="2" t="inlineStr">
+      <c r="O63" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -4693,7 +4890,7 @@
         </is>
       </c>
       <c r="H64" s="2" t="n">
-        <v>1038</v>
+        <v>851</v>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
@@ -4708,13 +4905,16 @@
       <c r="K64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L64" s="2" t="inlineStr">
+      <c r="L64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M64" s="2" t="inlineStr"/>
-      <c r="N64" s="2" t="inlineStr">
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -4757,7 +4957,7 @@
         </is>
       </c>
       <c r="H65" s="2" t="n">
-        <v>594</v>
+        <v>466</v>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
@@ -4772,17 +4972,20 @@
       <c r="K65" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="L65" s="2" t="inlineStr">
+      <c r="L65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M65" s="2" t="inlineStr">
+      <c r="N65" s="2" t="inlineStr">
         <is>
           <t>国产 | 日本 | 欧美 | 动漫 | 偷拍自拍 | 国产大制作 | 乱伦毁三观 | 嫖妓全过程 | 淫乱学生妹 | 黑料不打烊 | 监控摄像头 | 主播网红 | 高清无码 | 中文字幕 | 成人综艺 | 媚黑母狗 | 为国争光 | 少女破处 | 人兽典藏 | 中文剧情</t>
         </is>
       </c>
-      <c r="N65" s="2" t="inlineStr">
+      <c r="O65" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -4825,7 +5028,7 @@
         </is>
       </c>
       <c r="H66" s="2" t="n">
-        <v>804</v>
+        <v>1009</v>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
@@ -4840,13 +5043,16 @@
       <c r="K66" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L66" s="2" t="inlineStr">
+      <c r="L66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M66" s="2" t="inlineStr"/>
-      <c r="N66" s="2" t="inlineStr">
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -4889,7 +5095,7 @@
         </is>
       </c>
       <c r="H67" s="2" t="n">
-        <v>713</v>
+        <v>755</v>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
@@ -4904,17 +5110,20 @@
       <c r="K67" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="L67" s="2" t="inlineStr">
+      <c r="L67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M67" s="2" t="inlineStr">
+      <c r="N67" s="2" t="inlineStr">
         <is>
           <t>精品推荐 | 国产精品 | 主播秀色 | 日本有码 | 日本无码 | 中文字幕 | 童颜巨乳 | 性感人妻 | 强奸乱伦 | 欧美情色 | 三级伦理 | 卡通动漫 | 丝袜OL | 自拍偷拍 | 日本片商 | 剧情介绍 | 网曝系列 | 麻豆传媒 | 明星换脸 | 国产乱伦</t>
         </is>
       </c>
-      <c r="N67" s="2" t="inlineStr">
+      <c r="O67" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -4974,13 +5183,16 @@
       <c r="K68" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L68" s="2" t="inlineStr">
+      <c r="L68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M68" s="2" t="inlineStr"/>
-      <c r="N68" s="2" t="inlineStr">
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -5040,13 +5252,16 @@
       <c r="K69" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L69" s="2" t="inlineStr">
+      <c r="L69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M69" s="2" t="inlineStr"/>
-      <c r="N69" s="2" t="inlineStr">
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -5089,7 +5304,7 @@
         </is>
       </c>
       <c r="H70" s="2" t="n">
-        <v>829</v>
+        <v>898</v>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
@@ -5104,17 +5319,20 @@
       <c r="K70" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="L70" s="2" t="inlineStr">
+      <c r="L70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M70" s="2" t="inlineStr">
+      <c r="N70" s="2" t="inlineStr">
         <is>
           <t>国产自拍 | 欧美极品 | 日韩无码 | AV明星 | 公告 | 头条 | 中文字幕 | 动漫精品 | 极骚萝莉 | 人妖视频 | 重咸口味 | 三级自慰 | 强奸乱伦 | 独家擂台格斗 | 辣椒GIGA | HEYZO | 独家DMM | HEY诱惑 | 童颜巨乳 | 高潮喷吹</t>
         </is>
       </c>
-      <c r="N70" s="2" t="inlineStr">
+      <c r="O70" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -5157,7 +5375,7 @@
         </is>
       </c>
       <c r="H71" s="2" t="n">
-        <v>871</v>
+        <v>786</v>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
@@ -5172,13 +5390,16 @@
       <c r="K71" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L71" s="2" t="inlineStr">
+      <c r="L71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M71" s="2" t="inlineStr"/>
-      <c r="N71" s="2" t="inlineStr">
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -5212,22 +5433,20 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>域名/标记</t>
+          <t>上游标记</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>失活</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>存活</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>5519</v>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>动漫</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -5236,15 +5455,22 @@
         </is>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" s="2" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="L72" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M72" s="2" t="inlineStr"/>
       <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>国产情色 | 日本无码 | AV明星 | 中文字幕 | 网红主播 | 成人动漫 | 欧美情色 | 国模私拍 | 长腿丝袜 | 邻家人妻 | 韩国伦理 | 香港伦理 | 精品推荐 | 原纱央莉 | 柚木TINA | 大桥未久 | AV明星1 | 仁科百华 | 天海翼 | 小川阿佐美</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -5287,7 +5513,7 @@
         </is>
       </c>
       <c r="H73" s="2" t="n">
-        <v>720</v>
+        <v>568</v>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
@@ -5302,13 +5528,16 @@
       <c r="K73" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L73" s="2" t="inlineStr">
+      <c r="L73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M73" s="2" t="inlineStr"/>
-      <c r="N73" s="2" t="inlineStr">
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -5351,7 +5580,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>2264</v>
+        <v>3907</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -5360,23 +5589,26 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
         <v>1</v>
       </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>仅完整版</t>
-        </is>
-      </c>
       <c r="M74" t="inlineStr">
         <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
           <t>电影片 | 连续剧 | 综艺片 | 动漫片 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 韩国剧 | 欧美剧 | 记录片 | 台湾剧 | 日本剧 | 海外剧 | 泰国剧</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
+      <c r="O74" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -5419,7 +5651,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>298</v>
+        <v>431</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -5428,23 +5660,26 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
         <v>1</v>
       </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>仅完整版</t>
-        </is>
-      </c>
       <c r="M75" t="inlineStr">
         <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
           <t>电视剧 | 电影 | 欧美剧 | 香港剧 | 韩剧 | 日剧 | 马泰剧 | 伦理片 | 动作片 | 爱情片 | 喜剧片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 记录片 | 动漫 | 内地剧 | 动画片 | 中国动漫</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t>仓库1-增强版,仓库2-基础版,仓库3,cmliu配置,sp696</t>
         </is>
@@ -5500,13 +5735,16 @@
       <c r="K76" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L76" s="2" t="inlineStr">
+      <c r="L76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M76" s="2" t="inlineStr"/>
-      <c r="N76" s="2" t="inlineStr">
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -5536,7 +5774,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>分类实测</t>
+          <t>上游标记</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -5545,11 +5783,11 @@
         </is>
       </c>
       <c r="H77" s="2" t="n">
-        <v>687</v>
+        <v>598</v>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>18禁/动漫</t>
+          <t>动漫</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -5558,19 +5796,22 @@
         </is>
       </c>
       <c r="K77" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
+        <v>17</v>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M77" s="2" t="inlineStr">
+      <c r="N77" s="2" t="inlineStr">
         <is>
           <t>视频一区 | 日韩无码 | 国产主播 | 视频三区 | 日韩精品 | 欧美劲爆 | 成人动漫 | 自拍偷拍 | 伦理影片 | 中文字幕 | 人妻系列 | 制服诱惑 | 强奸乱伦 | AV明星 | SM重味 | 视频二区 | 巨乳尤物 | 颜射系列 | 口交视频 | 自慰系列</t>
         </is>
       </c>
-      <c r="N77" s="2" t="inlineStr">
+      <c r="O77" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置</t>
         </is>
@@ -5625,12 +5866,15 @@
       <c r="K78" t="n">
         <v>0</v>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="inlineStr">
         <is>
           <t>人版</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
+      <c r="O78" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -5686,13 +5930,16 @@
       <c r="K79" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L79" s="2" t="inlineStr">
+      <c r="L79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M79" s="2" t="inlineStr"/>
-      <c r="N79" s="2" t="inlineStr">
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -5748,13 +5995,16 @@
       <c r="K80" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L80" s="2" t="inlineStr">
+      <c r="L80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M80" s="2" t="inlineStr"/>
-      <c r="N80" s="2" t="inlineStr">
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -5792,7 +6042,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>617</v>
+        <v>695</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -5801,23 +6051,26 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
         <v>1</v>
       </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>仅完整版</t>
-        </is>
-      </c>
       <c r="M81" t="inlineStr">
         <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 港澳剧 | 日剧 | 欧美剧 | 台湾剧 | 泰剧 | 韩剧 | 纪录片 | 动漫电影</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr">
+      <c r="O81" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置</t>
         </is>
@@ -5860,7 +6113,7 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -5869,23 +6122,26 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>是(硬核)</t>
         </is>
       </c>
       <c r="K82" t="n">
-        <v>6</v>
-      </c>
-      <c r="L82" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="L82" t="n">
+        <v>4</v>
+      </c>
+      <c r="M82" t="inlineStr">
         <is>
           <t>仅完整版</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 欧美剧 | 韩剧 | 日剧 | 港剧 | 台剧 | 泰剧 | 纪录片 | 海外剧</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr">
+      <c r="O82" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置,sp696</t>
         </is>
@@ -5923,7 +6179,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>342</v>
+        <v>1890</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -5932,23 +6188,26 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
         <v>1</v>
       </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>仅完整版</t>
-        </is>
-      </c>
       <c r="M83" t="inlineStr">
         <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
           <t>电视剧 | 电影 | 欧美剧 | 香港剧 | 韩剧 | 日剧 | 马泰剧 | 伦理片 | 动作片 | 爱情片 | 喜剧片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 记录片 | 动漫 | 内地剧 | 动画片 | 中国动漫</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr">
+      <c r="O83" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -6003,12 +6262,15 @@
       <c r="K84" t="n">
         <v>0</v>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="inlineStr">
         <is>
           <t>人版</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr">
+      <c r="O84" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -6063,12 +6325,15 @@
       <c r="K85" t="n">
         <v>0</v>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="inlineStr">
         <is>
           <t>人版</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr">
+      <c r="O85" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -6106,7 +6371,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>535</v>
+        <v>508</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -6121,12 +6386,15 @@
       <c r="K86" t="n">
         <v>0</v>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="inlineStr">
         <is>
           <t>人版</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr">
+      <c r="O86" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -6165,7 +6433,7 @@
         </is>
       </c>
       <c r="H87" s="2" t="n">
-        <v>406</v>
+        <v>511</v>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
@@ -6180,17 +6448,20 @@
       <c r="K87" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="L87" s="2" t="inlineStr">
+      <c r="L87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M87" s="2" t="inlineStr">
+      <c r="N87" s="2" t="inlineStr">
         <is>
           <t>国产区 | AV区 | 欧美区 | 动漫区 | 网红主播 | 国产传媒 | 探花系列 | 人妻熟女 | 日本无码 | 美乳巨乳 | 强制侵犯 | 制服诱惑 | 绝色佳人 | 风俗泡泡浴 | 家庭乱伦 | AV解说 | 三级电影 | 少女萝莉 | SM调教 | 绝顶潮吹</t>
         </is>
       </c>
-      <c r="N87" s="2" t="inlineStr">
+      <c r="O87" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -6233,7 +6504,7 @@
         </is>
       </c>
       <c r="H88" s="2" t="n">
-        <v>474</v>
+        <v>318</v>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
@@ -6248,17 +6519,20 @@
       <c r="K88" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="L88" s="2" t="inlineStr">
+      <c r="L88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M88" s="2" t="inlineStr">
+      <c r="N88" s="2" t="inlineStr">
         <is>
           <t>国产自拍 | 日韩AV | 欧美精品 | 异族风情 | 动漫专栏 | 强奸迷奸 | 丝袜制服 | 国产厂牌 | SM调教 | 乱伦 | 网曝黑料 | 主播网红 | 自拍偷拍 | 口交自慰 | 群交多P | AI换脸 | 素人特摄 | 无码高清 | 经典有码 | 中文字幕</t>
         </is>
       </c>
-      <c r="N88" s="2" t="inlineStr">
+      <c r="O88" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -6296,7 +6570,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -6311,12 +6585,15 @@
       <c r="K89" t="n">
         <v>0</v>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="inlineStr">
         <is>
           <t>人版</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr">
+      <c r="O89" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -6355,7 +6632,7 @@
         </is>
       </c>
       <c r="H90" s="2" t="n">
-        <v>3854</v>
+        <v>794</v>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
@@ -6370,13 +6647,16 @@
       <c r="K90" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L90" s="2" t="inlineStr">
+      <c r="L90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M90" s="2" t="inlineStr"/>
-      <c r="N90" s="2" t="inlineStr">
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -6414,7 +6694,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>845</v>
+        <v>571</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -6429,12 +6709,15 @@
       <c r="K91" t="n">
         <v>0</v>
       </c>
-      <c r="L91" t="inlineStr">
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="inlineStr">
         <is>
           <t>人版</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr">
+      <c r="O91" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -6468,36 +6751,44 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>无法探测→按普通处理</t>
+          <t>分类实测</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>存活/非标准</t>
+          <t>存活</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>1711</v>
+        <v>2288</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>动漫/影视/短剧</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>是(硬核)</t>
         </is>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>人版</t>
+        <v>1</v>
+      </c>
+      <c r="L92" t="n">
+        <v>1</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>仅完整版</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
+        <is>
+          <t>国产动漫 | 日韩动漫 | 欧美动漫 | 港台动漫 | 动漫电影 | 里番动漫 | 电影 | 连续剧 | 综艺 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 惊悚片 | 家庭片 | 古装片 | 历史片</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置,sp696</t>
         </is>
@@ -6540,7 +6831,7 @@
         </is>
       </c>
       <c r="H93" s="2" t="n">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
@@ -6555,13 +6846,16 @@
       <c r="K93" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L93" s="2" t="inlineStr">
+      <c r="L93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M93" s="2" t="inlineStr"/>
-      <c r="N93" s="2" t="inlineStr">
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -6616,12 +6910,15 @@
       <c r="K94" t="n">
         <v>0</v>
       </c>
-      <c r="L94" t="inlineStr">
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="inlineStr">
         <is>
           <t>人版</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr">
+      <c r="O94" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -6664,7 +6961,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>2227</v>
+        <v>357</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -6673,23 +6970,26 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
         <v>1</v>
       </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>仅完整版</t>
-        </is>
-      </c>
       <c r="M95" t="inlineStr">
         <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
           <t>电影片 | 连续剧 | 综艺片 | 动漫片 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 韩国剧 | 欧美剧 | 记录片 | 台湾剧 | 日本剧 | 海外剧 | 泰国剧</t>
         </is>
       </c>
-      <c r="N95" t="inlineStr">
+      <c r="O95" t="inlineStr">
         <is>
           <t>仓库2-基础版</t>
         </is>
@@ -6732,7 +7032,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>271</v>
+        <v>395</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -6741,23 +7041,26 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>是(硬核)</t>
         </is>
       </c>
       <c r="K96" t="n">
-        <v>6</v>
-      </c>
-      <c r="L96" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="L96" t="n">
+        <v>4</v>
+      </c>
+      <c r="M96" t="inlineStr">
         <is>
           <t>仅完整版</t>
         </is>
       </c>
-      <c r="M96" t="inlineStr">
+      <c r="N96" t="inlineStr">
         <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 欧美剧 | 韩剧 | 日剧 | 港剧 | 台剧 | 泰剧 | 纪录片 | 海外剧</t>
         </is>
       </c>
-      <c r="N96" t="inlineStr">
+      <c r="O96" t="inlineStr">
         <is>
           <t>cmliu配置,sp696</t>
         </is>
@@ -6800,7 +7103,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>633</v>
+        <v>577</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -6809,23 +7112,26 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>是(硬核)</t>
         </is>
       </c>
       <c r="K97" t="n">
         <v>1</v>
       </c>
-      <c r="L97" t="inlineStr">
+      <c r="L97" t="n">
+        <v>1</v>
+      </c>
+      <c r="M97" t="inlineStr">
         <is>
           <t>仅完整版</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr">
+      <c r="N97" t="inlineStr">
         <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 伦理片 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 韩国剧 | 欧美剧 | 体育 | NBA | 惊悚片 | 家庭篇</t>
         </is>
       </c>
-      <c r="N97" t="inlineStr">
+      <c r="O97" t="inlineStr">
         <is>
           <t>cmliu配置,sp696</t>
         </is>
@@ -6868,7 +7174,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>2207</v>
+        <v>632</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -6877,23 +7183,26 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
         <v>1</v>
       </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>仅完整版</t>
-        </is>
-      </c>
       <c r="M98" t="inlineStr">
         <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
           <t>电影片 | 连续剧 | 综艺片 | 动漫片 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 韩国剧 | 欧美剧 | 记录片 | 台湾剧 | 日本剧 | 海外剧 | 泰国剧</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr">
+      <c r="O98" t="inlineStr">
         <is>
           <t>cmliu配置,sp696</t>
         </is>
@@ -6936,7 +7245,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>656</v>
+        <v>756</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -6945,23 +7254,26 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="n">
         <v>1</v>
       </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>仅完整版</t>
-        </is>
-      </c>
       <c r="M99" t="inlineStr">
         <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 伦理片 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 韩国剧 | 欧美剧 | 体育 | NBA | 惊悚片 | 家庭篇</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr">
+      <c r="O99" t="inlineStr">
         <is>
           <t>cmliu配置,sp696</t>
         </is>
@@ -7004,7 +7316,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>790</v>
+        <v>828</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -7013,23 +7325,26 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
         <v>1</v>
       </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>仅完整版</t>
-        </is>
-      </c>
       <c r="M100" t="inlineStr">
         <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
           <t>电影 | 连续剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 台湾剧 | 韩国剧 | 欧美剧 | 香港剧 | 泰国剧 | 日本剧 | 福利 | 记录片</t>
         </is>
       </c>
-      <c r="N100" t="inlineStr">
+      <c r="O100" t="inlineStr">
         <is>
           <t>cmliu配置,sp696</t>
         </is>
@@ -7072,7 +7387,7 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>648</v>
+        <v>1068</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -7081,23 +7396,26 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
         <v>1</v>
       </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>仅完整版</t>
-        </is>
-      </c>
       <c r="M101" t="inlineStr">
         <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
           <t>电影 | 连续剧 | 综艺片 | 动漫 | 纪录片 | 动作片 | 爱情片 | 喜剧片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 欧美剧 | 韩剧 | 动漫电影 | 泰国剧 | 日本剧 | 台湾剧</t>
         </is>
       </c>
-      <c r="N101" t="inlineStr">
+      <c r="O101" t="inlineStr">
         <is>
           <t>cmliu配置,sp696</t>
         </is>
@@ -7140,7 +7458,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -7149,23 +7467,26 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
         <v>1</v>
       </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>仅完整版</t>
-        </is>
-      </c>
       <c r="M102" t="inlineStr">
         <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
           <t>电视剧 | 电影 | 欧美剧 | 香港剧 | 韩剧 | 日剧 | 马泰剧 | 伦理片 | 动作片 | 爱情片 | 喜剧片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 记录片 | 动漫 | 内地剧 | 动画片 | 中国动漫</t>
         </is>
       </c>
-      <c r="N102" t="inlineStr">
+      <c r="O102" t="inlineStr">
         <is>
           <t>cmliu配置</t>
         </is>
@@ -7208,7 +7529,7 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>1395</v>
+        <v>1522</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -7217,23 +7538,26 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>是(硬核)</t>
         </is>
       </c>
       <c r="K103" t="n">
-        <v>8</v>
-      </c>
-      <c r="L103" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="L103" t="n">
+        <v>5</v>
+      </c>
+      <c r="M103" t="inlineStr">
         <is>
           <t>仅完整版</t>
         </is>
       </c>
-      <c r="M103" t="inlineStr">
+      <c r="N103" t="inlineStr">
         <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 福利视频 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 犯罪片 | 战争片 | 国产剧 | 港台剧 | 日韩剧 | 欧美剧 | 三级伦理 | 网红主播 | 动画电影 | 剧情片</t>
         </is>
       </c>
-      <c r="N103" t="inlineStr">
+      <c r="O103" t="inlineStr">
         <is>
           <t>cmliu配置,sp696</t>
         </is>
@@ -7276,7 +7600,7 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>1595</v>
+        <v>1625</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -7285,23 +7609,26 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="n">
         <v>1</v>
       </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>仅完整版</t>
-        </is>
-      </c>
       <c r="M104" t="inlineStr">
         <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
           <t>电影片 | 连续剧 | 综艺片 | 动漫片 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 国产剧 | 香港剧 | 韩国剧 | 欧美剧 | 记录片 | 台湾剧 | 日本剧 | 海外剧 | 泰国剧</t>
         </is>
       </c>
-      <c r="N104" t="inlineStr">
+      <c r="O104" t="inlineStr">
         <is>
           <t>cmliu配置</t>
         </is>
@@ -7344,7 +7671,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>465</v>
+        <v>346</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -7353,23 +7680,26 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>是(硬核)</t>
         </is>
       </c>
       <c r="K105" t="n">
-        <v>6</v>
-      </c>
-      <c r="L105" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="L105" t="n">
+        <v>4</v>
+      </c>
+      <c r="M105" t="inlineStr">
         <is>
           <t>仅完整版</t>
         </is>
       </c>
-      <c r="M105" t="inlineStr">
+      <c r="N105" t="inlineStr">
         <is>
           <t>电影 | 电视剧 | 综艺 | 动漫 | 动作片 | 喜剧片 | 爱情片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 大陆剧 | 欧美剧 | 韩剧 | 日剧 | 港澳剧 | 台湾剧 | 泰剧 | 纪录片 | 其他剧</t>
         </is>
       </c>
-      <c r="N105" t="inlineStr">
+      <c r="O105" t="inlineStr">
         <is>
           <t>cmliu配置,sp696</t>
         </is>
@@ -7412,7 +7742,7 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>764</v>
+        <v>624</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -7421,23 +7751,26 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>是(少量)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" t="n">
         <v>1</v>
       </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>仅完整版</t>
-        </is>
-      </c>
       <c r="M106" t="inlineStr">
         <is>
+          <t>人版</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
           <t>电视剧 | 电影 | 欧美剧 | 香港剧 | 韩剧 | 日剧 | 马泰剧 | 伦理片 | 动作片 | 爱情片 | 喜剧片 | 科幻片 | 恐怖片 | 剧情片 | 战争片 | 记录片 | 动漫 | 内地剧 | 动画片 | 中国动漫</t>
         </is>
       </c>
-      <c r="N106" t="inlineStr">
+      <c r="O106" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -7480,7 +7813,7 @@
         </is>
       </c>
       <c r="H107" s="2" t="n">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
@@ -7495,17 +7828,20 @@
       <c r="K107" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="L107" s="2" t="inlineStr">
+      <c r="L107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M107" s="2" t="inlineStr">
+      <c r="N107" s="2" t="inlineStr">
         <is>
           <t>国产区 | AV区 | 欧美区 | 动漫区 | 网红主播 | 国产传媒 | 探花系列 | 人妻熟女 | 日本无码 | 美乳巨乳 | 强制侵犯 | 制服诱惑 | 绝色佳人 | 风俗泡泡浴 | 家庭乱伦 | AV解说 | 三级电影 | 少女萝莉 | SM调教 | 绝顶潮吹</t>
         </is>
       </c>
-      <c r="N107" s="2" t="inlineStr">
+      <c r="O107" s="2" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -7548,7 +7884,7 @@
         </is>
       </c>
       <c r="H108" s="2" t="n">
-        <v>762</v>
+        <v>685</v>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
@@ -7563,17 +7899,20 @@
       <c r="K108" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="L108" s="2" t="inlineStr">
+      <c r="L108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M108" s="2" t="inlineStr">
+      <c r="N108" s="2" t="inlineStr">
         <is>
           <t>视频一区 | 视频二区 | 视频三区 | 视频四区 | 精品推荐 | 国产主播 | 国产乱伦 | 自拍偷拍 | 制服丝袜 | 网曝事件 | 传媒探花 | 清纯学生 | A V 解说 | 淫妻作乐 | 港台辣妹 | 足浴撩妹 | 反差母狗 | A I 换脸 | V R 视角 | 重口性癖</t>
         </is>
       </c>
-      <c r="N108" s="2" t="inlineStr">
+      <c r="O108" s="2" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -7616,7 +7955,7 @@
         </is>
       </c>
       <c r="H109" s="2" t="n">
-        <v>793</v>
+        <v>736</v>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
@@ -7631,17 +7970,20 @@
       <c r="K109" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="L109" s="2" t="inlineStr">
+      <c r="L109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M109" s="2" t="inlineStr">
+      <c r="N109" s="2" t="inlineStr">
         <is>
           <t>精品推荐 | 国产色情 | 主播直播 | 亚洲无码 | 亚洲有码 | 中文字幕 | 巨乳美乳 | 人妻熟女 | 强奸乱伦 | 欧美精品 | 萝莉少女 | 伦理三级 | 成人动漫 | 自拍偷拍 | 制服丝袜 | 口交颜射 | 日本精品 | Cosplay | 素人自拍 | 台湾辣妹</t>
         </is>
       </c>
-      <c r="N109" s="2" t="inlineStr">
+      <c r="O109" s="2" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -7684,7 +8026,7 @@
         </is>
       </c>
       <c r="H110" s="2" t="n">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
@@ -7699,17 +8041,20 @@
       <c r="K110" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="L110" s="2" t="inlineStr">
+      <c r="L110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M110" s="2" t="inlineStr">
+      <c r="N110" s="2" t="inlineStr">
         <is>
           <t>采集教程 | 国产视频 | 国产传媒 | 国产探花 | 极品学生 | 野战户外 | 网曝黑料 | 日本有码 | 主播大秀 | 校园春色 | SM虐待 | 巨乳系列 | 偷拍自拍 | 强奸乱伦 | 制服诱惑 | 欧美精品 | 三级伦理 | AV解说 | 成人动漫 | 日本无码</t>
         </is>
       </c>
-      <c r="N110" s="2" t="inlineStr">
+      <c r="O110" s="2" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -7752,7 +8097,7 @@
         </is>
       </c>
       <c r="H111" s="2" t="n">
-        <v>371</v>
+        <v>436</v>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
@@ -7767,17 +8112,20 @@
       <c r="K111" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="L111" s="2" t="inlineStr">
+      <c r="L111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M111" s="2" t="inlineStr">
+      <c r="N111" s="2" t="inlineStr">
         <is>
           <t>国产专区 | 国产厂商 | 主播视讯 | 日本无码 | 日本有码 | 中文字幕 | 中字无码 | 中字有码 | 水果派解说 | 麻豆传媒 | 91制片厂 | 蜜桃影像传媒 | 天美传媒 | 精东影业 | 星空无限传媒 | 台湾swag | 其他传媒 | 三级伦理 | 美女写真 | 卡通动漫</t>
         </is>
       </c>
-      <c r="N111" s="2" t="inlineStr">
+      <c r="O111" s="2" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -7820,7 +8168,7 @@
         </is>
       </c>
       <c r="H112" s="2" t="n">
-        <v>1255</v>
+        <v>1026</v>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
@@ -7835,17 +8183,20 @@
       <c r="K112" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="L112" s="2" t="inlineStr">
+      <c r="L112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M112" s="2" t="inlineStr">
+      <c r="N112" s="2" t="inlineStr">
         <is>
           <t>中文字幕 | 日本有码 | 日本无码 | AV解说 | cosplay | 都市激情 | 校园情事 | 人妻纵情 | 风俗伦理 | 另类小说 | 武侠古典 | 长篇连载 | 黑丝诱惑 | SWAG | 自拍偷拍 | 激情动漫 | 网红主播 | 探花系列 | 三级伦理 | VR视角</t>
         </is>
       </c>
-      <c r="N112" s="2" t="inlineStr">
+      <c r="O112" s="2" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -7888,7 +8239,7 @@
         </is>
       </c>
       <c r="H113" s="2" t="n">
-        <v>793</v>
+        <v>851</v>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
@@ -7903,17 +8254,20 @@
       <c r="K113" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="L113" s="2" t="inlineStr">
+      <c r="L113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M113" s="2" t="inlineStr">
+      <c r="N113" s="2" t="inlineStr">
         <is>
           <t>视频1区 | 国产精品 | 华语AV | 黑料吃瓜 | 欧美 | 禁漫 | 视频2区 | 学生 | 乱伦 | 探花 | 日本无码 | 日本有码 | 主播网红 | 日本素人 | AI短剧</t>
         </is>
       </c>
-      <c r="N113" s="2" t="inlineStr">
+      <c r="O113" s="2" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -7956,7 +8310,7 @@
         </is>
       </c>
       <c r="H114" s="2" t="n">
-        <v>2256</v>
+        <v>659</v>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
@@ -7969,19 +8323,22 @@
         </is>
       </c>
       <c r="K114" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="L114" s="2" t="inlineStr">
+        <v>36</v>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M114" s="2" t="inlineStr">
+      <c r="N114" s="2" t="inlineStr">
         <is>
           <t>中文传媒 | 国产 | 欧美AV | 日本AV | 传媒-麻豆传媒 | 传媒-精东影业 | 传媒-蜜桃传媒 | 传媒-果冻传媒 | 传媒-星空无限传媒 | 传媒-SA国际传媒 | 传媒-性视界传媒 | 国产-自拍 | 国产-偷拍 | 国产-探花 | 国产-主播 | 传媒-天美传媒 | 欧美-高清无码 | 欧美-高清有码 | 日本-中文字幕 | 日本-无码流出</t>
         </is>
       </c>
-      <c r="N114" s="2" t="inlineStr">
+      <c r="O114" s="2" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -8041,13 +8398,16 @@
       <c r="K115" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L115" s="2" t="inlineStr">
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M115" s="2" t="inlineStr"/>
-      <c r="N115" s="2" t="inlineStr">
+      <c r="N115" s="2" t="inlineStr"/>
+      <c r="O115" s="2" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -8081,7 +8441,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>分类实测</t>
+          <t>上游标记</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -8090,11 +8450,11 @@
         </is>
       </c>
       <c r="H116" s="2" t="n">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>18禁/动漫</t>
+          <t>动漫</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
@@ -8103,19 +8463,22 @@
         </is>
       </c>
       <c r="K116" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="L116" s="2" t="inlineStr">
+        <v>17</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M116" s="2" t="inlineStr">
+      <c r="N116" s="2" t="inlineStr">
         <is>
           <t>视频一区 | 日韩无码 | 国产主播 | 视频三区 | 日韩精品 | 欧美劲爆 | 成人动漫 | 自拍偷拍 | 伦理影片 | 中文字幕 | 人妻系列 | 制服诱惑 | 强奸乱伦 | AV明星 | SM重味 | 视频二区 | 巨乳尤物 | 颜射系列 | 口交视频 | 自慰系列</t>
         </is>
       </c>
-      <c r="N116" s="2" t="inlineStr">
+      <c r="O116" s="2" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -8173,13 +8536,16 @@
       <c r="K117" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L117" s="2" t="inlineStr">
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M117" s="2" t="inlineStr"/>
-      <c r="N117" s="2" t="inlineStr">
+      <c r="N117" s="2" t="inlineStr"/>
+      <c r="O117" s="2" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -8222,7 +8588,7 @@
         </is>
       </c>
       <c r="H118" s="2" t="n">
-        <v>731</v>
+        <v>709</v>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
@@ -8237,17 +8603,20 @@
       <c r="K118" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="L118" s="2" t="inlineStr">
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M118" s="2" t="inlineStr">
+      <c r="N118" s="2" t="inlineStr">
         <is>
           <t>国产自拍 | 日本无码 | 日本有码 | 中文字幕 | 欧美精品 | 成人动漫 | 日本素人 | 高清名优 | 三级伦理 | 网红主播 | 映画传媒 | 人妻熟女 | 口爆颜射 | 萝莉少女 | SM调教 | 美乳巨乳 | 短视频 | 制服诱惑 | 女同性爱 | AI换脸</t>
         </is>
       </c>
-      <c r="N118" s="2" t="inlineStr">
+      <c r="O118" s="2" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -8264,7 +8633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:O44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8325,15 +8694,20 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>软性栏目数</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>归属</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>分类名</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
@@ -8376,7 +8750,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -8391,17 +8765,20 @@
       <c r="K2" t="n">
         <v>17</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>无码专区 | 麻豆传媒 | 制服诱惑 | 三级伦理 | AI换脸 | 中文字幕 | 卡通动漫 | 欧美系列 | 美女主播 | 国产自拍 | 熟女人妻 | 萝莉少女 | 女同性爱 | 多人群交 | 美乳巨乳 | 强奸乱伦 | 生活都市 | 不偷恋情 | 学生校园 | 人妻熟女</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -8461,12 +8838,15 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -8509,7 +8889,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1060</v>
+        <v>776</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -8524,17 +8904,20 @@
       <c r="K4" t="n">
         <v>8</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>麻豆视频 | 91制片厂 | 天美传媒 | 蜜桃传媒 | 皇家华人 | 星空传媒 | 精东影业 | 海角社区 | 成人头条 | 乌鸦传媒 | 兔子先生 | 杏吧原创 | 玩偶姐姐 | mini传媒 | 大象传媒 | 91视频 | PsychoPorn | 糖心Vlog | 萝莉社 | 性视界</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -8589,12 +8972,15 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -8637,7 +9023,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>195</v>
+        <v>275</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -8652,17 +9038,20 @@
       <c r="K6" t="n">
         <v>12</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>中文字幕 | 日本有码 | 日本无码 | AV解说 | cosplay | 都市激情 | 校园情事 | 人妻纵情 | 风俗伦理 | 另类小说 | 武侠古典 | 长篇连载 | 黑丝诱惑 | SWAG | 自拍偷拍 | 激情动漫 | 网红主播 | 探花系列 | 三级伦理 | VR视角</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -8705,7 +9094,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>793</v>
+        <v>761</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -8718,19 +9107,22 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>37</v>
-      </c>
-      <c r="L7" t="inlineStr">
+        <v>36</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>中文传媒 | 国产 | 欧美AV | 日本AV | 传媒-麻豆传媒 | 传媒-精东影业 | 传媒-蜜桃传媒 | 传媒-果冻传媒 | 传媒-星空无限传媒 | 传媒-SA国际传媒 | 传媒-性视界传媒 | 国产-自拍 | 国产-偷拍 | 国产-探花 | 国产-主播 | 传媒-天美传媒 | 欧美-高清无码 | 欧美-高清有码 | 日本-中文字幕 | 日本-无码流出</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -8773,7 +9165,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>947</v>
+        <v>840</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -8786,19 +9178,22 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>11</v>
-      </c>
-      <c r="L8" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>亚洲情色 | 国产主播 | 国产自拍 | 无码专区 | 欧美性爱 | 熟女人妻 | 强奸乱伦 | 巨乳美乳 | 中文字幕 | 制服诱惑 | 女同性恋 | 卡通动画 | 视频伦理 | 少女萝莉 | 重口色情 | 人兽性交 | 福利姬</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -8841,7 +9236,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1028</v>
+        <v>798</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -8856,17 +9251,20 @@
       <c r="K9" t="n">
         <v>11</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>国产视频 | 中文字幕 | 国产传媒 | 日本有码 | 日本无码 | 欧美无码 | 强奸乱伦 | 制服诱惑 | 国产主播 | 激情动漫 | 明星换脸 | 抖阴视频 | 女优明星 | 视频一区 | 视频二区 | 网曝黑料 | 视频三区 | 伦理三级 | AV解说 | SM调教</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -8909,7 +9307,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1013</v>
+        <v>1587</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -8922,19 +9320,22 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>12</v>
-      </c>
-      <c r="L10" t="inlineStr">
+        <v>11</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>精品国产 | 精品日韩 | 精品综合 | 精品小说 | 精品美图 | 国产自拍 | 主播诱惑 | 探花约炮 | 偷拍偷窥 | 网曝吃瓜 | 抖阴短片 | 传媒剧情 | 日韩主播 | 日韩无码 | 中文字幕 | AV解说 | 换脸明星 | 强奸乱伦 | 女优明星 | 欧美激情</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -8977,7 +9378,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>753</v>
+        <v>2193</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -8992,17 +9393,20 @@
       <c r="K11" t="n">
         <v>22</v>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>精品推荐 | 国产色情 | 主播直播 | 亚洲无码 | 亚洲有码 | 中文字幕 | 巨乳美乳 | 人妻熟女 | 强奸乱伦 | 欧美精品 | 萝莉少女 | 伦理三级 | 成人动漫 | 自拍偷拍 | 制服丝袜 | 口交颜射 | 日本精品 | Cosplay | 素人自拍 | 台湾辣妹</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置</t>
         </is>
@@ -9045,7 +9449,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1266</v>
+        <v>884</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -9060,12 +9464,15 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -9108,7 +9515,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>602</v>
+        <v>406</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -9123,17 +9530,20 @@
       <c r="K13" t="n">
         <v>11</v>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>精品推荐 | 国产精品 | 主播秀色 | 日本有码 | 日本无码 | 中文字幕 | 童颜巨乳 | 性感人妻 | 强奸乱伦 | 欧美情色 | 三级伦理 | 卡通动漫 | 丝袜OL | 自拍偷拍 | 日本片商 | 剧情介绍 | 网曝系列 | 麻豆传媒 | 明星换脸 | 国产乱伦</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -9176,7 +9586,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>726</v>
+        <v>881</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -9191,17 +9601,20 @@
       <c r="K14" t="n">
         <v>12</v>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>制服丝袜 | 群交淫乱 | 无码专区 | 偷拍自拍 | 卡通动漫 | 中文字幕 | 欧美性爱 | 巨乳美乳 | 国产裸聊 | 国产自拍 | 国产盗摄 | 伦理三级 | 女同性恋 | 少女萝莉 | 人妖系列 | 虚拟VR | 亚州图片 | 欧美图片 | 美腿丝袜 | 网友自拍</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -9244,7 +9657,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1038</v>
+        <v>851</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -9259,12 +9672,15 @@
       <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -9307,7 +9723,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>594</v>
+        <v>466</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -9322,17 +9738,20 @@
       <c r="K16" t="n">
         <v>4</v>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>国产 | 日本 | 欧美 | 动漫 | 偷拍自拍 | 国产大制作 | 乱伦毁三观 | 嫖妓全过程 | 淫乱学生妹 | 黑料不打烊 | 监控摄像头 | 主播网红 | 高清无码 | 中文字幕 | 成人综艺 | 媚黑母狗 | 为国争光 | 少女破处 | 人兽典藏 | 中文剧情</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -9375,7 +9794,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>804</v>
+        <v>1009</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -9390,12 +9809,15 @@
       <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -9438,7 +9860,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>713</v>
+        <v>755</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -9453,17 +9875,20 @@
       <c r="K18" t="n">
         <v>11</v>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>精品推荐 | 国产精品 | 主播秀色 | 日本有码 | 日本无码 | 中文字幕 | 童颜巨乳 | 性感人妻 | 强奸乱伦 | 欧美情色 | 三级伦理 | 卡通动漫 | 丝袜OL | 自拍偷拍 | 日本片商 | 剧情介绍 | 网曝系列 | 麻豆传媒 | 明星换脸 | 国产乱伦</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -9523,12 +9948,15 @@
       <c r="K19" t="n">
         <v>0</v>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -9588,12 +10016,15 @@
       <c r="K20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -9636,7 +10067,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>829</v>
+        <v>898</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -9651,17 +10082,20 @@
       <c r="K21" t="n">
         <v>8</v>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>国产自拍 | 欧美极品 | 日韩无码 | AV明星 | 公告 | 头条 | 中文字幕 | 动漫精品 | 极骚萝莉 | 人妖视频 | 重咸口味 | 三级自慰 | 强奸乱伦 | 独家擂台格斗 | 辣椒GIGA | HEYZO | 独家DMM | HEY诱惑 | 童颜巨乳 | 高潮喷吹</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -9704,7 +10138,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>871</v>
+        <v>786</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -9719,12 +10153,15 @@
       <c r="K22" t="n">
         <v>0</v>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -9758,22 +10195,20 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>域名/标记</t>
+          <t>上游标记</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>失活</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>存活</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>5519</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>动漫</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -9782,14 +10217,22 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="L23" t="n">
+        <v>2</v>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
+        <is>
+          <t>国产情色 | 日本无码 | AV明星 | 中文字幕 | 网红主播 | 成人动漫 | 欧美情色 | 国模私拍 | 长腿丝袜 | 邻家人妻 | 韩国伦理 | 香港伦理 | 精品推荐 | 原纱央莉 | 柚木TINA | 大桥未久 | AV明星1 | 仁科百华 | 天海翼 | 小川阿佐美</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -9832,7 +10275,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>720</v>
+        <v>568</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -9847,12 +10290,15 @@
       <c r="K24" t="n">
         <v>0</v>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -9907,12 +10353,15 @@
       <c r="K25" t="n">
         <v>0</v>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -9941,7 +10390,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>分类实测</t>
+          <t>上游标记</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -9950,11 +10399,11 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>687</v>
+        <v>598</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>18禁/动漫</t>
+          <t>动漫</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -9963,19 +10412,22 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>18</v>
-      </c>
-      <c r="L26" t="inlineStr">
+        <v>17</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>视频一区 | 日韩无码 | 国产主播 | 视频三区 | 日韩精品 | 欧美劲爆 | 成人动漫 | 自拍偷拍 | 伦理影片 | 中文字幕 | 人妻系列 | 制服诱惑 | 强奸乱伦 | AV明星 | SM重味 | 视频二区 | 巨乳尤物 | 颜射系列 | 口交视频 | 自慰系列</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>仓库1-增强版,cmliu配置</t>
         </is>
@@ -10030,12 +10482,15 @@
       <c r="K27" t="n">
         <v>0</v>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -10090,12 +10545,15 @@
       <c r="K28" t="n">
         <v>0</v>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -10133,7 +10591,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>406</v>
+        <v>511</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -10148,17 +10606,20 @@
       <c r="K29" t="n">
         <v>9</v>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>国产区 | AV区 | 欧美区 | 动漫区 | 网红主播 | 国产传媒 | 探花系列 | 人妻熟女 | 日本无码 | 美乳巨乳 | 强制侵犯 | 制服诱惑 | 绝色佳人 | 风俗泡泡浴 | 家庭乱伦 | AV解说 | 三级电影 | 少女萝莉 | SM调教 | 绝顶潮吹</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -10201,7 +10662,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>474</v>
+        <v>318</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -10216,17 +10677,20 @@
       <c r="K30" t="n">
         <v>9</v>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>国产自拍 | 日韩AV | 欧美精品 | 异族风情 | 动漫专栏 | 强奸迷奸 | 丝袜制服 | 国产厂牌 | SM调教 | 乱伦 | 网曝黑料 | 主播网红 | 自拍偷拍 | 口交自慰 | 群交多P | AI换脸 | 素人特摄 | 无码高清 | 经典有码 | 中文字幕</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -10264,7 +10728,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>3854</v>
+        <v>794</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -10279,12 +10743,15 @@
       <c r="K31" t="n">
         <v>0</v>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>仓库1-增强版</t>
         </is>
@@ -10327,7 +10794,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -10342,12 +10809,15 @@
       <c r="K32" t="n">
         <v>0</v>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>仓库1-增强版,sp696</t>
         </is>
@@ -10390,7 +10860,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -10405,17 +10875,20 @@
       <c r="K33" t="n">
         <v>9</v>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>国产区 | AV区 | 欧美区 | 动漫区 | 网红主播 | 国产传媒 | 探花系列 | 人妻熟女 | 日本无码 | 美乳巨乳 | 强制侵犯 | 制服诱惑 | 绝色佳人 | 风俗泡泡浴 | 家庭乱伦 | AV解说 | 三级电影 | 少女萝莉 | SM调教 | 绝顶潮吹</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -10458,7 +10931,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>762</v>
+        <v>685</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -10473,17 +10946,20 @@
       <c r="K34" t="n">
         <v>7</v>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>视频一区 | 视频二区 | 视频三区 | 视频四区 | 精品推荐 | 国产主播 | 国产乱伦 | 自拍偷拍 | 制服丝袜 | 网曝事件 | 传媒探花 | 清纯学生 | A V 解说 | 淫妻作乐 | 港台辣妹 | 足浴撩妹 | 反差母狗 | A I 换脸 | V R 视角 | 重口性癖</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -10526,7 +11002,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>793</v>
+        <v>736</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -10541,17 +11017,20 @@
       <c r="K35" t="n">
         <v>22</v>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>精品推荐 | 国产色情 | 主播直播 | 亚洲无码 | 亚洲有码 | 中文字幕 | 巨乳美乳 | 人妻熟女 | 强奸乱伦 | 欧美精品 | 萝莉少女 | 伦理三级 | 成人动漫 | 自拍偷拍 | 制服丝袜 | 口交颜射 | 日本精品 | Cosplay | 素人自拍 | 台湾辣妹</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -10594,7 +11073,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -10609,17 +11088,20 @@
       <c r="K36" t="n">
         <v>10</v>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>采集教程 | 国产视频 | 国产传媒 | 国产探花 | 极品学生 | 野战户外 | 网曝黑料 | 日本有码 | 主播大秀 | 校园春色 | SM虐待 | 巨乳系列 | 偷拍自拍 | 强奸乱伦 | 制服诱惑 | 欧美精品 | 三级伦理 | AV解说 | 成人动漫 | 日本无码</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -10662,7 +11144,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>371</v>
+        <v>436</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -10677,17 +11159,20 @@
       <c r="K37" t="n">
         <v>13</v>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>国产专区 | 国产厂商 | 主播视讯 | 日本无码 | 日本有码 | 中文字幕 | 中字无码 | 中字有码 | 水果派解说 | 麻豆传媒 | 91制片厂 | 蜜桃影像传媒 | 天美传媒 | 精东影业 | 星空无限传媒 | 台湾swag | 其他传媒 | 三级伦理 | 美女写真 | 卡通动漫</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -10730,7 +11215,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1255</v>
+        <v>1026</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -10745,17 +11230,20 @@
       <c r="K38" t="n">
         <v>12</v>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>中文字幕 | 日本有码 | 日本无码 | AV解说 | cosplay | 都市激情 | 校园情事 | 人妻纵情 | 风俗伦理 | 另类小说 | 武侠古典 | 长篇连载 | 黑丝诱惑 | SWAG | 自拍偷拍 | 激情动漫 | 网红主播 | 探花系列 | 三级伦理 | VR视角</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -10798,7 +11286,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>793</v>
+        <v>851</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -10813,17 +11301,20 @@
       <c r="K39" t="n">
         <v>3</v>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>视频1区 | 国产精品 | 华语AV | 黑料吃瓜 | 欧美 | 禁漫 | 视频2区 | 学生 | 乱伦 | 探花 | 日本无码 | 日本有码 | 主播网红 | 日本素人 | AI短剧</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -10866,7 +11357,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>2256</v>
+        <v>659</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -10879,19 +11370,22 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>37</v>
-      </c>
-      <c r="L40" t="inlineStr">
+        <v>36</v>
+      </c>
+      <c r="L40" t="n">
+        <v>2</v>
+      </c>
+      <c r="M40" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>中文传媒 | 国产 | 欧美AV | 日本AV | 传媒-麻豆传媒 | 传媒-精东影业 | 传媒-蜜桃传媒 | 传媒-果冻传媒 | 传媒-星空无限传媒 | 传媒-SA国际传媒 | 传媒-性视界传媒 | 国产-自拍 | 国产-偷拍 | 国产-探花 | 国产-主播 | 传媒-天美传媒 | 欧美-高清无码 | 欧美-高清有码 | 日本-中文字幕 | 日本-无码流出</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -10951,12 +11445,15 @@
       <c r="K41" t="n">
         <v>0</v>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -10990,7 +11487,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>分类实测</t>
+          <t>上游标记</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -10999,11 +11496,11 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>18禁/动漫</t>
+          <t>动漫</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -11012,19 +11509,22 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>18</v>
-      </c>
-      <c r="L42" t="inlineStr">
+        <v>17</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>视频一区 | 日韩无码 | 国产主播 | 视频三区 | 日韩精品 | 欧美劲爆 | 成人动漫 | 自拍偷拍 | 伦理影片 | 中文字幕 | 人妻系列 | 制服诱惑 | 强奸乱伦 | AV明星 | SM重味 | 视频二区 | 巨乳尤物 | 颜射系列 | 口交视频 | 自慰系列</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -11082,12 +11582,15 @@
       <c r="K43" t="n">
         <v>0</v>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -11130,7 +11633,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>731</v>
+        <v>709</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -11145,17 +11648,20 @@
       <c r="K44" t="n">
         <v>12</v>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t>18禁版</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>国产自拍 | 日本无码 | 日本有码 | 中文字幕 | 欧美精品 | 成人动漫 | 日本素人 | 高清名优 | 三级伦理 | 网红主播 | 映画传媒 | 人妻熟女 | 口爆颜射 | 萝莉少女 | SM调教 | 美乳巨乳 | 短视频 | 制服诱惑 | 女同性爱 | AI换脸</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>sp696</t>
         </is>
@@ -11172,7 +11678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11220,12 +11726,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TV-CK资源</t>
+          <t>TV-ikun资源</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://ckzy.me/api.php/provide/vod</t>
+          <t>https://ikunzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -11235,14 +11741,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>如果感激的话就回报到下半身吧</t>
+          <t>某暗部的少女共栖</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="F2" t="n">
-        <v>490</v>
+        <v>456</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -11258,12 +11764,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TV-ikun资源</t>
+          <t>🎬猫眼资源</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://ikunzyapi.com/api.php/provide/vod</t>
+          <t>https://api.maoyanapi.top/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -11273,14 +11779,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>某暗部的少女共栖</t>
+          <t>斗罗大陆Ⅱ绝世唐门</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>556</v>
+        <v>755</v>
       </c>
       <c r="F3" t="n">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -11289,19 +11795,19 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>🎬猫眼资源</t>
+          <t>如意资源(代理)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://api.maoyanapi.top/api.php/provide/vod</t>
+          <t>https://pz.v88.qzz.io/?url=https://cj.rycjapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -11311,14 +11817,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>斗罗大陆Ⅱ绝世唐门</t>
+          <t>霹雳英雄战纪之塗附世界</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>745</v>
+        <v>1713</v>
       </c>
       <c r="F4" t="n">
-        <v>438</v>
+        <v>324</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -11327,19 +11833,19 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>如意资源(代理)</t>
+          <t>TV-360资源</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://pz.v88.qzz.io/?url=https://cj.rycjapi.com/api.php/provide/vod</t>
+          <t>https://360zy.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -11349,14 +11855,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>霹雳英雄战纪之塗附世界</t>
+          <t>某暗部的少女共栖</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2138</v>
+        <v>1282</v>
       </c>
       <c r="F5" t="n">
-        <v>369</v>
+        <v>267</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -11365,19 +11871,19 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TV-360资源</t>
+          <t>iqiyi资源</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://360zy.com/api.php/provide/vod</t>
+          <t>https://www.iqiyizyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -11387,18 +11893,18 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>某暗部的少女共栖</t>
+          <t>万物生灵第七季</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1369</v>
+        <v>1658</v>
       </c>
       <c r="F6" t="n">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>慢</t>
+          <t>中</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -11429,10 +11935,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>440</v>
+        <v>542</v>
       </c>
       <c r="F7" t="n">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -11448,12 +11954,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TV-百度云资源</t>
+          <t>TV-CK资源</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://api.apibdzy.com/api.php/provide/vod</t>
+          <t>https://ckzy.me/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -11463,14 +11969,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>玄苍路之初入宗门</t>
+          <t>如果感激的话就回报到下半身吧</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1552</v>
+        <v>561</v>
       </c>
       <c r="F8" t="n">
-        <v>196</v>
+        <v>244</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -11486,12 +11992,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TV-茅台资源</t>
+          <t>TV-百度云资源</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://caiji.maotaizy.cc/api.php/provide/vod</t>
+          <t>https://api.apibdzy.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -11501,14 +12007,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>梦想改造家 第13季</t>
+          <t>玄苍路之初入宗门</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1578</v>
+        <v>466</v>
       </c>
       <c r="F9" t="n">
-        <v>112</v>
+        <v>199</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -11517,7 +12023,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -11543,7 +12049,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F10" t="n">
         <v>108</v>
@@ -11562,12 +12068,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TV-如意资源</t>
+          <t>TV-茅台资源</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://cj.rycjapi.com/api.php/provide/vod</t>
+          <t>https://caiji.maotaizy.cc/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -11577,14 +12083,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>霹雳英雄战纪之塗附世界</t>
+          <t>梦想改造家 第13季</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2739</v>
+        <v>1730</v>
       </c>
       <c r="F11" t="n">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -11619,10 +12125,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1190</v>
+        <v>1023</v>
       </c>
       <c r="F12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -11657,10 +12163,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>628</v>
+        <v>1151</v>
       </c>
       <c r="F13" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -11676,12 +12182,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TV-光速资源</t>
+          <t>TV-如意资源</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://api.guangsuapi.com/api.php/provide/vod</t>
+          <t>https://cj.rycjapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -11691,39 +12197,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>方舟一号第三季</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>霹雳英雄战纪之塗附世界</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3010</v>
+      </c>
+      <c r="F14" t="n">
+        <v>55</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>慢</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TV-新浪点播</t>
+          <t>TV-光速资源</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://api.xinlangapi.com/xinlangapi.php/provide/vod</t>
+          <t>https://api.guangsuapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -11760,12 +12262,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TV-U酷资源88</t>
+          <t>TV-新浪点播</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://api.ukuapi88.com/api.php/provide/vod</t>
+          <t>https://api.xinlangapi.com/xinlangapi.php/provide/vod</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -11775,7 +12277,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>谋杀奇闻 第一季</t>
+          <t>方舟一号第三季</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -11802,12 +12304,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TV-最大资源</t>
+          <t>TV-U酷资源88</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://api.zuidapi.com/api.php/provide/vod</t>
+          <t>https://api.ukuapi88.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -11817,11 +12319,13 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>可以爱你吗</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>72</v>
+          <t>谋杀奇闻 第一季</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -11830,7 +12334,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>未测出</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -11842,12 +12346,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TV-丫丫点播</t>
+          <t>TV-wujinapi无尽</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://cj.yayazy.net/api.php/provide/vod</t>
+          <t>https://api.wujinapi.cc/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -11857,11 +12361,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>可以爱你吗</t>
+          <t>穿越时空甩掉你</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>732</v>
+        <v>55</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -11882,12 +12386,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TV-最大点播</t>
+          <t>TV-无尽资源</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>http://zuidazy.me/api.php/provide/vod</t>
+          <t>https://api.wujinapi.me/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -11897,11 +12401,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>可以爱你吗</t>
+          <t>穿越时空甩掉你</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>729</v>
+        <v>213</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -11941,7 +12445,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>741</v>
+        <v>553</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -11962,12 +12466,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TV-无尽资源</t>
+          <t>TV-U酷资源</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://api.wujinapi.com/api.php/provide/vod</t>
+          <t>https://api.ukuapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -11977,11 +12481,13 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>穿越时空甩掉你</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>1989</v>
+          <t>谋杀奇闻 第一季</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -11990,7 +12496,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>未测出</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -12002,12 +12508,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TV-无尽资源</t>
+          <t>TV-电影天堂资源</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://api.wujinapi.net/api.php/provide/vod</t>
+          <t>http://caiji.dyttzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -12017,11 +12523,13 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>穿越时空甩掉你</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>489</v>
+          <t>霹雳英雄战纪之塗附世界</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -12030,12 +12538,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>未测出</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -12126,12 +12634,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TV-虎牙资源</t>
+          <t>TV-无尽资源</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://www.huyaapi.com/api.php/provide/vod</t>
+          <t>https://api.wujinapi.net/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -12141,13 +12649,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>南瓜头怪2</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>穿越时空甩掉你</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2859</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -12156,7 +12662,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -12168,12 +12674,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TV-豆瓣资源</t>
+          <t>TV-虎牙资源</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://dbzy.tv/api.php/provide/vod</t>
+          <t>https://www.huyaapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -12183,7 +12689,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>骑士情缘</t>
+          <t>南瓜头怪2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12203,7 +12709,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -12252,12 +12758,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TV-速博资源</t>
+          <t>TV-牛牛点播</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://subocaiji.com/api.php/provide/vod</t>
+          <t>https://api.niuniuzy.me/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -12267,13 +12773,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>方舟一号第三季</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>可以爱你吗</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>790</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -12282,7 +12786,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -12294,12 +12798,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TV-量子资源</t>
+          <t>TV-豆瓣资源</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://cj.lziapi.com/api.php/provide/vod</t>
+          <t>https://dbzy.tv/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -12309,7 +12813,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>霹雳英雄战纪之塗附世界</t>
+          <t>骑士情缘</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -12329,19 +12833,19 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TV-金鹰点播</t>
+          <t>TV-速博资源</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://jinyingzy.com/api.php/provide/vod</t>
+          <t>https://subocaiji.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -12420,12 +12924,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TV-电影天堂资源</t>
+          <t>TV-索尼资源</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>http://caiji.dyttzyapi.com/api.php/provide/vod</t>
+          <t>https://suoniapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -12435,13 +12939,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>霹雳英雄战纪之塗附世界</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>改造旧冷库后我住成了大别墅</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>66</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -12450,24 +12952,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TV-无尽资源</t>
+          <t>TV-金鹰点播</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://api.wujinapi.me/api.php/provide/vod</t>
+          <t>https://jinyingzy.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -12477,11 +12979,13 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>穿越时空甩掉你</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>62</v>
+          <t>方舟一号第三季</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -12490,7 +12994,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>未测出</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -12502,12 +13006,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TV-牛牛点播</t>
+          <t>TV-无尽资源</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://api.niuniuzy.me/api.php/provide/vod</t>
+          <t>https://api.wujinapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -12517,11 +13021,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>可以爱你吗</t>
+          <t>穿越时空甩掉你</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>748</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -12542,12 +13046,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TV-闪电资源</t>
+          <t>TV-非凡资源</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://sdzyapi.com/api.php/provide/vod</t>
+          <t>https://cj.ffzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -12557,11 +13061,13 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>可以爱你吗</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>712</v>
+          <t>我与你在一起的理由 特别篇：关岛所赐、那一天的延</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -12570,24 +13076,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>未测出</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TV-wujinapi无尽</t>
+          <t>TV-闪电资源</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://api.wujinapi.cc/api.php/provide/vod</t>
+          <t>https://sdzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -12597,11 +13103,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>穿越时空甩掉你</t>
+          <t>可以爱你吗</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>454</v>
+        <v>730</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -12622,12 +13128,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TV-天涯资源</t>
+          <t>TV-最大资源</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://tyyszy.com/api.php/provide/vod</t>
+          <t>https://api.zuidapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -12637,11 +13143,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>梦醒时遇见你</t>
+          <t>可以爱你吗</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>271</v>
+        <v>60</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -12650,7 +13156,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>失败:ReadTimeout</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -12662,12 +13168,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TV-索尼资源</t>
+          <t>TV-1080资源</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://suoniapi.com/api.php/provide/vod</t>
+          <t>https://api.1080zyku.com/inc/api_mac10.php</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -12677,11 +13183,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>改造旧冷库后我住成了大别墅</t>
+          <t>冰雪狙击</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>69</v>
+        <v>780</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -12695,19 +13201,19 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>🎬极速资源</t>
+          <t>TV-最大点播</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://jszyapi.com/api.php/provide/vod</t>
+          <t>http://zuidazy.me/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -12717,13 +13223,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>方舟一号第三季</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>可以爱你吗</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>670</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -12732,7 +13236,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>失败:ReadTimeout</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -12744,12 +13248,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TV-神马云</t>
+          <t>TV-丫丫点播</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://api.1080zyku.com/inc/apijson.php</t>
+          <t>https://cj.yayazy.net/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -12759,11 +13263,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>坠落的大力神</t>
+          <t>可以爱你吗</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>895</v>
+        <v>714</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -12772,24 +13276,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>失败:ReadTimeout</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>红牛资源3</t>
+          <t>TV-天涯资源</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://www.hongniuzy3.com/api.php/provide/vod</t>
+          <t>https://tyyszy.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -12799,13 +13303,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>药屋少女的呢喃第三季</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>梦醒时遇见你</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>520</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -12814,24 +13316,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>失败:ReadTimeout</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>TV-1080资源</t>
+          <t>🎬极速资源</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://api.1080zyku.com/inc/api_mac10.php</t>
+          <t>https://jszyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -12841,11 +13343,13 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>冰雪狙击</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>697</v>
+          <t>方舟一号第三季</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -12854,24 +13358,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>未测出</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>非凡影视</t>
+          <t>非凡影视new</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>http://ffzy5.tv/api.php/provide/vod</t>
+          <t>https://api.ffzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -12908,12 +13412,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>金鹰资源采集网</t>
+          <t>红牛资源3</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://jyzyapi.com/provide/vod</t>
+          <t>https://www.hongniuzy3.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -12923,7 +13427,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>方舟一号第三季</t>
+          <t>药屋少女的呢喃第三季</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -12943,19 +13447,19 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>豪华资源(代理)</t>
+          <t>金鹰资源采集网</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://pz.v88.qzz.io/?url=https://hhzyapi.com/api.php/provide/vod</t>
+          <t>https://jyzyapi.com/provide/vod</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -12992,12 +13496,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TV-U酷资源</t>
+          <t>非凡影视</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://api.ukuapi.com/api.php/provide/vod</t>
+          <t>http://ffzy5.tv/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -13007,7 +13511,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>谋杀奇闻 第一季</t>
+          <t>我与你在一起的理由 特别篇：关岛所赐、那一天的延</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -13027,19 +13531,19 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>非凡影视new</t>
+          <t>TV-量子资源</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://api.ffzyapi.com/api.php/provide/vod</t>
+          <t>https://cj.lziapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -13049,7 +13553,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>金缮</t>
+          <t>霹雳英雄战纪之塗附世界</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -13069,19 +13573,19 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>索尼-闪电资源</t>
+          <t>豪华资源(代理)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://xsd.sdzyapi.com/api.php/provide/vod</t>
+          <t>https://pz.v88.qzz.io/?url=https://hhzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -13091,11 +13595,13 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>可以爱你吗</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>679</v>
+          <t>方舟一号第三季</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -13104,7 +13610,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>未测出</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -13116,12 +13622,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>🎬豆瓣资源</t>
+          <t>索尼-闪电资源</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://caiji.dbzy5.com/api.php/provide/vod</t>
+          <t>https://xsd.sdzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -13131,13 +13637,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>骑士情缘</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>可以爱你吗</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>710</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -13146,24 +13650,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>🎬金鹰点播</t>
+          <t>🎬量子资源</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://jyzyapi.com/provide/vod/from/jinyingyun/at/json</t>
+          <t>https://cj.lzcaiji.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -13173,7 +13677,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>方舟一号第三季</t>
+          <t>霹雳英雄战纪之塗附世界</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -13200,12 +13704,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>🎬360 资源</t>
+          <t>🎬豆瓣资源</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://360zyzz.com/api.php/provide/vod</t>
+          <t>https://caiji.dbzy5.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -13215,11 +13719,13 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Doctor X：白色黑手党时代</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>606</v>
+          <t>骑士情缘</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -13228,7 +13734,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>未测出</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -13240,12 +13746,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>艾旦影视(代理)</t>
+          <t>🎬金鹰点播</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://pz.v88.qzz.io/?url=https://lovedan.net/api.php/provide/vod</t>
+          <t>https://jyzyapi.com/provide/vod/from/jinyingyun/at/json</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -13255,11 +13761,13 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>伟大的长征</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>1536</v>
+          <t>方舟一号第三季</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -13268,7 +13776,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>未测出</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -13280,12 +13788,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>🎬量子资源</t>
+          <t>🎬360 资源</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://cj.lzcaiji.com/api.php/provide/vod</t>
+          <t>https://360zyzz.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -13295,13 +13803,11 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>霹雳英雄战纪之塗附世界</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Doctor X：白色黑手党时代</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>661</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -13310,24 +13816,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>🎬优质资源</t>
+          <t>🎬快车资源</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://api.yzzy-api.com/inc/apijson.php</t>
+          <t>https://caiji.kuaichezy.org/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -13337,11 +13843,11 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>坠落的大力神</t>
+          <t>可以爱你吗</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>910</v>
+        <v>716</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -13355,19 +13861,19 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>🎬快车资源</t>
+          <t>艾旦影视(代理)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://caiji.kuaichezy.org/api.php/provide/vod</t>
+          <t>https://pz.v88.qzz.io/?url=https://lovedan.net/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -13377,11 +13883,11 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>可以爱你吗</t>
+          <t>伟大的长征</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>560</v>
+        <v>1484</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -13402,33 +13908,35 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AV-辣椒资源</t>
+          <t>🎬优质资源</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://apilj.com/api.php/provide/vod</t>
+          <t>https://api.yzzy-api.com/inc/apijson.php</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>泌尿科的美人女医8人プラネットプラス伊织凉子,管</t>
+          <t>现场报道</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>691</v>
-      </c>
-      <c r="F56" t="n">
-        <v>11428</v>
+        <v>916</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>快</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -13440,50 +13948,52 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>🔞森林资源</t>
+          <t>TV-神马云</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://beiyong.slapibf.com/api.php/provide/vod</t>
+          <t>https://api.1080zyku.com/inc/apijson.php</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>FTHTD-144FALENO学校训练营公共浴池</t>
+          <t>现场报道</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>494</v>
-      </c>
-      <c r="F57" t="n">
-        <v>11350</v>
+        <v>1285</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>快</t>
+          <t>样例过小</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AV-155资源</t>
+          <t>AV-森林资源</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://155api.com/api.php/provide/vod</t>
+          <t>https://slapibf.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -13493,14 +14003,14 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>内裤走光后宫学园只有我一MOODYZ大崎広浩治沙</t>
+          <t>FTHTD-144FALENO学校训练营公共浴池</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>61</v>
+        <v>3553</v>
       </c>
       <c r="F58" t="n">
-        <v>11045</v>
+        <v>11092</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -13516,12 +14026,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>性吧资源</t>
+          <t>AV-辣椒资源</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://xingba111.com/api.php/provide/vod</t>
+          <t>https://apilj.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -13531,14 +14041,14 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">DASS-303 被派遣按摩師 按摩到敏感部位 </t>
+          <t>泌尿科的美人女医8人プラネットプラス伊织凉子,管</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>545</v>
+        <v>714</v>
       </c>
       <c r="F59" t="n">
-        <v>7924</v>
+        <v>10868</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -13547,19 +14057,19 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AV-番号资源</t>
+          <t>AV-155资源</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>http://fhapi9.com/api.php/provide/vod</t>
+          <t>https://155api.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -13569,14 +14079,14 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>[SSNI-666] 极品人妻被睡服，巨乳爆操内</t>
+          <t>内裤走光后宫学园只有我一MOODYZ大崎広浩治沙</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>605</v>
+        <v>56</v>
       </c>
       <c r="F60" t="n">
-        <v>7269</v>
+        <v>10738</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -13585,19 +14095,19 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>🔞杏吧资源</t>
+          <t>🔞森林资源</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://xingba222.com/api.php/provide/vod</t>
+          <t>https://beiyong.slapibf.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -13607,14 +14117,14 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">DASS-303 被派遣按摩師 按摩到敏感部位 </t>
+          <t>FTHTD-144FALENO学校训练营公共浴池</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>528</v>
+        <v>546</v>
       </c>
       <c r="F61" t="n">
-        <v>6395</v>
+        <v>10570</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -13630,12 +14140,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AV-乐播资源</t>
+          <t>性吧资源</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://lbapi9.com/api.php/provide/vod</t>
+          <t>https://xingba111.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -13645,14 +14155,14 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>[无码] 苗条人妻床上骚劲爆棚，风骚妩媚狂求内射</t>
+          <t xml:space="preserve">DASS-303 被派遣按摩師 按摩到敏感部位 </t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>714</v>
+        <v>486</v>
       </c>
       <c r="F62" t="n">
-        <v>5055</v>
+        <v>7765</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -13668,12 +14178,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AV-森林资源</t>
+          <t>AV-番号资源</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://slapibf.com/api.php/provide/vod</t>
+          <t>http://fhapi9.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -13683,14 +14193,14 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>FTHTD-144FALENO学校训练营公共浴池</t>
+          <t>[SSNI-666] 极品人妻被睡服，巨乳爆操内</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>390</v>
+        <v>686</v>
       </c>
       <c r="F63" t="n">
-        <v>3419</v>
+        <v>5804</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -13699,19 +14209,19 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>🔞豆豆资源</t>
+          <t>AV-鲨鱼资源</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://api.douapi.cc/api.php/provide/vod</t>
+          <t>https://shayuapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -13721,35 +14231,35 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>美腿玉足控韩国水娃【Hella_cute】顶级吊</t>
+          <t>[瘦猴勾搭] 良家人妻被撩到腿软，眼睛妹妹骚穴求</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>338</v>
+        <v>7451</v>
       </c>
       <c r="F64" t="n">
-        <v>855</v>
+        <v>5126</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>快</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>🔞滴滴资源</t>
+          <t>AV-乐播资源</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://api.ddapi.cc/api.php/provide/vod</t>
+          <t>https://lbapi9.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -13759,18 +14269,18 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>双飞学生妹【蔡萝莉】SM捆绑~白丝足交~强制高潮</t>
+          <t>[无码] 苗条人妻床上骚劲爆棚，风骚妩媚狂求内射</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>328</v>
+        <v>873</v>
       </c>
       <c r="F65" t="n">
-        <v>838</v>
+        <v>5019</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>快</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -13782,12 +14292,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AV-JKUN资源</t>
+          <t>🔞杏吧资源</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://jkunzyapi.com/api.php/provide/vod</t>
+          <t>https://xingba222.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -13797,18 +14307,18 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>pacopacomama-072023_880-</t>
+          <t xml:space="preserve">DASS-303 被派遣按摩師 按摩到敏感部位 </t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>48</v>
+        <v>532</v>
       </c>
       <c r="F66" t="n">
-        <v>642</v>
+        <v>2595</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>快</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -13820,12 +14330,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AV-玉兔资源</t>
+          <t>🔞豆豆资源</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://apiyutu.com/api.php/provide/vod</t>
+          <t>https://api.douapi.cc/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -13835,14 +14345,14 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>家庭旅馆偷拍性饥渴嫂子偷情小叔子裤子都没脱就主动</t>
+          <t>美腿玉足控韩国水娃【Hella_cute】顶级吊</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>375</v>
+        <v>337</v>
       </c>
       <c r="F67" t="n">
-        <v>471</v>
+        <v>896</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -13858,12 +14368,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AV-老色逼资源</t>
+          <t>🔞滴滴资源</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://apilsbzy1.com/api.php/provide/vod</t>
+          <t>https://api.ddapi.cc/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -13873,14 +14383,14 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>家庭旅馆偷拍性饥渴嫂子偷情小叔子裤子都没脱就主动</t>
+          <t>双飞学生妹【蔡萝莉】SM捆绑~白丝足交~强制高潮</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>225</v>
+        <v>422</v>
       </c>
       <c r="F68" t="n">
-        <v>466</v>
+        <v>839</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -13896,12 +14406,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AV-奶香香</t>
+          <t>AV-JKUN资源</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://Naixxzy.com/api.php/provide/vod</t>
+          <t>https://jkunzyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -13911,14 +14421,14 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>[换脸]孙彩瑛 热热的骚逼..</t>
+          <t>pacopacomama-072023_880-</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>565</v>
+        <v>426</v>
       </c>
       <c r="F69" t="n">
-        <v>326</v>
+        <v>638</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -13927,19 +14437,19 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>🔞桃花资源</t>
+          <t>AV-奥斯卡资源</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://thzy1.me/api.php/provide/vod</t>
+          <t>https://aosikazy.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -13949,18 +14459,18 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>[HornyVerse]_Jane_Doe_Fu</t>
+          <t>真实与后妈乱伦9个月</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>522</v>
+        <v>619</v>
       </c>
       <c r="F70" t="n">
-        <v>248</v>
+        <v>576</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>慢</t>
+          <t>中</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -13972,12 +14482,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>🔞-大奶子-</t>
+          <t>AV-老色逼资源</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://apidanaizi.com/api.php/provide/vod</t>
+          <t>https://apilsbzy1.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -13987,18 +14497,18 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>【最新自录-清纯甜美二次元美少女】白裙情趣装罕见</t>
+          <t>家庭旅馆偷拍性饥渴嫂子偷情小叔子裤子都没脱就主动</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>571</v>
+        <v>517</v>
       </c>
       <c r="F71" t="n">
-        <v>223</v>
+        <v>482</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>慢</t>
+          <t>中</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -14010,12 +14520,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AV-奥斯卡资源</t>
+          <t>AV-玉兔资源</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://aosikazy.com/api.php/provide/vod</t>
+          <t>https://apiyutu.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -14025,35 +14535,35 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>真实与后妈乱伦9个月</t>
+          <t>家庭旅馆偷拍性饥渴嫂子偷情小叔子裤子都没脱就主动</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>665</v>
+        <v>382</v>
       </c>
       <c r="F72" t="n">
-        <v>178</v>
+        <v>417</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>慢</t>
+          <t>中</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>🔞小鸡资源</t>
+          <t>AV-奶香香</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://api.xiaojizy.live/provide/vod</t>
+          <t>https://Naixxzy.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -14063,18 +14573,18 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>李素英合3</t>
+          <t>[换脸]孙彩瑛 热热的骚逼..</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>281</v>
+        <v>578</v>
       </c>
       <c r="F73" t="n">
-        <v>176</v>
+        <v>322</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>慢</t>
+          <t>中</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -14086,12 +14596,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>🔞黑料资源</t>
+          <t>🔞-大奶子-</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://www.heiliaozyapi.com/api.php/provide/vod</t>
+          <t>https://apidanaizi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -14101,14 +14611,14 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>绿播福利姬女神下海硬控你十分钟一看就高端货超美脸</t>
+          <t>【最新自录-清纯甜美二次元美少女】白裙情趣装罕见</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>985</v>
+        <v>522</v>
       </c>
       <c r="F74" t="n">
-        <v>148</v>
+        <v>234</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -14117,19 +14627,19 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AV-91麻豆</t>
+          <t>🔞桃花资源</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://91md.me/api.php/provide/vod</t>
+          <t>https://thzy1.me/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -14139,14 +14649,14 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>被老师欺负的黑丝女高-桥本香菜</t>
+          <t>[HornyVerse]_Jane_Doe_Fu</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2328</v>
+        <v>524</v>
       </c>
       <c r="F75" t="n">
-        <v>129</v>
+        <v>220</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -14155,7 +14665,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -14181,10 +14691,10 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>444</v>
+        <v>395</v>
       </c>
       <c r="F76" t="n">
-        <v>83</v>
+        <v>189</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -14200,12 +14710,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AV-souav资源</t>
+          <t>🔞小鸡资源</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://api.souavzy.vip/api.php/provide/vod</t>
+          <t>https://api.xiaojizy.live/provide/vod</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -14215,37 +14725,35 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>白嫩美女月月无套内射初体验</t>
+          <t>李素英合3</t>
         </is>
       </c>
       <c r="E77" t="n">
         <v>307</v>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F77" t="n">
+        <v>171</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>样例过小</t>
+          <t>慢</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>黄色资源啊啊</t>
+          <t>🔞黑料资源</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://hsckzy888.com/api.php/provide/vod</t>
+          <t>https://www.heiliaozyapi.com/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -14255,39 +14763,35 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>公共厕所肉便器 我二话 高岭千佳</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>绿播福利姬女神下海硬控你十分钟一看就高端货超美脸</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>891</v>
+      </c>
+      <c r="F78" t="n">
+        <v>135</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>慢</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>🔞黄色仓库</t>
+          <t>AV-91麻豆</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://hsckzy.xyz/api.php/provide/vod</t>
+          <t>https://91md.me/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -14297,22 +14801,18 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>公共厕所肉便器 我二话 高岭千佳</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>被老师欺负的黑丝女高-桥本香菜</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>784</v>
+      </c>
+      <c r="F79" t="n">
+        <v>130</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>未测出</t>
+          <t>慢</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -14324,12 +14824,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>🔞souavZY</t>
+          <t>AV-souav资源</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://api.souavzyw.net/api.php/provide/vod</t>
+          <t>https://api.souavzy.vip/api.php/provide/vod</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -14339,11 +14839,11 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>与儿子所在托儿所的巨乳人妻老师缠绵做爱～老师太过</t>
+          <t>白嫩美女月月无套内射初体验</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>455</v>
+        <v>944</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -14364,36 +14864,160 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>黄色资源啊啊</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>https://hsckzy888.com/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>公共厕所肉便器 我二话 高岭千佳</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>🔞黄色仓库</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>https://hsckzy.xyz/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>公共厕所肉便器 我二话 高岭千佳</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>未测出</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>🔞souavZY</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>https://api.souavzyw.net/api.php/provide/vod</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>与儿子所在托儿所的巨乳人妻老师缠绵做爱～老师太过</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>431</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>样例过小</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
           <t>🔞色猫资源</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>https://caiji.semaozy.net/inc/apijson_vod.php/provide/vod</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
         <is>
           <t>未测出</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>是</t>
         </is>
